--- a/Waterjet Efficiency Shiftwise.xlsx
+++ b/Waterjet Efficiency Shiftwise.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6806" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6802" uniqueCount="76">
   <si>
     <t>DATE</t>
   </si>
@@ -186,10 +186,10 @@
     <t>06/02/2026</t>
   </si>
   <si>
-    <t>14/01/2026</t>
+    <t>16/01/2026</t>
   </si>
   <si>
-    <t>16/01/2026</t>
+    <t>14/01/2026</t>
   </si>
   <si>
     <t>08/02/2026</t>
@@ -240,10 +240,13 @@
     <t>29/01/2026</t>
   </si>
   <si>
-    <t>04/02/2026</t>
+    <t>11/02/2026</t>
   </si>
   <si>
     <t>KASAB FLUTE</t>
+  </si>
+  <si>
+    <t>04/02/2026</t>
   </si>
 </sst>
 </file>
@@ -44338,7 +44341,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="15.7109375" customWidth="1"/>
@@ -44439,36 +44442,36 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
       </c>
       <c r="C5">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
       </c>
       <c r="E5">
-        <v>3600</v>
+        <v>4200</v>
       </c>
       <c r="F5">
-        <v>3131</v>
+        <v>3204</v>
       </c>
       <c r="G5" s="5">
-        <v>469</v>
+        <v>996</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
       </c>
       <c r="C6">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -44477,159 +44480,159 @@
         <v>4200</v>
       </c>
       <c r="F6">
-        <v>3204</v>
+        <v>3320</v>
       </c>
       <c r="G6" s="5">
-        <v>996</v>
+        <v>880</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>4200</v>
+        <v>8000</v>
       </c>
       <c r="F7">
-        <v>3320</v>
+        <v>571</v>
       </c>
       <c r="G7" s="5">
-        <v>880</v>
+        <v>7429</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
       </c>
       <c r="E8">
-        <v>8000</v>
+        <v>6400</v>
       </c>
       <c r="F8">
-        <v>571</v>
+        <v>3908</v>
       </c>
       <c r="G8" s="5">
-        <v>7429</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="D9" t="s">
         <v>34</v>
       </c>
       <c r="E9">
-        <v>6400</v>
+        <v>7700</v>
       </c>
       <c r="F9">
-        <v>3908</v>
+        <v>2900</v>
       </c>
       <c r="G9" s="5">
-        <v>2492</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="D10" t="s">
         <v>34</v>
       </c>
       <c r="E10">
-        <v>7700</v>
+        <v>5300</v>
       </c>
       <c r="F10">
-        <v>2900</v>
+        <v>3854</v>
       </c>
       <c r="G10" s="5">
-        <v>4800</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="D11" t="s">
         <v>34</v>
       </c>
       <c r="E11">
-        <v>5300</v>
+        <v>7750</v>
       </c>
       <c r="F11">
-        <v>3854</v>
+        <v>414</v>
       </c>
       <c r="G11" s="5">
-        <v>1446</v>
+        <v>7336</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D12" t="s">
         <v>34</v>
       </c>
       <c r="E12">
-        <v>7750</v>
+        <v>8000</v>
       </c>
       <c r="F12">
-        <v>414</v>
+        <v>2908</v>
       </c>
       <c r="G12" s="5">
-        <v>7336</v>
+        <v>5092</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C13">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D13" t="s">
         <v>34</v>
@@ -44638,21 +44641,21 @@
         <v>8000</v>
       </c>
       <c r="F13">
-        <v>2908</v>
+        <v>1911</v>
       </c>
       <c r="G13" s="5">
-        <v>5092</v>
+        <v>6089</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D14" t="s">
         <v>34</v>
@@ -44661,113 +44664,113 @@
         <v>8000</v>
       </c>
       <c r="F14">
-        <v>1911</v>
+        <v>3924</v>
       </c>
       <c r="G14" s="5">
-        <v>6089</v>
+        <v>4076</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C15">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D15" t="s">
         <v>34</v>
       </c>
       <c r="E15">
-        <v>8000</v>
+        <v>7700</v>
       </c>
       <c r="F15">
-        <v>3924</v>
+        <v>3109</v>
       </c>
       <c r="G15" s="5">
-        <v>4076</v>
+        <v>4591</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C16">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="D16" t="s">
         <v>34</v>
       </c>
       <c r="E16">
-        <v>7700</v>
+        <v>8000</v>
       </c>
       <c r="F16">
-        <v>3109</v>
+        <v>936</v>
       </c>
       <c r="G16" s="5">
-        <v>4591</v>
+        <v>7064</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C17">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D17" t="s">
         <v>34</v>
       </c>
       <c r="E17">
-        <v>8000</v>
+        <v>9600</v>
       </c>
       <c r="F17">
-        <v>936</v>
+        <v>303</v>
       </c>
       <c r="G17" s="5">
-        <v>7064</v>
+        <v>9297</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C18">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E18">
         <v>9600</v>
       </c>
       <c r="F18">
-        <v>303</v>
+        <v>3408</v>
       </c>
       <c r="G18" s="5">
-        <v>9297</v>
+        <v>6192</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C19">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D19" t="s">
         <v>33</v>
@@ -44776,240 +44779,214 @@
         <v>9600</v>
       </c>
       <c r="F19">
-        <v>3408</v>
+        <v>1304</v>
       </c>
       <c r="G19" s="5">
-        <v>6192</v>
+        <v>8296</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C20">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E20">
-        <v>9600</v>
+        <v>7800</v>
       </c>
       <c r="F20">
-        <v>1304</v>
+        <v>0</v>
       </c>
       <c r="G20" s="5">
-        <v>8296</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C21">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D21" t="s">
         <v>34</v>
       </c>
       <c r="E21">
-        <v>7800</v>
+        <v>8000</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>932</v>
       </c>
       <c r="G21" s="5">
-        <v>7800</v>
+        <v>7068</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C22">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
         <v>34</v>
       </c>
       <c r="E22">
-        <v>8000</v>
+        <v>3600</v>
       </c>
       <c r="F22">
-        <v>932</v>
+        <v>3128</v>
       </c>
       <c r="G22" s="5">
-        <v>7068</v>
+        <v>472</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C23">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="D23" t="s">
         <v>34</v>
       </c>
       <c r="E23">
-        <v>3600</v>
+        <v>7700</v>
       </c>
       <c r="F23">
-        <v>3128</v>
+        <v>1864</v>
       </c>
       <c r="G23" s="5">
-        <v>472</v>
+        <v>5836</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C24">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E24">
-        <v>7700</v>
+        <v>6700</v>
       </c>
       <c r="F24">
-        <v>1864</v>
+        <v>4054</v>
       </c>
       <c r="G24" s="5">
-        <v>5836</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C25">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D25" t="s">
         <v>33</v>
       </c>
       <c r="E25">
-        <v>6700</v>
+        <v>13350</v>
       </c>
       <c r="F25">
-        <v>4054</v>
+        <v>4113</v>
       </c>
       <c r="G25" s="5">
-        <v>2646</v>
+        <v>9237</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="C26">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D26" t="s">
         <v>33</v>
       </c>
       <c r="E26">
-        <v>13350</v>
+        <v>9600</v>
       </c>
       <c r="F26">
-        <v>4113</v>
+        <v>3473</v>
       </c>
       <c r="G26" s="5">
-        <v>9237</v>
+        <v>6127</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C27">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
         <v>33</v>
       </c>
       <c r="E27">
-        <v>4300</v>
+        <v>6650</v>
       </c>
       <c r="F27">
-        <v>3842</v>
+        <v>4084</v>
       </c>
       <c r="G27" s="5">
-        <v>458</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28">
-        <v>27</v>
-      </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C28">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="D28" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="E28">
-        <v>9600</v>
+        <v>6000</v>
       </c>
       <c r="F28">
-        <v>3473</v>
+        <v>0</v>
       </c>
       <c r="G28" s="5">
-        <v>6127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29">
-        <v>127</v>
-      </c>
-      <c r="D29" t="s">
-        <v>33</v>
-      </c>
-      <c r="E29">
-        <v>6650</v>
-      </c>
-      <c r="F29">
-        <v>4084</v>
-      </c>
-      <c r="G29" s="5">
-        <v>2566</v>
+        <v>6000</v>
       </c>
     </row>
   </sheetData>
@@ -45019,7 +44996,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" style="6" customWidth="1"/>
@@ -45055,7 +45032,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B3" s="6">
         <v>144</v>
@@ -45069,16 +45046,16 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B4" s="6">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C4" s="6">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -45086,26 +45063,12 @@
         <v>61</v>
       </c>
       <c r="B5" s="6">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C5" s="6">
-        <v>8000</v>
+        <v>7750</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="6">
-        <v>152</v>
-      </c>
-      <c r="C6" s="6">
-        <v>7750</v>
-      </c>
-      <c r="D6" s="6" t="s">
         <v>34</v>
       </c>
     </row>

--- a/Waterjet Efficiency Shiftwise.xlsx
+++ b/Waterjet Efficiency Shiftwise.xlsx
@@ -237,10 +237,10 @@
     <t>22/01/2026</t>
   </si>
   <si>
-    <t>29/01/2026</t>
+    <t>11/02/2026</t>
   </si>
   <si>
-    <t>11/02/2026</t>
+    <t>29/01/2026</t>
   </si>
   <si>
     <t>04/02/2026</t>
@@ -46311,68 +46311,71 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
         <v>72</v>
       </c>
       <c r="C26">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="D26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E26">
-        <v>9600</v>
+        <v>6000</v>
       </c>
       <c r="F26">
-        <v>3576</v>
+        <v>0</v>
       </c>
       <c r="G26" s="5">
-        <v>6024</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27">
+        <v>135</v>
+      </c>
+      <c r="D27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27">
+        <v>9600</v>
+      </c>
+      <c r="F27">
+        <v>3576</v>
+      </c>
+      <c r="G27" s="5">
+        <v>6024</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
         <v>28</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>71</v>
       </c>
-      <c r="C27">
+      <c r="C28">
         <v>127</v>
       </c>
-      <c r="D27" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27">
+      <c r="D28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28">
         <v>6650</v>
       </c>
-      <c r="F27">
+      <c r="F28">
         <v>4233</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G28" s="5">
         <v>2417</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="B28" t="s">
-        <v>73</v>
-      </c>
-      <c r="C28">
-        <v>150</v>
-      </c>
-      <c r="D28" t="s">
-        <v>34</v>
-      </c>
-      <c r="E28">
-        <v>6000</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28" s="5">
-        <v>6000</v>
       </c>
     </row>
   </sheetData>
@@ -46404,7 +46407,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B2" s="6">
         <v>136</v>

--- a/Waterjet Efficiency Shiftwise.xlsx
+++ b/Waterjet Efficiency Shiftwise.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7027" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7027" uniqueCount="76">
   <si>
     <t>DATE</t>
   </si>
@@ -123,7 +123,7 @@
     <t>FLUTE</t>
   </si>
   <si>
-    <t>KASAB FLUTE</t>
+    <t>SUNSHINE</t>
   </si>
   <si>
     <t>PURE GOLD</t>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>29/01/2026</t>
+  </si>
+  <si>
+    <t>KASAB FLUTE</t>
   </si>
   <si>
     <t>04/02/2026</t>
@@ -722,10 +725,10 @@
         <v>0.8242827196385248</v>
       </c>
       <c r="F2" s="2">
-        <v>0.9022599305104881</v>
+        <v>0.8854281330823822</v>
       </c>
       <c r="G2" s="3">
-        <v>-7.797721087196329</v>
+        <v>-6.114541344385738</v>
       </c>
       <c r="H2">
         <v>10</v>
@@ -752,10 +755,10 @@
         <v>0.7850218886804252</v>
       </c>
       <c r="P2" s="2">
-        <v>0.8897323197824237</v>
+        <v>0.8567540311007951</v>
       </c>
       <c r="Q2" s="3">
-        <v>-10.47104311019985</v>
+        <v>-7.173214242036985</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -775,10 +778,10 @@
         <v>0.9464569374360094</v>
       </c>
       <c r="F3" s="2">
-        <v>0.9022599305104881</v>
+        <v>0.8854281330823822</v>
       </c>
       <c r="G3" s="3">
-        <v>4.419700692552131</v>
+        <v>6.102880435362723</v>
       </c>
       <c r="H3">
         <v>18</v>
@@ -805,10 +808,10 @@
         <v>0.9456287758329098</v>
       </c>
       <c r="P3" s="2">
-        <v>0.8897323197824237</v>
+        <v>0.8567540311007951</v>
       </c>
       <c r="Q3" s="3">
-        <v>5.589645605048609</v>
+        <v>8.887474473211476</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -822,16 +825,16 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>0.1856314882065955</v>
       </c>
       <c r="F4" s="2">
-        <v>0.9022599305104881</v>
+        <v>0.8854281330823822</v>
       </c>
       <c r="G4" s="3">
-        <v>-90.22599305104882</v>
+        <v>-69.97966448757866</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -852,16 +855,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="1">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="O4" s="2">
-        <v>0</v>
+        <v>0.1856314882065955</v>
       </c>
       <c r="P4" s="2">
-        <v>0.8897323197824237</v>
+        <v>0.8567540311007951</v>
       </c>
       <c r="Q4" s="3">
-        <v>-88.97323197824237</v>
+        <v>-67.11225428941997</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -46320,7 +46323,7 @@
         <v>150</v>
       </c>
       <c r="D26" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="E26">
         <v>6000</v>
@@ -46421,7 +46424,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B3" s="6">
         <v>144</v>

--- a/Waterjet Efficiency Shiftwise.xlsx
+++ b/Waterjet Efficiency Shiftwise.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7027" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7027" uniqueCount="75">
   <si>
     <t>DATE</t>
   </si>
@@ -241,9 +241,6 @@
   </si>
   <si>
     <t>29/01/2026</t>
-  </si>
-  <si>
-    <t>KASAB FLUTE</t>
   </si>
   <si>
     <t>04/02/2026</t>
@@ -46323,7 +46320,7 @@
         <v>150</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="E26">
         <v>6000</v>
@@ -46424,7 +46421,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3" s="6">
         <v>144</v>

--- a/Waterjet Efficiency Shiftwise.xlsx
+++ b/Waterjet Efficiency Shiftwise.xlsx
@@ -254,7 +254,7 @@
     <numFmt numFmtId="164" formatCode="0.00%"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,15 +270,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF649FAD"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -288,12 +281,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCFE2F3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -339,7 +326,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>

--- a/Waterjet Efficiency Shiftwise.xlsx
+++ b/Waterjet Efficiency Shiftwise.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7237" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7241" uniqueCount="76">
   <si>
     <t>DATE</t>
   </si>
@@ -189,6 +189,9 @@
     <t>06/02/2026</t>
   </si>
   <si>
+    <t>11/02/2026</t>
+  </si>
+  <si>
     <t>16/01/2026</t>
   </si>
   <si>
@@ -238,9 +241,6 @@
   </si>
   <si>
     <t>22/01/2026</t>
-  </si>
-  <si>
-    <t>11/02/2026</t>
   </si>
   <si>
     <t>29/01/2026</t>
@@ -47104,7 +47104,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="15.7109375" customWidth="1"/>
@@ -47205,36 +47205,36 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
       </c>
       <c r="C5">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>4200</v>
+        <v>6800</v>
       </c>
       <c r="F5">
-        <v>3435</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5">
-        <v>765</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
       </c>
       <c r="C6">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -47243,159 +47243,159 @@
         <v>4200</v>
       </c>
       <c r="F6">
-        <v>3490</v>
+        <v>3435</v>
       </c>
       <c r="G6" s="5">
-        <v>710</v>
+        <v>765</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
       </c>
       <c r="C7">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>8000</v>
+        <v>4200</v>
       </c>
       <c r="F7">
-        <v>849</v>
+        <v>3490</v>
       </c>
       <c r="G7" s="5">
-        <v>7151</v>
+        <v>710</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>59</v>
       </c>
       <c r="C8">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
       </c>
       <c r="E8">
-        <v>6400</v>
+        <v>8000</v>
       </c>
       <c r="F8">
-        <v>4189</v>
+        <v>849</v>
       </c>
       <c r="G8" s="5">
-        <v>2211</v>
+        <v>7151</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>60</v>
       </c>
       <c r="C9">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D9" t="s">
         <v>34</v>
       </c>
       <c r="E9">
-        <v>7700</v>
+        <v>6400</v>
       </c>
       <c r="F9">
-        <v>3176</v>
+        <v>4189</v>
       </c>
       <c r="G9" s="5">
-        <v>4524</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>61</v>
       </c>
       <c r="C10">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D10" t="s">
         <v>34</v>
       </c>
       <c r="E10">
-        <v>5300</v>
+        <v>7700</v>
       </c>
       <c r="F10">
-        <v>4137</v>
+        <v>3176</v>
       </c>
       <c r="G10" s="5">
-        <v>1163</v>
+        <v>4524</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>62</v>
       </c>
       <c r="C11">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D11" t="s">
         <v>34</v>
       </c>
       <c r="E11">
-        <v>7750</v>
+        <v>5300</v>
       </c>
       <c r="F11">
-        <v>693</v>
+        <v>4137</v>
       </c>
       <c r="G11" s="5">
-        <v>7057</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>63</v>
       </c>
       <c r="C12">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="D12" t="s">
         <v>34</v>
       </c>
       <c r="E12">
-        <v>8000</v>
+        <v>7750</v>
       </c>
       <c r="F12">
-        <v>3172</v>
+        <v>693</v>
       </c>
       <c r="G12" s="5">
-        <v>4828</v>
+        <v>7057</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>64</v>
       </c>
       <c r="C13">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D13" t="s">
         <v>34</v>
@@ -47404,21 +47404,21 @@
         <v>8000</v>
       </c>
       <c r="F13">
-        <v>2181</v>
+        <v>3172</v>
       </c>
       <c r="G13" s="5">
-        <v>5819</v>
+        <v>4828</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>65</v>
       </c>
       <c r="C14">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D14" t="s">
         <v>34</v>
@@ -47427,113 +47427,113 @@
         <v>8000</v>
       </c>
       <c r="F14">
-        <v>4203</v>
+        <v>2181</v>
       </c>
       <c r="G14" s="5">
-        <v>3797</v>
+        <v>5819</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C15">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D15" t="s">
         <v>34</v>
       </c>
       <c r="E15">
-        <v>7700</v>
+        <v>8000</v>
       </c>
       <c r="F15">
-        <v>3386</v>
+        <v>4203</v>
       </c>
       <c r="G15" s="5">
-        <v>4314</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C16">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="D16" t="s">
         <v>34</v>
       </c>
       <c r="E16">
-        <v>8000</v>
+        <v>7700</v>
       </c>
       <c r="F16">
-        <v>1211</v>
+        <v>3386</v>
       </c>
       <c r="G16" s="5">
-        <v>6789</v>
+        <v>4314</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C17">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D17" t="s">
         <v>34</v>
       </c>
       <c r="E17">
-        <v>9600</v>
+        <v>8000</v>
       </c>
       <c r="F17">
-        <v>584</v>
+        <v>1211</v>
       </c>
       <c r="G17" s="5">
-        <v>9016</v>
+        <v>6789</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C18">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18">
         <v>9600</v>
       </c>
       <c r="F18">
-        <v>3674</v>
+        <v>584</v>
       </c>
       <c r="G18" s="5">
-        <v>5926</v>
+        <v>9016</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>68</v>
       </c>
       <c r="C19">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D19" t="s">
         <v>33</v>
@@ -47542,216 +47542,239 @@
         <v>9600</v>
       </c>
       <c r="F19">
-        <v>1544</v>
+        <v>3674</v>
       </c>
       <c r="G19" s="5">
-        <v>8056</v>
+        <v>5926</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>69</v>
       </c>
       <c r="C20">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E20">
-        <v>7800</v>
+        <v>9600</v>
       </c>
       <c r="F20">
-        <v>328</v>
+        <v>1544</v>
       </c>
       <c r="G20" s="5">
-        <v>7472</v>
+        <v>8056</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C21">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D21" t="s">
         <v>34</v>
       </c>
       <c r="E21">
-        <v>8000</v>
+        <v>7800</v>
       </c>
       <c r="F21">
-        <v>1149</v>
+        <v>328</v>
       </c>
       <c r="G21" s="5">
-        <v>6851</v>
+        <v>7472</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="C22">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="D22" t="s">
         <v>34</v>
       </c>
       <c r="E22">
-        <v>3600</v>
+        <v>8000</v>
       </c>
       <c r="F22">
-        <v>3348</v>
+        <v>1149</v>
       </c>
       <c r="G22" s="5">
-        <v>252</v>
+        <v>6851</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
         <v>71</v>
       </c>
       <c r="C23">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s">
         <v>34</v>
       </c>
       <c r="E23">
-        <v>7700</v>
+        <v>3600</v>
       </c>
       <c r="F23">
-        <v>2141</v>
+        <v>3348</v>
       </c>
       <c r="G23" s="5">
-        <v>5559</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
         <v>72</v>
       </c>
       <c r="C24">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E24">
-        <v>6700</v>
+        <v>7700</v>
       </c>
       <c r="F24">
-        <v>4352</v>
+        <v>2141</v>
       </c>
       <c r="G24" s="5">
-        <v>2348</v>
+        <v>5559</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C25">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D25" t="s">
         <v>33</v>
       </c>
       <c r="E25">
-        <v>13350</v>
+        <v>6700</v>
       </c>
       <c r="F25">
-        <v>4404</v>
+        <v>4352</v>
       </c>
       <c r="G25" s="5">
-        <v>8946</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="C26">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E26">
-        <v>6000</v>
+        <v>13350</v>
       </c>
       <c r="F26">
-        <v>137</v>
+        <v>4404</v>
       </c>
       <c r="G26" s="5">
-        <v>5863</v>
+        <v>8946</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C27">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="D27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E27">
-        <v>9600</v>
+        <v>6000</v>
       </c>
       <c r="F27">
-        <v>3708</v>
+        <v>137</v>
       </c>
       <c r="G27" s="5">
-        <v>5892</v>
+        <v>5863</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28">
+        <v>135</v>
+      </c>
+      <c r="D28" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28">
+        <v>9600</v>
+      </c>
+      <c r="F28">
+        <v>3708</v>
+      </c>
+      <c r="G28" s="5">
+        <v>5892</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B28" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28">
+      <c r="B29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29">
         <v>127</v>
       </c>
-      <c r="D28" t="s">
-        <v>33</v>
-      </c>
-      <c r="E28">
+      <c r="D29" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29">
         <v>6650</v>
       </c>
-      <c r="F28">
+      <c r="F29">
         <v>4375</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G29" s="5">
         <v>2275</v>
       </c>
     </row>
@@ -47762,7 +47785,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" style="6" customWidth="1"/>
@@ -47812,7 +47835,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B4" s="6">
         <v>151</v>
@@ -47826,7 +47849,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B5" s="6">
         <v>152</v>
@@ -47836,6 +47859,20 @@
       </c>
       <c r="D5" s="6" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="6">
+        <v>154</v>
+      </c>
+      <c r="C6" s="6">
+        <v>6750</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Waterjet Efficiency Shiftwise.xlsx
+++ b/Waterjet Efficiency Shiftwise.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7474" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7472" uniqueCount="76">
   <si>
     <t>DATE</t>
   </si>
@@ -234,7 +234,7 @@
     <t>10/02/2026</t>
   </si>
   <si>
-    <t>07/01/2026</t>
+    <t>12/02/2026</t>
   </si>
   <si>
     <t>02/02/2026</t>
@@ -49113,19 +49113,19 @@
         <v>71</v>
       </c>
       <c r="C23">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23">
-        <v>3600</v>
+        <v>6750</v>
       </c>
       <c r="F23">
-        <v>3380</v>
+        <v>0</v>
       </c>
       <c r="G23" s="5">
-        <v>220</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -49273,7 +49273,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" style="6" customWidth="1"/>
@@ -49349,20 +49349,6 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="6">
-        <v>154</v>
-      </c>
-      <c r="C6" s="6">
-        <v>6750</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Waterjet Efficiency Shiftwise.xlsx
+++ b/Waterjet Efficiency Shiftwise.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7903" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7909" uniqueCount="76">
   <si>
     <t>DATE</t>
   </si>
@@ -183,9 +183,6 @@
     <t>Pending Meters</t>
   </si>
   <si>
-    <t>23/01/2026</t>
-  </si>
-  <si>
     <t>26/01/2026</t>
   </si>
   <si>
@@ -208,9 +205,6 @@
   </si>
   <si>
     <t>31/01/2026</t>
-  </si>
-  <si>
-    <t>17/01/2026</t>
   </si>
   <si>
     <t>09/02/2026</t>
@@ -244,6 +238,9 @@
   </si>
   <si>
     <t>22/01/2026</t>
+  </si>
+  <si>
+    <t>23/01/2026</t>
   </si>
   <si>
     <t>29/01/2026</t>
@@ -51378,7 +51375,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="15.7109375" customWidth="1"/>
@@ -51410,105 +51407,105 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
       </c>
       <c r="C2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
         <v>35</v>
       </c>
       <c r="E2">
-        <v>8000</v>
+        <v>7650</v>
       </c>
       <c r="F2">
-        <v>3578</v>
+        <v>3635</v>
       </c>
       <c r="G2" s="5">
-        <v>4422</v>
+        <v>4015</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
       </c>
       <c r="C3">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="D3" t="s">
         <v>35</v>
       </c>
       <c r="E3">
-        <v>7650</v>
+        <v>7700</v>
       </c>
       <c r="F3">
-        <v>3635</v>
+        <v>1398</v>
       </c>
       <c r="G3" s="5">
-        <v>4015</v>
+        <v>6302</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
       </c>
       <c r="C4">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>7700</v>
+        <v>6800</v>
       </c>
       <c r="F4">
-        <v>1398</v>
+        <v>173</v>
       </c>
       <c r="G4" s="5">
-        <v>6302</v>
+        <v>6627</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
       </c>
       <c r="C5">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>6800</v>
+        <v>4200</v>
       </c>
       <c r="F5">
-        <v>173</v>
+        <v>3777</v>
       </c>
       <c r="G5" s="5">
-        <v>6627</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
       </c>
       <c r="C6">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D6" t="s">
         <v>34</v>
@@ -51517,159 +51514,159 @@
         <v>4200</v>
       </c>
       <c r="F6">
-        <v>3777</v>
+        <v>3825</v>
       </c>
       <c r="G6" s="5">
-        <v>423</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
       </c>
       <c r="C7">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>4200</v>
+        <v>8000</v>
       </c>
       <c r="F7">
-        <v>3825</v>
+        <v>1278</v>
       </c>
       <c r="G7" s="5">
-        <v>375</v>
+        <v>6722</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>60</v>
       </c>
       <c r="C8">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D8" t="s">
         <v>35</v>
       </c>
       <c r="E8">
-        <v>8000</v>
+        <v>6400</v>
       </c>
       <c r="F8">
-        <v>1278</v>
+        <v>4605</v>
       </c>
       <c r="G8" s="5">
-        <v>6722</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>61</v>
       </c>
       <c r="C9">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="D9" t="s">
         <v>35</v>
       </c>
       <c r="E9">
-        <v>6400</v>
+        <v>7700</v>
       </c>
       <c r="F9">
-        <v>4605</v>
+        <v>3592</v>
       </c>
       <c r="G9" s="5">
-        <v>1795</v>
+        <v>4108</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C10">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D10" t="s">
         <v>35</v>
       </c>
       <c r="E10">
-        <v>7700</v>
+        <v>8000</v>
       </c>
       <c r="F10">
-        <v>3592</v>
+        <v>3721</v>
       </c>
       <c r="G10" s="5">
-        <v>4108</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="D11" t="s">
         <v>35</v>
       </c>
       <c r="E11">
-        <v>5300</v>
+        <v>7750</v>
       </c>
       <c r="F11">
-        <v>4562</v>
+        <v>1082</v>
       </c>
       <c r="G11" s="5">
-        <v>738</v>
+        <v>6668</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
       </c>
       <c r="E12">
-        <v>7750</v>
+        <v>8000</v>
       </c>
       <c r="F12">
-        <v>1082</v>
+        <v>3579</v>
       </c>
       <c r="G12" s="5">
-        <v>6668</v>
+        <v>4421</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C13">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D13" t="s">
         <v>35</v>
@@ -51678,21 +51675,21 @@
         <v>8000</v>
       </c>
       <c r="F13">
-        <v>3579</v>
+        <v>2575</v>
       </c>
       <c r="G13" s="5">
-        <v>4421</v>
+        <v>5425</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C14">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D14" t="s">
         <v>35</v>
@@ -51701,113 +51698,113 @@
         <v>8000</v>
       </c>
       <c r="F14">
-        <v>2575</v>
+        <v>4607</v>
       </c>
       <c r="G14" s="5">
-        <v>5425</v>
+        <v>3393</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C15">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D15" t="s">
         <v>35</v>
       </c>
       <c r="E15">
-        <v>8000</v>
+        <v>7700</v>
       </c>
       <c r="F15">
-        <v>4607</v>
+        <v>3800</v>
       </c>
       <c r="G15" s="5">
-        <v>3393</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C16">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="D16" t="s">
         <v>35</v>
       </c>
       <c r="E16">
-        <v>7700</v>
+        <v>8000</v>
       </c>
       <c r="F16">
-        <v>3800</v>
+        <v>1605</v>
       </c>
       <c r="G16" s="5">
-        <v>3900</v>
+        <v>6395</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C17">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D17" t="s">
         <v>35</v>
       </c>
       <c r="E17">
-        <v>8000</v>
+        <v>9600</v>
       </c>
       <c r="F17">
-        <v>1605</v>
+        <v>1003</v>
       </c>
       <c r="G17" s="5">
-        <v>6395</v>
+        <v>8597</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C18">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18">
         <v>9600</v>
       </c>
       <c r="F18">
-        <v>1003</v>
+        <v>4071</v>
       </c>
       <c r="G18" s="5">
-        <v>8597</v>
+        <v>5529</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C19">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D19" t="s">
         <v>34</v>
@@ -51816,239 +51813,216 @@
         <v>9600</v>
       </c>
       <c r="F19">
-        <v>4071</v>
+        <v>1915</v>
       </c>
       <c r="G19" s="5">
-        <v>5529</v>
+        <v>7685</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C20">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E20">
-        <v>9600</v>
+        <v>7800</v>
       </c>
       <c r="F20">
-        <v>1915</v>
+        <v>652</v>
       </c>
       <c r="G20" s="5">
-        <v>7685</v>
+        <v>7148</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="C21">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D21" t="s">
         <v>35</v>
       </c>
       <c r="E21">
-        <v>7800</v>
+        <v>8000</v>
       </c>
       <c r="F21">
-        <v>652</v>
+        <v>1482</v>
       </c>
       <c r="G21" s="5">
-        <v>7148</v>
+        <v>6518</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C22">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E22">
-        <v>8000</v>
+        <v>6750</v>
       </c>
       <c r="F22">
-        <v>1482</v>
+        <v>2</v>
       </c>
       <c r="G22" s="5">
-        <v>6518</v>
+        <v>6748</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C23">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E23">
-        <v>6750</v>
+        <v>7700</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>2550</v>
       </c>
       <c r="G23" s="5">
-        <v>6748</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C24">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E24">
-        <v>7700</v>
+        <v>6700</v>
       </c>
       <c r="F24">
-        <v>2550</v>
+        <v>4681</v>
       </c>
       <c r="G24" s="5">
-        <v>5150</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C25">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D25" t="s">
         <v>34</v>
       </c>
       <c r="E25">
-        <v>6700</v>
+        <v>13350</v>
       </c>
       <c r="F25">
-        <v>4681</v>
+        <v>4846</v>
       </c>
       <c r="G25" s="5">
-        <v>2019</v>
+        <v>8504</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C26">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="D26" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E26">
-        <v>13350</v>
+        <v>6000</v>
       </c>
       <c r="F26">
-        <v>4846</v>
+        <v>573</v>
       </c>
       <c r="G26" s="5">
-        <v>8504</v>
+        <v>5427</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C27">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D27" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E27">
-        <v>6000</v>
+        <v>9600</v>
       </c>
       <c r="F27">
-        <v>573</v>
+        <v>4127</v>
       </c>
       <c r="G27" s="5">
-        <v>5427</v>
+        <v>5473</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C28">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
         <v>34</v>
       </c>
       <c r="E28">
-        <v>9600</v>
+        <v>6650</v>
       </c>
       <c r="F28">
-        <v>4127</v>
+        <v>4788</v>
       </c>
       <c r="G28" s="5">
-        <v>5473</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29">
-        <v>127</v>
-      </c>
-      <c r="D29" t="s">
-        <v>34</v>
-      </c>
-      <c r="E29">
-        <v>6650</v>
-      </c>
-      <c r="F29">
-        <v>4788</v>
-      </c>
-      <c r="G29" s="5">
         <v>1862</v>
       </c>
     </row>
@@ -52059,7 +52033,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" style="6" customWidth="1"/>
@@ -52081,27 +52055,27 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="B2" s="6">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="C2" s="6">
-        <v>9600</v>
+        <v>501.5591931023519</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B3" s="6">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="C3" s="6">
-        <v>9600</v>
+        <v>439.530612762238</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>34</v>
@@ -52109,29 +52083,85 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B4" s="6">
-        <v>151</v>
+        <v>122</v>
       </c>
       <c r="C4" s="6">
-        <v>8000</v>
+        <v>424.2204365634361</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B5" s="6">
+        <v>124</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1304.485146482305</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="6">
+        <v>136</v>
+      </c>
+      <c r="C6" s="6">
+        <v>9600</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="6">
+        <v>144</v>
+      </c>
+      <c r="C7" s="6">
+        <v>9600</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="6">
+        <v>151</v>
+      </c>
+      <c r="C8" s="6">
+        <v>8000</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="6">
         <v>152</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C9" s="6">
         <v>7750</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>35</v>
       </c>
     </row>

--- a/Waterjet Efficiency Shiftwise.xlsx
+++ b/Waterjet Efficiency Shiftwise.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7909" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7909" uniqueCount="77">
   <si>
     <t>DATE</t>
   </si>
@@ -183,6 +183,9 @@
     <t>Pending Meters</t>
   </si>
   <si>
+    <t>23/01/2026</t>
+  </si>
+  <si>
     <t>26/01/2026</t>
   </si>
   <si>
@@ -205,6 +208,9 @@
   </si>
   <si>
     <t>31/01/2026</t>
+  </si>
+  <si>
+    <t>17/01/2026</t>
   </si>
   <si>
     <t>09/02/2026</t>
@@ -238,9 +244,6 @@
   </si>
   <si>
     <t>22/01/2026</t>
-  </si>
-  <si>
-    <t>23/01/2026</t>
   </si>
   <si>
     <t>29/01/2026</t>
@@ -51375,7 +51378,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="15.7109375" customWidth="1"/>
@@ -51407,105 +51410,105 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
       </c>
       <c r="C2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
         <v>35</v>
       </c>
       <c r="E2">
-        <v>7650</v>
+        <v>8000</v>
       </c>
       <c r="F2">
-        <v>3635</v>
+        <v>3578</v>
       </c>
       <c r="G2" s="5">
-        <v>4015</v>
+        <v>4422</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
       </c>
       <c r="C3">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s">
         <v>35</v>
       </c>
       <c r="E3">
-        <v>7700</v>
+        <v>7650</v>
       </c>
       <c r="F3">
-        <v>1398</v>
+        <v>3635</v>
       </c>
       <c r="G3" s="5">
-        <v>6302</v>
+        <v>4015</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
       </c>
       <c r="C4">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>6800</v>
+        <v>7700</v>
       </c>
       <c r="F4">
-        <v>173</v>
+        <v>1398</v>
       </c>
       <c r="G4" s="5">
-        <v>6627</v>
+        <v>6302</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
       </c>
       <c r="C5">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>4200</v>
+        <v>6800</v>
       </c>
       <c r="F5">
-        <v>3777</v>
+        <v>173</v>
       </c>
       <c r="G5" s="5">
-        <v>423</v>
+        <v>6627</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
       </c>
       <c r="C6">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s">
         <v>34</v>
@@ -51514,159 +51517,159 @@
         <v>4200</v>
       </c>
       <c r="F6">
-        <v>3825</v>
+        <v>3777</v>
       </c>
       <c r="G6" s="5">
-        <v>375</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
       </c>
       <c r="C7">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>8000</v>
+        <v>4200</v>
       </c>
       <c r="F7">
-        <v>1278</v>
+        <v>3825</v>
       </c>
       <c r="G7" s="5">
-        <v>6722</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>60</v>
       </c>
       <c r="C8">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="D8" t="s">
         <v>35</v>
       </c>
       <c r="E8">
-        <v>6400</v>
+        <v>8000</v>
       </c>
       <c r="F8">
-        <v>4605</v>
+        <v>1278</v>
       </c>
       <c r="G8" s="5">
-        <v>1795</v>
+        <v>6722</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>61</v>
       </c>
       <c r="C9">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D9" t="s">
         <v>35</v>
       </c>
       <c r="E9">
-        <v>7700</v>
+        <v>6400</v>
       </c>
       <c r="F9">
-        <v>3592</v>
+        <v>4605</v>
       </c>
       <c r="G9" s="5">
-        <v>4108</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C10">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D10" t="s">
         <v>35</v>
       </c>
       <c r="E10">
-        <v>8000</v>
+        <v>7700</v>
       </c>
       <c r="F10">
-        <v>3721</v>
+        <v>3592</v>
       </c>
       <c r="G10" s="5">
-        <v>4279</v>
+        <v>4108</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D11" t="s">
         <v>35</v>
       </c>
       <c r="E11">
-        <v>7750</v>
+        <v>5300</v>
       </c>
       <c r="F11">
-        <v>1082</v>
+        <v>4562</v>
       </c>
       <c r="G11" s="5">
-        <v>6668</v>
+        <v>738</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
       </c>
       <c r="E12">
-        <v>8000</v>
+        <v>7750</v>
       </c>
       <c r="F12">
-        <v>3579</v>
+        <v>1082</v>
       </c>
       <c r="G12" s="5">
-        <v>4421</v>
+        <v>6668</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D13" t="s">
         <v>35</v>
@@ -51675,21 +51678,21 @@
         <v>8000</v>
       </c>
       <c r="F13">
-        <v>2575</v>
+        <v>3579</v>
       </c>
       <c r="G13" s="5">
-        <v>5425</v>
+        <v>4421</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C14">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D14" t="s">
         <v>35</v>
@@ -51698,113 +51701,113 @@
         <v>8000</v>
       </c>
       <c r="F14">
-        <v>4607</v>
+        <v>2575</v>
       </c>
       <c r="G14" s="5">
-        <v>3393</v>
+        <v>5425</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C15">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D15" t="s">
         <v>35</v>
       </c>
       <c r="E15">
-        <v>7700</v>
+        <v>8000</v>
       </c>
       <c r="F15">
-        <v>3800</v>
+        <v>4607</v>
       </c>
       <c r="G15" s="5">
-        <v>3900</v>
+        <v>3393</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C16">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="D16" t="s">
         <v>35</v>
       </c>
       <c r="E16">
-        <v>8000</v>
+        <v>7700</v>
       </c>
       <c r="F16">
-        <v>1605</v>
+        <v>3800</v>
       </c>
       <c r="G16" s="5">
-        <v>6395</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C17">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D17" t="s">
         <v>35</v>
       </c>
       <c r="E17">
-        <v>9600</v>
+        <v>8000</v>
       </c>
       <c r="F17">
-        <v>1003</v>
+        <v>1605</v>
       </c>
       <c r="G17" s="5">
-        <v>8597</v>
+        <v>6395</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C18">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E18">
         <v>9600</v>
       </c>
       <c r="F18">
-        <v>4071</v>
+        <v>1003</v>
       </c>
       <c r="G18" s="5">
-        <v>5529</v>
+        <v>8597</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C19">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D19" t="s">
         <v>34</v>
@@ -51813,216 +51816,239 @@
         <v>9600</v>
       </c>
       <c r="F19">
-        <v>1915</v>
+        <v>4071</v>
       </c>
       <c r="G19" s="5">
-        <v>7685</v>
+        <v>5529</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E20">
-        <v>7800</v>
+        <v>9600</v>
       </c>
       <c r="F20">
-        <v>652</v>
+        <v>1915</v>
       </c>
       <c r="G20" s="5">
-        <v>7148</v>
+        <v>7685</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C21">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D21" t="s">
         <v>35</v>
       </c>
       <c r="E21">
-        <v>8000</v>
+        <v>7800</v>
       </c>
       <c r="F21">
-        <v>1482</v>
+        <v>652</v>
       </c>
       <c r="G21" s="5">
-        <v>6518</v>
+        <v>7148</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C22">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22">
-        <v>6750</v>
+        <v>8000</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1482</v>
       </c>
       <c r="G22" s="5">
-        <v>6748</v>
+        <v>6518</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E23">
-        <v>7700</v>
+        <v>6750</v>
       </c>
       <c r="F23">
-        <v>2550</v>
+        <v>2</v>
       </c>
       <c r="G23" s="5">
-        <v>5150</v>
+        <v>6748</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C24">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E24">
-        <v>6700</v>
+        <v>7700</v>
       </c>
       <c r="F24">
-        <v>4681</v>
+        <v>2550</v>
       </c>
       <c r="G24" s="5">
-        <v>2019</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C25">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D25" t="s">
         <v>34</v>
       </c>
       <c r="E25">
-        <v>13350</v>
+        <v>6700</v>
       </c>
       <c r="F25">
-        <v>4846</v>
+        <v>4681</v>
       </c>
       <c r="G25" s="5">
-        <v>8504</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C26">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E26">
-        <v>6000</v>
+        <v>13350</v>
       </c>
       <c r="F26">
-        <v>573</v>
+        <v>4846</v>
       </c>
       <c r="G26" s="5">
-        <v>5427</v>
+        <v>8504</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="C27">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="D27" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E27">
-        <v>9600</v>
+        <v>6000</v>
       </c>
       <c r="F27">
-        <v>4127</v>
+        <v>573</v>
       </c>
       <c r="G27" s="5">
-        <v>5473</v>
+        <v>5427</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28">
+        <v>135</v>
+      </c>
+      <c r="D28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28">
+        <v>9600</v>
+      </c>
+      <c r="F28">
+        <v>4127</v>
+      </c>
+      <c r="G28" s="5">
+        <v>5473</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B28" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28">
+      <c r="B29" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29">
         <v>127</v>
       </c>
-      <c r="D28" t="s">
-        <v>34</v>
-      </c>
-      <c r="E28">
+      <c r="D29" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29">
         <v>6650</v>
       </c>
-      <c r="F28">
+      <c r="F29">
         <v>4788</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G29" s="5">
         <v>1862</v>
       </c>
     </row>
@@ -52033,7 +52059,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" style="6" customWidth="1"/>
@@ -52055,7 +52081,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B2" s="6">
         <v>115</v>
@@ -52069,7 +52095,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B3" s="6">
         <v>121</v>
@@ -52083,7 +52109,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B4" s="6">
         <v>122</v>
@@ -52097,24 +52123,24 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B5" s="6">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C5" s="6">
-        <v>1304.485146482305</v>
+        <v>9600</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B6" s="6">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C6" s="6">
         <v>9600</v>
@@ -52125,43 +52151,29 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B7" s="6">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C7" s="6">
-        <v>9600</v>
+        <v>8000</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B8" s="6">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C8" s="6">
-        <v>8000</v>
+        <v>7750</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="6">
-        <v>152</v>
-      </c>
-      <c r="C9" s="6">
-        <v>7750</v>
-      </c>
-      <c r="D9" s="6" t="s">
         <v>35</v>
       </c>
     </row>

--- a/Waterjet Efficiency Shiftwise.xlsx
+++ b/Waterjet Efficiency Shiftwise.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8406" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8412" uniqueCount="79">
   <si>
     <t>DATE</t>
   </si>
@@ -201,7 +201,7 @@
     <t>16/01/2026</t>
   </si>
   <si>
-    <t>14/01/2026</t>
+    <t>14/02/2026</t>
   </si>
   <si>
     <t>08/02/2026</t>
@@ -246,10 +246,13 @@
     <t>02/02/2026</t>
   </si>
   <si>
-    <t>22/01/2026</t>
+    <t>13/02/2026</t>
   </si>
   <si>
     <t>29/01/2026</t>
+  </si>
+  <si>
+    <t>22/01/2026</t>
   </si>
   <si>
     <t>04/02/2026</t>
@@ -54869,19 +54872,19 @@
         <v>60</v>
       </c>
       <c r="C7">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E7">
-        <v>4200</v>
+        <v>6750</v>
       </c>
       <c r="F7">
-        <v>3895</v>
+        <v>0</v>
       </c>
       <c r="G7" s="5">
-        <v>305</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -55283,19 +55286,19 @@
         <v>75</v>
       </c>
       <c r="C25">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="D25" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E25">
-        <v>6700</v>
+        <v>8000</v>
       </c>
       <c r="F25">
-        <v>4681</v>
+        <v>0</v>
       </c>
       <c r="G25" s="5">
-        <v>2019</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -55372,7 +55375,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C29">
         <v>127</v>
@@ -55397,7 +55400,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" style="6" customWidth="1"/>
@@ -55433,7 +55436,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B3" s="6">
         <v>144</v>
@@ -55471,6 +55474,48 @@
       </c>
       <c r="D5" s="6" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="6">
+        <v>155</v>
+      </c>
+      <c r="C6" s="6">
+        <v>6800</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="6">
+        <v>158</v>
+      </c>
+      <c r="C7" s="6">
+        <v>4000</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="6">
+        <v>159</v>
+      </c>
+      <c r="C8" s="6">
+        <v>3800</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Waterjet Efficiency Shiftwise.xlsx
+++ b/Waterjet Efficiency Shiftwise.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8412" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8410" uniqueCount="78">
   <si>
     <t>DATE</t>
   </si>
@@ -250,9 +250,6 @@
   </si>
   <si>
     <t>29/01/2026</t>
-  </si>
-  <si>
-    <t>22/01/2026</t>
   </si>
   <si>
     <t>04/02/2026</t>
@@ -54719,7 +54716,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="15.7109375" customWidth="1"/>
@@ -55368,29 +55365,6 @@
       </c>
       <c r="G28" s="5">
         <v>5187</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29">
-        <v>127</v>
-      </c>
-      <c r="D29" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29">
-        <v>6650</v>
-      </c>
-      <c r="F29">
-        <v>5059</v>
-      </c>
-      <c r="G29" s="5">
-        <v>1591</v>
       </c>
     </row>
   </sheetData>
@@ -55436,7 +55410,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B3" s="6">
         <v>144</v>

--- a/Waterjet Efficiency Shiftwise.xlsx
+++ b/Waterjet Efficiency Shiftwise.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8410" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8412" uniqueCount="79">
   <si>
     <t>DATE</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>29/01/2026</t>
+  </si>
+  <si>
+    <t>22/01/2026</t>
   </si>
   <si>
     <t>04/02/2026</t>
@@ -54716,7 +54719,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="15.7109375" customWidth="1"/>
@@ -55365,6 +55368,29 @@
       </c>
       <c r="G28" s="5">
         <v>5187</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29">
+        <v>127</v>
+      </c>
+      <c r="D29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29">
+        <v>6650</v>
+      </c>
+      <c r="F29">
+        <v>5059</v>
+      </c>
+      <c r="G29" s="5">
+        <v>1591</v>
       </c>
     </row>
   </sheetData>
@@ -55410,7 +55436,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B3" s="6">
         <v>144</v>

--- a/Waterjet Efficiency Shiftwise.xlsx
+++ b/Waterjet Efficiency Shiftwise.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8412" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8422" uniqueCount="79">
   <si>
     <t>DATE</t>
   </si>
@@ -55400,7 +55400,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" style="6" customWidth="1"/>
@@ -55422,27 +55422,27 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="B2" s="6">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="C2" s="6">
-        <v>9600</v>
+        <v>501.5591931023519</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B3" s="6">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="C3" s="6">
-        <v>9600</v>
+        <v>439.530612762238</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>35</v>
@@ -55450,30 +55450,30 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B4" s="6">
-        <v>151</v>
+        <v>122</v>
       </c>
       <c r="C4" s="6">
-        <v>8000</v>
+        <v>424.2204365634361</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B5" s="6">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="C5" s="6">
-        <v>7750</v>
+        <v>304.6544423211399</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -55481,40 +55481,110 @@
         <v>73</v>
       </c>
       <c r="B6" s="6">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="C6" s="6">
-        <v>6800</v>
+        <v>2019.249991491841</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B7" s="6">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="C7" s="6">
-        <v>4000</v>
+        <v>9600</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="6">
+        <v>144</v>
+      </c>
+      <c r="C8" s="6">
+        <v>9600</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="6">
+        <v>151</v>
+      </c>
+      <c r="C9" s="6">
+        <v>8000</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="6">
+        <v>152</v>
+      </c>
+      <c r="C10" s="6">
+        <v>7750</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="6">
+        <v>155</v>
+      </c>
+      <c r="C11" s="6">
+        <v>6800</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="6">
+        <v>158</v>
+      </c>
+      <c r="C12" s="6">
+        <v>4000</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B13" s="6">
         <v>159</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C13" s="6">
         <v>3800</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D13" s="6" t="s">
         <v>38</v>
       </c>
     </row>

--- a/Waterjet Efficiency Shiftwise.xlsx
+++ b/Waterjet Efficiency Shiftwise.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8422" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8418" uniqueCount="79">
   <si>
     <t>DATE</t>
   </si>
@@ -55400,7 +55400,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" style="6" customWidth="1"/>
@@ -55450,13 +55450,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B4" s="6">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C4" s="6">
-        <v>424.2204365634361</v>
+        <v>2019.249991491841</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>35</v>
@@ -55464,13 +55464,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B5" s="6">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="C5" s="6">
-        <v>304.6544423211399</v>
+        <v>9600</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>35</v>
@@ -55478,13 +55478,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B6" s="6">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="C6" s="6">
-        <v>2019.249991491841</v>
+        <v>9600</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>35</v>
@@ -55492,99 +55492,71 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B7" s="6">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="C7" s="6">
-        <v>9600</v>
+        <v>8000</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B8" s="6">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C8" s="6">
-        <v>9600</v>
+        <v>7750</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B9" s="6">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C9" s="6">
-        <v>8000</v>
+        <v>6800</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B10" s="6">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C10" s="6">
-        <v>7750</v>
+        <v>4000</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="6" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B11" s="6">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C11" s="6">
-        <v>6800</v>
+        <v>3800</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" s="6">
-        <v>158</v>
-      </c>
-      <c r="C12" s="6">
-        <v>4000</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="6">
-        <v>159</v>
-      </c>
-      <c r="C13" s="6">
-        <v>3800</v>
-      </c>
-      <c r="D13" s="6" t="s">
         <v>38</v>
       </c>
     </row>

--- a/Waterjet Efficiency Shiftwise.xlsx
+++ b/Waterjet Efficiency Shiftwise.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8853" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8855" uniqueCount="80">
   <si>
     <t>DATE</t>
   </si>
@@ -718,22 +718,22 @@
         <v>6</v>
       </c>
       <c r="D2" s="1">
-        <v>1259</v>
+        <v>1244</v>
       </c>
       <c r="E2" s="2">
-        <v>0.84939271728015</v>
+        <v>0.8533013385569703</v>
       </c>
       <c r="F2" s="2">
-        <v>0.8748758910158874</v>
+        <v>0.8744496686743556</v>
       </c>
       <c r="G2" s="3">
-        <v>-2.548317373573739</v>
+        <v>-2.114833011738526</v>
       </c>
       <c r="H2">
         <v>6</v>
       </c>
       <c r="I2" s="1">
-        <v>716</v>
+        <v>656</v>
       </c>
       <c r="J2" s="2">
         <v>0.8106730957701204</v>
@@ -748,7 +748,7 @@
         <v>4</v>
       </c>
       <c r="N2" s="1">
-        <v>543</v>
+        <v>588</v>
       </c>
       <c r="O2" s="2">
         <v>0.9065115482481895</v>
@@ -771,22 +771,22 @@
         <v>3</v>
       </c>
       <c r="D3" s="1">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E3" s="2">
-        <v>0.9334555688214223</v>
+        <v>0.9316641260162603</v>
       </c>
       <c r="F3" s="2">
-        <v>0.8748758910158874</v>
+        <v>0.8744496686743556</v>
       </c>
       <c r="G3" s="3">
-        <v>5.857967780553497</v>
+        <v>5.721445734190467</v>
       </c>
       <c r="H3">
         <v>3</v>
       </c>
       <c r="I3" s="1">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="J3" s="2">
         <v>0.9549528824833702</v>
@@ -801,16 +801,16 @@
         <v>3</v>
       </c>
       <c r="N3" s="1">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="O3" s="2">
-        <v>0.9119582551594745</v>
+        <v>0.9119582551594746</v>
       </c>
       <c r="P3" s="2">
         <v>0.8697857416341145</v>
       </c>
       <c r="Q3" s="3">
-        <v>4.217251352536</v>
+        <v>4.217251352536011</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -824,46 +824,46 @@
         <v>4</v>
       </c>
       <c r="D4" s="1">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="E4" s="2">
-        <v>0.5616304095145965</v>
+        <v>0.5584273277439331</v>
       </c>
       <c r="F4" s="2">
-        <v>0.8748758910158874</v>
+        <v>0.8744496686743556</v>
       </c>
       <c r="G4" s="3">
-        <v>-31.32454815012908</v>
+        <v>-31.60223409304225</v>
       </c>
       <c r="H4">
         <v>2</v>
       </c>
       <c r="I4" s="1">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="J4" s="2">
-        <v>0.6186088351324402</v>
+        <v>0.6186088351324404</v>
       </c>
       <c r="K4" s="2">
         <v>0.8800198420557523</v>
       </c>
       <c r="L4" s="3">
-        <v>-26.14110069233121</v>
+        <v>-26.1411006923312</v>
       </c>
       <c r="M4">
         <v>4</v>
       </c>
       <c r="N4" s="1">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="O4" s="2">
-        <v>0.5314919914238869</v>
+        <v>0.531491991423887</v>
       </c>
       <c r="P4" s="2">
         <v>0.8697857416341145</v>
       </c>
       <c r="Q4" s="3">
-        <v>-33.82937502102276</v>
+        <v>-33.82937502102274</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -877,37 +877,37 @@
         <v>17</v>
       </c>
       <c r="D5" s="1">
-        <v>4374</v>
+        <v>4377</v>
       </c>
       <c r="E5" s="2">
-        <v>0.9473372393825916</v>
+        <v>0.948070827959247</v>
       </c>
       <c r="F5" s="2">
-        <v>0.8748758910158874</v>
+        <v>0.8744496686743556</v>
       </c>
       <c r="G5" s="3">
-        <v>7.246134836670426</v>
+        <v>7.362115928489144</v>
       </c>
       <c r="H5">
         <v>17</v>
       </c>
       <c r="I5" s="1">
-        <v>2167</v>
+        <v>1986</v>
       </c>
       <c r="J5" s="2">
-        <v>0.9385341764627285</v>
+        <v>0.9385341764627286</v>
       </c>
       <c r="K5" s="2">
         <v>0.8800198420557523</v>
       </c>
       <c r="L5" s="3">
-        <v>5.851433440697617</v>
+        <v>5.851433440697629</v>
       </c>
       <c r="M5">
         <v>17</v>
       </c>
       <c r="N5" s="1">
-        <v>2207</v>
+        <v>2391</v>
       </c>
       <c r="O5" s="2">
         <v>0.9561403023024546</v>
@@ -930,46 +930,46 @@
         <v>7</v>
       </c>
       <c r="D6" s="1">
-        <v>1626</v>
+        <v>1621</v>
       </c>
       <c r="E6" s="2">
-        <v>0.8597175401801566</v>
+        <v>0.8615203595178088</v>
       </c>
       <c r="F6" s="2">
-        <v>0.8379308364375717</v>
+        <v>0.8378258964871993</v>
       </c>
       <c r="G6" s="3">
-        <v>2.178670374258485</v>
+        <v>2.369446303060951</v>
       </c>
       <c r="H6">
         <v>7</v>
       </c>
       <c r="I6" s="1">
-        <v>847</v>
+        <v>776</v>
       </c>
       <c r="J6" s="2">
         <v>0.8395411981161869</v>
       </c>
       <c r="K6" s="2">
-        <v>0.8391880909312647</v>
+        <v>0.8391880909312648</v>
       </c>
       <c r="L6" s="3">
-        <v>0.03531071849222078</v>
+        <v>0.03531071849220968</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6" s="1">
-        <v>780</v>
+        <v>845</v>
       </c>
       <c r="O6" s="2">
-        <v>0.8827598102630445</v>
+        <v>0.8827598102630443</v>
       </c>
       <c r="P6" s="2">
         <v>0.8366698385455618</v>
       </c>
       <c r="Q6" s="3">
-        <v>4.608997171748275</v>
+        <v>4.608997171748253</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -983,28 +983,28 @@
         <v>18</v>
       </c>
       <c r="D7" s="1">
-        <v>4349</v>
+        <v>4356</v>
       </c>
       <c r="E7" s="2">
-        <v>0.9194427520485838</v>
+        <v>0.9190045408616682</v>
       </c>
       <c r="F7" s="2">
-        <v>0.8379308364375717</v>
+        <v>0.8378258964871993</v>
       </c>
       <c r="G7" s="3">
-        <v>8.151191561101212</v>
+        <v>8.117864437446887</v>
       </c>
       <c r="H7">
         <v>17</v>
       </c>
       <c r="I7" s="1">
-        <v>2135</v>
+        <v>1957</v>
       </c>
       <c r="J7" s="2">
-        <v>0.9248412315360933</v>
+        <v>0.9248412315360934</v>
       </c>
       <c r="K7" s="2">
-        <v>0.8391880909312647</v>
+        <v>0.8391880909312648</v>
       </c>
       <c r="L7" s="3">
         <v>8.565314060482866</v>
@@ -1013,7 +1013,7 @@
         <v>18</v>
       </c>
       <c r="N7" s="1">
-        <v>2214</v>
+        <v>2399</v>
       </c>
       <c r="O7" s="2">
         <v>0.9142970875366448</v>
@@ -1036,28 +1036,28 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E8" s="2">
-        <v>0.6097984243064334</v>
+        <v>0.6043295325986093</v>
       </c>
       <c r="F8" s="2">
-        <v>0.8379308364375717</v>
+        <v>0.8378258964871993</v>
       </c>
       <c r="G8" s="3">
-        <v>-22.81324121311383</v>
+        <v>-23.349636388859</v>
       </c>
       <c r="H8">
         <v>2</v>
       </c>
       <c r="I8" s="1">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="J8" s="2">
-        <v>0.6755228730939088</v>
+        <v>0.6755228730939089</v>
       </c>
       <c r="K8" s="2">
-        <v>0.8391880909312647</v>
+        <v>0.8391880909312648</v>
       </c>
       <c r="L8" s="3">
         <v>-16.36652178373559</v>
@@ -1066,7 +1066,7 @@
         <v>2</v>
       </c>
       <c r="N8" s="1">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="O8" s="2">
         <v>0.5442542070969859</v>
@@ -1089,37 +1089,37 @@
         <v>2</v>
       </c>
       <c r="D9" s="1">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E9" s="2">
-        <v>0.3733987698043492</v>
+        <v>0.3726340208233985</v>
       </c>
       <c r="F9" s="2">
-        <v>0.8379308364375717</v>
+        <v>0.8378258964871993</v>
       </c>
       <c r="G9" s="3">
-        <v>-46.45320666332226</v>
+        <v>-46.51918756638008</v>
       </c>
       <c r="H9">
         <v>2</v>
       </c>
       <c r="I9" s="1">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J9" s="2">
         <v>0.3825757575757576</v>
       </c>
       <c r="K9" s="2">
-        <v>0.8391880909312647</v>
+        <v>0.8391880909312648</v>
       </c>
       <c r="L9" s="3">
-        <v>-45.6612333355507</v>
+        <v>-45.66123333555072</v>
       </c>
       <c r="M9">
         <v>2</v>
       </c>
       <c r="N9" s="1">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="O9" s="2">
         <v>0.3642217820329408</v>
@@ -1142,43 +1142,43 @@
         <v>8</v>
       </c>
       <c r="D10" s="1">
-        <v>2040</v>
+        <v>2028</v>
       </c>
       <c r="E10" s="2">
-        <v>0.8730495920403999</v>
+        <v>0.867717908598996</v>
       </c>
       <c r="F10" s="2">
-        <v>0.8892476183952933</v>
+        <v>0.8877963428508072</v>
       </c>
       <c r="G10" s="3">
-        <v>-1.619802635489342</v>
+        <v>-2.007843425181122</v>
       </c>
       <c r="H10">
         <v>8</v>
       </c>
       <c r="I10" s="1">
-        <v>1095</v>
+        <v>1004</v>
       </c>
       <c r="J10" s="2">
         <v>0.937029793337245</v>
       </c>
       <c r="K10" s="2">
-        <v>0.9067056666109792</v>
+        <v>0.9067056666109793</v>
       </c>
       <c r="L10" s="3">
-        <v>3.032412672626583</v>
+        <v>3.032412672626572</v>
       </c>
       <c r="M10">
         <v>8</v>
       </c>
       <c r="N10" s="1">
-        <v>945</v>
+        <v>1024</v>
       </c>
       <c r="O10" s="2">
-        <v>0.8090693907435547</v>
+        <v>0.8090693907435546</v>
       </c>
       <c r="P10" s="2">
-        <v>0.8718683147728952</v>
+        <v>0.8718683147728951</v>
       </c>
       <c r="Q10" s="3">
         <v>-6.279892402934051</v>
@@ -1195,46 +1195,46 @@
         <v>18</v>
       </c>
       <c r="D11" s="1">
-        <v>4380</v>
+        <v>4382</v>
       </c>
       <c r="E11" s="2">
-        <v>0.9259057303431975</v>
+        <v>0.9245344703748343</v>
       </c>
       <c r="F11" s="2">
-        <v>0.8892476183952933</v>
+        <v>0.8877963428508072</v>
       </c>
       <c r="G11" s="3">
-        <v>3.665811194790414</v>
+        <v>3.673812752402705</v>
       </c>
       <c r="H11">
         <v>17</v>
       </c>
       <c r="I11" s="1">
-        <v>2176</v>
+        <v>1995</v>
       </c>
       <c r="J11" s="2">
-        <v>0.9427987696637025</v>
+        <v>0.9427987696637027</v>
       </c>
       <c r="K11" s="2">
-        <v>0.9067056666109792</v>
+        <v>0.9067056666109793</v>
       </c>
       <c r="L11" s="3">
-        <v>3.609310305272329</v>
+        <v>3.60931030527234</v>
       </c>
       <c r="M11">
         <v>18</v>
       </c>
       <c r="N11" s="1">
-        <v>2203</v>
+        <v>2387</v>
       </c>
       <c r="O11" s="2">
         <v>0.9098038051378817</v>
       </c>
       <c r="P11" s="2">
-        <v>0.8718683147728952</v>
+        <v>0.8718683147728951</v>
       </c>
       <c r="Q11" s="3">
-        <v>3.793549036498656</v>
+        <v>3.793549036498667</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1251,43 +1251,43 @@
         <v>145</v>
       </c>
       <c r="E12" s="2">
-        <v>0.505867756937439</v>
+        <v>0.5192243878584651</v>
       </c>
       <c r="F12" s="2">
-        <v>0.8892476183952933</v>
+        <v>0.8877963428508072</v>
       </c>
       <c r="G12" s="3">
-        <v>-38.33798614578543</v>
+        <v>-36.85719549923421</v>
       </c>
       <c r="H12">
         <v>2</v>
       </c>
       <c r="I12" s="1">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="J12" s="2">
-        <v>0.3890370246923868</v>
+        <v>0.3890370246923867</v>
       </c>
       <c r="K12" s="2">
-        <v>0.9067056666109792</v>
+        <v>0.9067056666109793</v>
       </c>
       <c r="L12" s="3">
-        <v>-51.76686419185924</v>
+        <v>-51.76686419185926</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
       <c r="N12" s="1">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O12" s="2">
-        <v>0.7397435897435897</v>
+        <v>0.7397435897435898</v>
       </c>
       <c r="P12" s="2">
-        <v>0.8718683147728952</v>
+        <v>0.8718683147728951</v>
       </c>
       <c r="Q12" s="3">
-        <v>-13.21247250293055</v>
+        <v>-13.21247250293053</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1301,46 +1301,46 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E13" s="2">
-        <v>0.8199112284949194</v>
+        <v>0.8215704975361628</v>
       </c>
       <c r="F13" s="2">
-        <v>0.8892476183952933</v>
+        <v>0.8877963428508072</v>
       </c>
       <c r="G13" s="3">
-        <v>-6.933638990037394</v>
+        <v>-6.622584531464437</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="I13" s="1">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J13" s="2">
-        <v>0.8</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="K13" s="2">
-        <v>0.9067056666109792</v>
+        <v>0.9067056666109793</v>
       </c>
       <c r="L13" s="3">
-        <v>-10.67056666109791</v>
+        <v>-10.67056666109794</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13" s="1">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2">
         <v>0.839822456989839</v>
       </c>
       <c r="P13" s="2">
-        <v>0.8718683147728952</v>
+        <v>0.8718683147728951</v>
       </c>
       <c r="Q13" s="3">
-        <v>-3.204585778305613</v>
+        <v>-3.204585778305602</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1354,28 +1354,28 @@
         <v>9</v>
       </c>
       <c r="D14" s="1">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="E14" s="2">
-        <v>0.8308405718627611</v>
+        <v>0.8334285107518109</v>
       </c>
       <c r="F14" s="2">
-        <v>0.8832310106190311</v>
+        <v>0.8820441438344169</v>
       </c>
       <c r="G14" s="3">
-        <v>-5.239043875627003</v>
+        <v>-4.861563308260597</v>
       </c>
       <c r="H14">
         <v>9</v>
       </c>
       <c r="I14" s="1">
-        <v>1036</v>
+        <v>950</v>
       </c>
       <c r="J14" s="2">
-        <v>0.8014056257163361</v>
+        <v>0.8014056257163362</v>
       </c>
       <c r="K14" s="2">
-        <v>0.8974165249242002</v>
+        <v>0.8974165249242003</v>
       </c>
       <c r="L14" s="3">
         <v>-9.601089920786411</v>
@@ -1384,16 +1384,16 @@
         <v>8</v>
       </c>
       <c r="N14" s="1">
-        <v>1009</v>
+        <v>1093</v>
       </c>
       <c r="O14" s="2">
-        <v>0.8634130196031233</v>
+        <v>0.8634130196031231</v>
       </c>
       <c r="P14" s="2">
-        <v>0.8689401163742244</v>
+        <v>0.8689401163742245</v>
       </c>
       <c r="Q14" s="3">
-        <v>-0.5527096771101081</v>
+        <v>-0.5527096771101414</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1407,43 +1407,43 @@
         <v>18</v>
       </c>
       <c r="D15" s="1">
-        <v>4513</v>
+        <v>4502</v>
       </c>
       <c r="E15" s="2">
-        <v>0.9317578224731498</v>
+        <v>0.9294131381574559</v>
       </c>
       <c r="F15" s="2">
-        <v>0.8832310106190311</v>
+        <v>0.8820441438344169</v>
       </c>
       <c r="G15" s="3">
-        <v>4.852681185411867</v>
+        <v>4.736899432303899</v>
       </c>
       <c r="H15">
         <v>18</v>
       </c>
       <c r="I15" s="1">
-        <v>2325</v>
+        <v>2131</v>
       </c>
       <c r="J15" s="2">
         <v>0.9598940342614757</v>
       </c>
       <c r="K15" s="2">
-        <v>0.8974165249242002</v>
+        <v>0.8974165249242003</v>
       </c>
       <c r="L15" s="3">
-        <v>6.247750933727547</v>
+        <v>6.247750933727536</v>
       </c>
       <c r="M15">
         <v>18</v>
       </c>
       <c r="N15" s="1">
-        <v>2188</v>
+        <v>2371</v>
       </c>
       <c r="O15" s="2">
-        <v>0.9036216106848236</v>
+        <v>0.9036216106848237</v>
       </c>
       <c r="P15" s="2">
-        <v>0.8689401163742244</v>
+        <v>0.8689401163742245</v>
       </c>
       <c r="Q15" s="3">
         <v>3.468149431059919</v>
@@ -1460,16 +1460,16 @@
         <v>1</v>
       </c>
       <c r="D16" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E16" s="2">
-        <v>0.2833333333333333</v>
+        <v>0.2833333333333334</v>
       </c>
       <c r="F16" s="2">
-        <v>0.8832310106190311</v>
+        <v>0.8820441438344169</v>
       </c>
       <c r="G16" s="3">
-        <v>-59.98976772856979</v>
+        <v>-59.87108105010834</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -1490,13 +1490,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O16" s="2">
-        <v>0.2833333333333333</v>
+        <v>0.2833333333333334</v>
       </c>
       <c r="P16" s="2">
-        <v>0.8689401163742244</v>
+        <v>0.8689401163742245</v>
       </c>
       <c r="Q16" s="3">
         <v>-58.56067830408911</v>
@@ -1516,43 +1516,43 @@
         <v>274</v>
       </c>
       <c r="E17" s="2">
-        <v>0.7499861607157744</v>
+        <v>0.7501112700683514</v>
       </c>
       <c r="F17" s="2">
-        <v>0.8832310106190311</v>
+        <v>0.8820441438344169</v>
       </c>
       <c r="G17" s="3">
-        <v>-13.32448499032567</v>
+        <v>-13.19328737660654</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="I17" s="1">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="J17" s="2">
-        <v>0.7484848484848485</v>
+        <v>0.7484848484848484</v>
       </c>
       <c r="K17" s="2">
-        <v>0.8974165249242002</v>
+        <v>0.8974165249242003</v>
       </c>
       <c r="L17" s="3">
-        <v>-14.89316764393517</v>
+        <v>-14.89316764393519</v>
       </c>
       <c r="M17">
         <v>1</v>
       </c>
       <c r="N17" s="1">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="O17" s="2">
         <v>0.7514874729467003</v>
       </c>
       <c r="P17" s="2">
-        <v>0.8689401163742244</v>
+        <v>0.8689401163742245</v>
       </c>
       <c r="Q17" s="3">
-        <v>-11.74526434275242</v>
+        <v>-11.74526434275243</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1566,37 +1566,37 @@
         <v>10</v>
       </c>
       <c r="D18" s="1">
-        <v>2263</v>
+        <v>2244</v>
       </c>
       <c r="E18" s="2">
-        <v>0.8242827196385248</v>
+        <v>0.8211863127057473</v>
       </c>
       <c r="F18" s="2">
-        <v>0.8854281330823822</v>
+        <v>0.8830321953349407</v>
       </c>
       <c r="G18" s="3">
-        <v>-6.114541344385738</v>
+        <v>-6.184588262919344</v>
       </c>
       <c r="H18">
         <v>10</v>
       </c>
       <c r="I18" s="1">
-        <v>1248</v>
+        <v>1144</v>
       </c>
       <c r="J18" s="2">
-        <v>0.8592265267111892</v>
+        <v>0.8592265267111894</v>
       </c>
       <c r="K18" s="2">
         <v>0.9142711014561837</v>
       </c>
       <c r="L18" s="3">
-        <v>-5.504457474499458</v>
+        <v>-5.504457474499436</v>
       </c>
       <c r="M18">
         <v>9</v>
       </c>
       <c r="N18" s="1">
-        <v>1015</v>
+        <v>1099</v>
       </c>
       <c r="O18" s="2">
         <v>0.7850218886804252</v>
@@ -1622,19 +1622,19 @@
         <v>4584</v>
       </c>
       <c r="E19" s="2">
-        <v>0.9464569374360094</v>
+        <v>0.9463879239690844</v>
       </c>
       <c r="F19" s="2">
-        <v>0.8854281330823822</v>
+        <v>0.8830321953349407</v>
       </c>
       <c r="G19" s="3">
-        <v>6.102880435362723</v>
+        <v>6.335572863414374</v>
       </c>
       <c r="H19">
         <v>18</v>
       </c>
       <c r="I19" s="1">
-        <v>2294</v>
+        <v>2103</v>
       </c>
       <c r="J19" s="2">
         <v>0.9472850990391087</v>
@@ -1649,16 +1649,16 @@
         <v>18</v>
       </c>
       <c r="N19" s="1">
-        <v>2290</v>
+        <v>2481</v>
       </c>
       <c r="O19" s="2">
-        <v>0.9456287758329098</v>
+        <v>0.9456287758329101</v>
       </c>
       <c r="P19" s="2">
         <v>0.8567540311007951</v>
       </c>
       <c r="Q19" s="3">
-        <v>8.887474473211476</v>
+        <v>8.887474473211498</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1672,16 +1672,16 @@
         <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2">
         <v>0.1856314882065955</v>
       </c>
       <c r="F20" s="2">
-        <v>0.8854281330823822</v>
+        <v>0.8830321953349407</v>
       </c>
       <c r="G20" s="3">
-        <v>-69.97966448757866</v>
+        <v>-69.74007071283452</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1702,7 +1702,7 @@
         <v>1</v>
       </c>
       <c r="N20" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O20" s="2">
         <v>0.1856314882065955</v>
@@ -1725,37 +1725,37 @@
         <v>10</v>
       </c>
       <c r="D21" s="1">
-        <v>2575</v>
+        <v>2567</v>
       </c>
       <c r="E21" s="2">
-        <v>0.8864505493457829</v>
+        <v>0.8835069171342177</v>
       </c>
       <c r="F21" s="2">
-        <v>0.900596320229565</v>
+        <v>0.900363951394849</v>
       </c>
       <c r="G21" s="3">
-        <v>-1.414577088378211</v>
+        <v>-1.685703426063134</v>
       </c>
       <c r="H21">
         <v>10</v>
       </c>
       <c r="I21" s="1">
-        <v>1339</v>
+        <v>1227</v>
       </c>
       <c r="J21" s="2">
         <v>0.9217741358845654</v>
       </c>
       <c r="K21" s="2">
-        <v>0.9033915164078746</v>
+        <v>0.9033915164078745</v>
       </c>
       <c r="L21" s="3">
-        <v>1.838261947669073</v>
+        <v>1.838261947669084</v>
       </c>
       <c r="M21">
         <v>10</v>
       </c>
       <c r="N21" s="1">
-        <v>1236</v>
+        <v>1339</v>
       </c>
       <c r="O21" s="2">
         <v>0.8511269628070005</v>
@@ -1778,46 +1778,46 @@
         <v>18</v>
       </c>
       <c r="D22" s="1">
-        <v>4311</v>
+        <v>4325</v>
       </c>
       <c r="E22" s="2">
-        <v>0.911121537870012</v>
+        <v>0.9123725801641929</v>
       </c>
       <c r="F22" s="2">
-        <v>0.900596320229565</v>
+        <v>0.900363951394849</v>
       </c>
       <c r="G22" s="3">
-        <v>1.0525217640447</v>
+        <v>1.200862876934383</v>
       </c>
       <c r="H22">
         <v>17</v>
       </c>
       <c r="I22" s="1">
-        <v>2069</v>
+        <v>1896</v>
       </c>
       <c r="J22" s="2">
-        <v>0.8957133395476622</v>
+        <v>0.8957133395476624</v>
       </c>
       <c r="K22" s="2">
-        <v>0.9033915164078746</v>
+        <v>0.9033915164078745</v>
       </c>
       <c r="L22" s="3">
-        <v>-0.7678176860212438</v>
+        <v>-0.7678176860212105</v>
       </c>
       <c r="M22">
         <v>18</v>
       </c>
       <c r="N22" s="1">
-        <v>2242</v>
+        <v>2429</v>
       </c>
       <c r="O22" s="2">
-        <v>0.9258147661870106</v>
+        <v>0.9258147661870108</v>
       </c>
       <c r="P22" s="2">
         <v>0.8978135972482332</v>
       </c>
       <c r="Q22" s="3">
-        <v>2.800116893877747</v>
+        <v>2.800116893877758</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -1831,31 +1831,31 @@
         <v>1</v>
       </c>
       <c r="D23" s="1">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E23" s="2">
-        <v>0.8090685038929032</v>
+        <v>0.8090685038929034</v>
       </c>
       <c r="F23" s="2">
-        <v>0.900596320229565</v>
+        <v>0.900363951394849</v>
       </c>
       <c r="G23" s="3">
-        <v>-9.152781633666185</v>
+        <v>-9.129544750194562</v>
       </c>
       <c r="H23">
         <v>1</v>
       </c>
       <c r="I23" s="1">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="J23" s="2">
-        <v>0.8090685038929032</v>
+        <v>0.8090685038929034</v>
       </c>
       <c r="K23" s="2">
-        <v>0.9033915164078746</v>
+        <v>0.9033915164078745</v>
       </c>
       <c r="L23" s="3">
-        <v>-9.432301251497144</v>
+        <v>-9.43230125149711</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -1887,43 +1887,43 @@
         <v>2666</v>
       </c>
       <c r="E24" s="2">
-        <v>0.9178438558452716</v>
+        <v>0.9177074047856255</v>
       </c>
       <c r="F24" s="2">
-        <v>0.8976433816886573</v>
+        <v>0.897420995390633</v>
       </c>
       <c r="G24" s="3">
-        <v>2.02004741566143</v>
+        <v>2.028640939499249</v>
       </c>
       <c r="H24">
         <v>10</v>
       </c>
       <c r="I24" s="1">
-        <v>1336</v>
+        <v>1224</v>
       </c>
       <c r="J24" s="2">
         <v>0.9194812685610232</v>
       </c>
       <c r="K24" s="2">
-        <v>0.9003120172649495</v>
+        <v>0.9003120172649496</v>
       </c>
       <c r="L24" s="3">
-        <v>1.916925129607372</v>
+        <v>1.916925129607361</v>
       </c>
       <c r="M24">
         <v>10</v>
       </c>
       <c r="N24" s="1">
-        <v>1331</v>
+        <v>1442</v>
       </c>
       <c r="O24" s="2">
-        <v>0.9162064431295202</v>
+        <v>0.91620644312952</v>
       </c>
       <c r="P24" s="2">
-        <v>0.8949747461123653</v>
+        <v>0.8949747461123654</v>
       </c>
       <c r="Q24" s="3">
-        <v>2.123169701715488</v>
+        <v>2.123169701715466</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -1937,28 +1937,28 @@
         <v>17</v>
       </c>
       <c r="D25" s="1">
-        <v>4079</v>
+        <v>4078</v>
       </c>
       <c r="E25" s="2">
-        <v>0.8829938672288915</v>
+        <v>0.8827683711099118</v>
       </c>
       <c r="F25" s="2">
-        <v>0.8976433816886573</v>
+        <v>0.897420995390633</v>
       </c>
       <c r="G25" s="3">
-        <v>-1.464951445976581</v>
+        <v>-1.465262428072123</v>
       </c>
       <c r="H25">
         <v>17</v>
       </c>
       <c r="I25" s="1">
-        <v>2046</v>
+        <v>1875</v>
       </c>
       <c r="J25" s="2">
-        <v>0.8856998206566474</v>
+        <v>0.8856998206566475</v>
       </c>
       <c r="K25" s="2">
-        <v>0.9003120172649495</v>
+        <v>0.9003120172649496</v>
       </c>
       <c r="L25" s="3">
         <v>-1.461219660830204</v>
@@ -1967,16 +1967,16 @@
         <v>17</v>
       </c>
       <c r="N25" s="1">
-        <v>2033</v>
+        <v>2202</v>
       </c>
       <c r="O25" s="2">
         <v>0.8802879138011356</v>
       </c>
       <c r="P25" s="2">
-        <v>0.8949747461123653</v>
+        <v>0.8949747461123654</v>
       </c>
       <c r="Q25" s="3">
-        <v>-1.468683231122969</v>
+        <v>-1.46868323112298</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -1990,46 +1990,46 @@
         <v>1</v>
       </c>
       <c r="D26" s="1">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E26" s="2">
-        <v>0.9448668398760819</v>
+        <v>0.9434072704867532</v>
       </c>
       <c r="F26" s="2">
-        <v>0.8976433816886573</v>
+        <v>0.897420995390633</v>
       </c>
       <c r="G26" s="3">
-        <v>4.722345818742458</v>
+        <v>4.598627509612019</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26" s="1">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="J26" s="2">
-        <v>0.962381672548031</v>
+        <v>0.9623816725480314</v>
       </c>
       <c r="K26" s="2">
-        <v>0.9003120172649495</v>
+        <v>0.9003120172649496</v>
       </c>
       <c r="L26" s="3">
-        <v>6.20696552830815</v>
+        <v>6.206965528308183</v>
       </c>
       <c r="M26">
         <v>1</v>
       </c>
       <c r="N26" s="1">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="O26" s="2">
-        <v>0.9273520072041328</v>
+        <v>0.927352007204133</v>
       </c>
       <c r="P26" s="2">
-        <v>0.8949747461123653</v>
+        <v>0.8949747461123654</v>
       </c>
       <c r="Q26" s="3">
-        <v>3.237726109176753</v>
+        <v>3.237726109176764</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -2043,43 +2043,43 @@
         <v>10</v>
       </c>
       <c r="D27" s="1">
-        <v>2553</v>
+        <v>2559</v>
       </c>
       <c r="E27" s="2">
-        <v>0.8786414348589903</v>
+        <v>0.8808554218446855</v>
       </c>
       <c r="F27" s="2">
-        <v>0.9089816498597452</v>
+        <v>0.9107816193810581</v>
       </c>
       <c r="G27" s="3">
-        <v>-3.03402150007549</v>
+        <v>-2.99261975363726</v>
       </c>
       <c r="H27">
         <v>10</v>
       </c>
       <c r="I27" s="1">
-        <v>1238</v>
+        <v>1135</v>
       </c>
       <c r="J27" s="2">
-        <v>0.8520735910306462</v>
+        <v>0.8520735910306463</v>
       </c>
       <c r="K27" s="2">
         <v>0.8873820156039891</v>
       </c>
       <c r="L27" s="3">
-        <v>-3.530842457334293</v>
+        <v>-3.530842457334282</v>
       </c>
       <c r="M27">
         <v>10</v>
       </c>
       <c r="N27" s="1">
-        <v>1315</v>
+        <v>1424</v>
       </c>
       <c r="O27" s="2">
-        <v>0.9052092786873343</v>
+        <v>0.9052092786873344</v>
       </c>
       <c r="P27" s="2">
-        <v>0.9305812841155011</v>
+        <v>0.9305812841155012</v>
       </c>
       <c r="Q27" s="3">
         <v>-2.537200542816687</v>
@@ -2096,22 +2096,22 @@
         <v>17</v>
       </c>
       <c r="D28" s="1">
-        <v>4283</v>
+        <v>4290</v>
       </c>
       <c r="E28" s="2">
-        <v>0.927226114564215</v>
+        <v>0.9287760963202814</v>
       </c>
       <c r="F28" s="2">
-        <v>0.9089816498597452</v>
+        <v>0.9107816193810581</v>
       </c>
       <c r="G28" s="3">
-        <v>1.824446470446983</v>
+        <v>1.799447693922329</v>
       </c>
       <c r="H28">
         <v>17</v>
       </c>
       <c r="I28" s="1">
-        <v>2098</v>
+        <v>1924</v>
       </c>
       <c r="J28" s="2">
         <v>0.9086263334914172</v>
@@ -2126,16 +2126,16 @@
         <v>17</v>
       </c>
       <c r="N28" s="1">
-        <v>2184</v>
+        <v>2366</v>
       </c>
       <c r="O28" s="2">
         <v>0.9458258956370127</v>
       </c>
       <c r="P28" s="2">
-        <v>0.9305812841155011</v>
+        <v>0.9305812841155012</v>
       </c>
       <c r="Q28" s="3">
-        <v>1.524461152151158</v>
+        <v>1.524461152151146</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2152,43 +2152,43 @@
         <v>177</v>
       </c>
       <c r="E29" s="2">
-        <v>0.9293370215736204</v>
+        <v>0.9308841651263093</v>
       </c>
       <c r="F29" s="2">
-        <v>0.9089816498597452</v>
+        <v>0.9107816193810581</v>
       </c>
       <c r="G29" s="3">
-        <v>2.035537171387525</v>
+        <v>2.010254574525128</v>
       </c>
       <c r="H29">
         <v>1</v>
       </c>
       <c r="I29" s="1">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="J29" s="2">
-        <v>0.9107712989413542</v>
+        <v>0.9107712989413546</v>
       </c>
       <c r="K29" s="2">
         <v>0.8873820156039891</v>
       </c>
       <c r="L29" s="3">
-        <v>2.338928333736512</v>
+        <v>2.338928333736545</v>
       </c>
       <c r="M29">
         <v>1</v>
       </c>
       <c r="N29" s="1">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="O29" s="2">
         <v>0.9479027442058864</v>
       </c>
       <c r="P29" s="2">
-        <v>0.9305812841155011</v>
+        <v>0.9305812841155012</v>
       </c>
       <c r="Q29" s="3">
-        <v>1.732146009038527</v>
+        <v>1.732146009038515</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2202,46 +2202,46 @@
         <v>10</v>
       </c>
       <c r="D30" s="1">
-        <v>2624</v>
+        <v>2618</v>
       </c>
       <c r="E30" s="2">
-        <v>0.903181871350819</v>
+        <v>0.9012379179557094</v>
       </c>
       <c r="F30" s="2">
-        <v>0.8899624718866596</v>
+        <v>0.8892359879245889</v>
       </c>
       <c r="G30" s="3">
-        <v>1.32193994641594</v>
+        <v>1.200193003112049</v>
       </c>
       <c r="H30">
         <v>10</v>
       </c>
       <c r="I30" s="1">
-        <v>1346</v>
+        <v>1234</v>
       </c>
       <c r="J30" s="2">
-        <v>0.9265093120921341</v>
+        <v>0.9265093120921343</v>
       </c>
       <c r="K30" s="2">
-        <v>0.8987016100814504</v>
+        <v>0.8987016100814506</v>
       </c>
       <c r="L30" s="3">
-        <v>2.780770201068361</v>
+        <v>2.780770201068372</v>
       </c>
       <c r="M30">
         <v>10</v>
       </c>
       <c r="N30" s="1">
-        <v>1278</v>
+        <v>1385</v>
       </c>
       <c r="O30" s="2">
         <v>0.8798544306095037</v>
       </c>
       <c r="P30" s="2">
-        <v>0.8812626321898004</v>
+        <v>0.8812626321898005</v>
       </c>
       <c r="Q30" s="3">
-        <v>-0.1408201580296642</v>
+        <v>-0.1408201580296753</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2255,28 +2255,28 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E31" s="2">
-        <v>0.6968224669941409</v>
+        <v>0.6823299157526626</v>
       </c>
       <c r="F31" s="2">
-        <v>0.8899624718866596</v>
+        <v>0.8892359879245889</v>
       </c>
       <c r="G31" s="3">
-        <v>-19.31400048925187</v>
+        <v>-20.69060721719264</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31" s="1">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="J31" s="2">
-        <v>0.8707330818918803</v>
+        <v>0.8707330818918804</v>
       </c>
       <c r="K31" s="2">
-        <v>0.8987016100814504</v>
+        <v>0.8987016100814506</v>
       </c>
       <c r="L31" s="3">
         <v>-2.796852818957019</v>
@@ -2285,16 +2285,16 @@
         <v>1</v>
       </c>
       <c r="N31" s="1">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="O31" s="2">
-        <v>0.5229118520964015</v>
+        <v>0.5229118520964013</v>
       </c>
       <c r="P31" s="2">
-        <v>0.8812626321898004</v>
+        <v>0.8812626321898005</v>
       </c>
       <c r="Q31" s="3">
-        <v>-35.8350780093399</v>
+        <v>-35.83507800933992</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2308,46 +2308,46 @@
         <v>16</v>
       </c>
       <c r="D32" s="1">
-        <v>3809</v>
+        <v>3820</v>
       </c>
       <c r="E32" s="2">
-        <v>0.9037525403789572</v>
+        <v>0.9042387895378126</v>
       </c>
       <c r="F32" s="2">
-        <v>0.8899624718866596</v>
+        <v>0.8892359879245889</v>
       </c>
       <c r="G32" s="3">
-        <v>1.379006849229769</v>
+        <v>1.500280161322365</v>
       </c>
       <c r="H32">
         <v>15</v>
       </c>
       <c r="I32" s="1">
-        <v>1841</v>
+        <v>1687</v>
       </c>
       <c r="J32" s="2">
-        <v>0.8977420850179436</v>
+        <v>0.8977420850179435</v>
       </c>
       <c r="K32" s="2">
-        <v>0.8987016100814504</v>
+        <v>0.8987016100814506</v>
       </c>
       <c r="L32" s="3">
-        <v>-0.09595250635068275</v>
+        <v>-0.09595250635070496</v>
       </c>
       <c r="M32">
         <v>16</v>
       </c>
       <c r="N32" s="1">
-        <v>1968</v>
+        <v>2132</v>
       </c>
       <c r="O32" s="2">
         <v>0.9094468685168369</v>
       </c>
       <c r="P32" s="2">
-        <v>0.8812626321898004</v>
+        <v>0.8812626321898005</v>
       </c>
       <c r="Q32" s="3">
-        <v>2.818423632703648</v>
+        <v>2.818423632703637</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2361,43 +2361,43 @@
         <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E33" s="2">
-        <v>0.7991594806011983</v>
+        <v>0.8076977698295813</v>
       </c>
       <c r="F33" s="2">
-        <v>0.8899624718866596</v>
+        <v>0.8892359879245889</v>
       </c>
       <c r="G33" s="3">
-        <v>-9.080299128546121</v>
+        <v>-8.15382180950076</v>
       </c>
       <c r="H33">
         <v>2</v>
       </c>
       <c r="I33" s="1">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="J33" s="2">
         <v>0.7246278209088127</v>
       </c>
       <c r="K33" s="2">
-        <v>0.8987016100814504</v>
+        <v>0.8987016100814506</v>
       </c>
       <c r="L33" s="3">
-        <v>-17.40737891726377</v>
+        <v>-17.40737891726378</v>
       </c>
       <c r="M33">
         <v>1</v>
       </c>
       <c r="N33" s="1">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="O33" s="2">
-        <v>0.949187165268496</v>
+        <v>0.9491871652684961</v>
       </c>
       <c r="P33" s="2">
-        <v>0.8812626321898004</v>
+        <v>0.8812626321898005</v>
       </c>
       <c r="Q33" s="3">
         <v>6.792453307869561</v>
@@ -2414,37 +2414,37 @@
         <v>11</v>
       </c>
       <c r="D34" s="1">
-        <v>2846</v>
+        <v>2850</v>
       </c>
       <c r="E34" s="2">
-        <v>0.9026263386372083</v>
+        <v>0.9036828703703704</v>
       </c>
       <c r="F34" s="2">
-        <v>0.8989994739016479</v>
+        <v>0.8987230663251737</v>
       </c>
       <c r="G34" s="3">
-        <v>0.3626864735560398</v>
+        <v>0.4959804045196692</v>
       </c>
       <c r="H34">
         <v>11</v>
       </c>
       <c r="I34" s="1">
-        <v>1403</v>
+        <v>1286</v>
       </c>
       <c r="J34" s="2">
-        <v>0.8899479578392622</v>
+        <v>0.8899479578392623</v>
       </c>
       <c r="K34" s="2">
-        <v>0.9023163648193399</v>
+        <v>0.9023163648193397</v>
       </c>
       <c r="L34" s="3">
-        <v>-1.236840698007768</v>
+        <v>-1.236840698007746</v>
       </c>
       <c r="M34">
         <v>11</v>
       </c>
       <c r="N34" s="1">
-        <v>1443</v>
+        <v>1563</v>
       </c>
       <c r="O34" s="2">
         <v>0.9153047194351542</v>
@@ -2467,37 +2467,37 @@
         <v>1</v>
       </c>
       <c r="D35" s="1">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E35" s="2">
-        <v>0.9134381117213735</v>
+        <v>0.9146836750914006</v>
       </c>
       <c r="F35" s="2">
-        <v>0.8989994739016479</v>
+        <v>0.8987230663251737</v>
       </c>
       <c r="G35" s="3">
-        <v>1.443863781972554</v>
+        <v>1.596060876622685</v>
       </c>
       <c r="H35">
         <v>1</v>
       </c>
       <c r="I35" s="1">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="J35" s="2">
-        <v>0.8984913512810507</v>
+        <v>0.898491351281051</v>
       </c>
       <c r="K35" s="2">
-        <v>0.9023163648193399</v>
+        <v>0.9023163648193397</v>
       </c>
       <c r="L35" s="3">
-        <v>-0.3825013538289124</v>
+        <v>-0.3825013538288791</v>
       </c>
       <c r="M35">
         <v>1</v>
       </c>
       <c r="N35" s="1">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="O35" s="2">
         <v>0.9283848721616962</v>
@@ -2520,37 +2520,37 @@
         <v>14</v>
       </c>
       <c r="D36" s="1">
-        <v>3463</v>
+        <v>3457</v>
       </c>
       <c r="E36" s="2">
-        <v>0.893674513558197</v>
+        <v>0.8920566960882409</v>
       </c>
       <c r="F36" s="2">
-        <v>0.8989994739016479</v>
+        <v>0.8987230663251737</v>
       </c>
       <c r="G36" s="3">
-        <v>-0.5324960343450869</v>
+        <v>-0.6666370236932839</v>
       </c>
       <c r="H36">
         <v>14</v>
       </c>
       <c r="I36" s="1">
-        <v>1769</v>
+        <v>1622</v>
       </c>
       <c r="J36" s="2">
-        <v>0.9130883231976713</v>
+        <v>0.9130883231976714</v>
       </c>
       <c r="K36" s="2">
-        <v>0.9023163648193399</v>
+        <v>0.9023163648193397</v>
       </c>
       <c r="L36" s="3">
-        <v>1.077195837833145</v>
+        <v>1.077195837833167</v>
       </c>
       <c r="M36">
         <v>14</v>
       </c>
       <c r="N36" s="1">
-        <v>1694</v>
+        <v>1835</v>
       </c>
       <c r="O36" s="2">
         <v>0.8742607039187227</v>
@@ -2576,34 +2576,34 @@
         <v>348</v>
       </c>
       <c r="E37" s="2">
-        <v>0.9092608646327653</v>
+        <v>0.9101328946025917</v>
       </c>
       <c r="F37" s="2">
-        <v>0.8989994739016479</v>
+        <v>0.8987230663251737</v>
       </c>
       <c r="G37" s="3">
-        <v>1.026139073111743</v>
+        <v>1.140982827741799</v>
       </c>
       <c r="H37">
         <v>2</v>
       </c>
       <c r="I37" s="1">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="J37" s="2">
-        <v>0.8987965049948521</v>
+        <v>0.8987965049948522</v>
       </c>
       <c r="K37" s="2">
-        <v>0.9023163648193399</v>
+        <v>0.9023163648193397</v>
       </c>
       <c r="L37" s="3">
-        <v>-0.351985982448777</v>
+        <v>-0.3519859824487548</v>
       </c>
       <c r="M37">
         <v>2</v>
       </c>
       <c r="N37" s="1">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="O37" s="2">
         <v>0.9197252242706788</v>
@@ -2626,46 +2626,46 @@
         <v>11</v>
       </c>
       <c r="D38" s="1">
-        <v>2711</v>
+        <v>2700</v>
       </c>
       <c r="E38" s="2">
-        <v>0.8597541214823824</v>
+        <v>0.8561875</v>
       </c>
       <c r="F38" s="2">
-        <v>0.9011232026280093</v>
+        <v>0.9004013768967175</v>
       </c>
       <c r="G38" s="3">
-        <v>-4.136908114562687</v>
+        <v>-4.421387689671752</v>
       </c>
       <c r="H38">
         <v>11</v>
       </c>
       <c r="I38" s="1">
-        <v>1423</v>
+        <v>1304</v>
       </c>
       <c r="J38" s="2">
         <v>0.9025535792709706</v>
       </c>
       <c r="K38" s="2">
-        <v>0.9097851114035129</v>
+        <v>0.909785111403513</v>
       </c>
       <c r="L38" s="3">
-        <v>-0.7231532132542351</v>
+        <v>-0.7231532132542462</v>
       </c>
       <c r="M38">
         <v>11</v>
       </c>
       <c r="N38" s="1">
-        <v>1288</v>
+        <v>1395</v>
       </c>
       <c r="O38" s="2">
         <v>0.8169546636937941</v>
       </c>
       <c r="P38" s="2">
-        <v>0.8924612938525056</v>
+        <v>0.8924612938525057</v>
       </c>
       <c r="Q38" s="3">
-        <v>-7.550663015871151</v>
+        <v>-7.550663015871162</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -2679,46 +2679,46 @@
         <v>1</v>
       </c>
       <c r="D39" s="1">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E39" s="2">
-        <v>0.8914113068619506</v>
+        <v>0.8932562390716896</v>
       </c>
       <c r="F39" s="2">
-        <v>0.9011232026280093</v>
+        <v>0.9004013768967175</v>
       </c>
       <c r="G39" s="3">
-        <v>-0.9711895766058687</v>
+        <v>-0.7145137825027903</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39" s="1">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="J39" s="2">
         <v>0.8692721203450816</v>
       </c>
       <c r="K39" s="2">
-        <v>0.9097851114035129</v>
+        <v>0.909785111403513</v>
       </c>
       <c r="L39" s="3">
-        <v>-4.051299105843132</v>
+        <v>-4.051299105843142</v>
       </c>
       <c r="M39">
         <v>1</v>
       </c>
       <c r="N39" s="1">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="O39" s="2">
-        <v>0.9135504933788197</v>
+        <v>0.9135504933788196</v>
       </c>
       <c r="P39" s="2">
-        <v>0.8924612938525056</v>
+        <v>0.8924612938525057</v>
       </c>
       <c r="Q39" s="3">
-        <v>2.108919952631405</v>
+        <v>2.108919952631383</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -2732,46 +2732,46 @@
         <v>14</v>
       </c>
       <c r="D40" s="1">
-        <v>3627</v>
+        <v>3631</v>
       </c>
       <c r="E40" s="2">
-        <v>0.9358336194608706</v>
+        <v>0.9370332898561082</v>
       </c>
       <c r="F40" s="2">
-        <v>0.9011232026280093</v>
+        <v>0.9004013768967175</v>
       </c>
       <c r="G40" s="3">
-        <v>3.471041683286136</v>
+        <v>3.663191295939072</v>
       </c>
       <c r="H40">
         <v>14</v>
       </c>
       <c r="I40" s="1">
-        <v>1785</v>
+        <v>1637</v>
       </c>
       <c r="J40" s="2">
         <v>0.9214375747180207</v>
       </c>
       <c r="K40" s="2">
-        <v>0.9097851114035129</v>
+        <v>0.909785111403513</v>
       </c>
       <c r="L40" s="3">
-        <v>1.165246331450775</v>
+        <v>1.165246331450764</v>
       </c>
       <c r="M40">
         <v>14</v>
       </c>
       <c r="N40" s="1">
-        <v>1841</v>
+        <v>1995</v>
       </c>
       <c r="O40" s="2">
         <v>0.9502296642037207</v>
       </c>
       <c r="P40" s="2">
-        <v>0.8924612938525056</v>
+        <v>0.8924612938525057</v>
       </c>
       <c r="Q40" s="3">
-        <v>5.776837035121507</v>
+        <v>5.776837035121495</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -2785,46 +2785,46 @@
         <v>2</v>
       </c>
       <c r="D41" s="1">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E41" s="2">
-        <v>0.8997632074078353</v>
+        <v>0.900574558718498</v>
       </c>
       <c r="F41" s="2">
-        <v>0.9011232026280093</v>
+        <v>0.9004013768967175</v>
       </c>
       <c r="G41" s="3">
-        <v>-0.1359995220173937</v>
+        <v>0.01731818217804992</v>
       </c>
       <c r="H41">
         <v>2</v>
       </c>
       <c r="I41" s="1">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="J41" s="2">
-        <v>0.8900269916798841</v>
+        <v>0.8900269916798843</v>
       </c>
       <c r="K41" s="2">
-        <v>0.9097851114035129</v>
+        <v>0.909785111403513</v>
       </c>
       <c r="L41" s="3">
-        <v>-1.975811972362884</v>
+        <v>-1.975811972362873</v>
       </c>
       <c r="M41">
         <v>2</v>
       </c>
       <c r="N41" s="1">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="O41" s="2">
         <v>0.9094994231357866</v>
       </c>
       <c r="P41" s="2">
-        <v>0.8924612938525056</v>
+        <v>0.8924612938525057</v>
       </c>
       <c r="Q41" s="3">
-        <v>1.703812928328097</v>
+        <v>1.703812928328086</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -2838,46 +2838,46 @@
         <v>11</v>
       </c>
       <c r="D42" s="1">
-        <v>2798</v>
+        <v>2800</v>
       </c>
       <c r="E42" s="2">
-        <v>0.8874809381439817</v>
+        <v>0.8879067028985507</v>
       </c>
       <c r="F42" s="2">
-        <v>0.8896079030766169</v>
+        <v>0.8904269118708189</v>
       </c>
       <c r="G42" s="3">
-        <v>-0.21269649326352</v>
+        <v>-0.2520208972268234</v>
       </c>
       <c r="H42">
         <v>11</v>
       </c>
       <c r="I42" s="1">
-        <v>1391</v>
+        <v>1275</v>
       </c>
       <c r="J42" s="2">
-        <v>0.8823717610891525</v>
+        <v>0.8823717610891524</v>
       </c>
       <c r="K42" s="2">
         <v>0.8797797975461918</v>
       </c>
       <c r="L42" s="3">
-        <v>0.2591963542960651</v>
+        <v>0.259196354296054</v>
       </c>
       <c r="M42">
         <v>11</v>
       </c>
       <c r="N42" s="1">
-        <v>1407</v>
+        <v>1525</v>
       </c>
       <c r="O42" s="2">
-        <v>0.8925901151988109</v>
+        <v>0.8925901151988108</v>
       </c>
       <c r="P42" s="2">
         <v>0.8994360086070419</v>
       </c>
       <c r="Q42" s="3">
-        <v>-0.6845893408230941</v>
+        <v>-0.6845893408231052</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -2891,46 +2891,46 @@
         <v>1</v>
       </c>
       <c r="D43" s="1">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E43" s="2">
-        <v>0.8524710625568995</v>
+        <v>0.8550886186615799</v>
       </c>
       <c r="F43" s="2">
-        <v>0.8896079030766169</v>
+        <v>0.8904269118708189</v>
       </c>
       <c r="G43" s="3">
-        <v>-3.713684051971733</v>
+        <v>-3.533829320923898</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43" s="1">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="J43" s="2">
-        <v>0.8210603893007328</v>
+        <v>0.8210603893007326</v>
       </c>
       <c r="K43" s="2">
         <v>0.8797797975461918</v>
       </c>
       <c r="L43" s="3">
-        <v>-5.871940824545907</v>
+        <v>-5.871940824545929</v>
       </c>
       <c r="M43">
         <v>1</v>
       </c>
       <c r="N43" s="1">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="O43" s="2">
-        <v>0.8838817358130663</v>
+        <v>0.8838817358130662</v>
       </c>
       <c r="P43" s="2">
         <v>0.8994360086070419</v>
       </c>
       <c r="Q43" s="3">
-        <v>-1.555427279397559</v>
+        <v>-1.55542727939757</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -2944,37 +2944,37 @@
         <v>14</v>
       </c>
       <c r="D44" s="1">
-        <v>3468</v>
+        <v>3473</v>
       </c>
       <c r="E44" s="2">
-        <v>0.8949823288132678</v>
+        <v>0.8960717880455499</v>
       </c>
       <c r="F44" s="2">
-        <v>0.8896079030766169</v>
+        <v>0.8904269118708189</v>
       </c>
       <c r="G44" s="3">
-        <v>0.5374425736650923</v>
+        <v>0.5644876174730973</v>
       </c>
       <c r="H44">
         <v>14</v>
       </c>
       <c r="I44" s="1">
-        <v>1709</v>
+        <v>1566</v>
       </c>
       <c r="J44" s="2">
-        <v>0.8819088180258848</v>
+        <v>0.8819088180258849</v>
       </c>
       <c r="K44" s="2">
         <v>0.8797797975461918</v>
       </c>
       <c r="L44" s="3">
-        <v>0.2129020479692989</v>
+        <v>0.21290204796931</v>
       </c>
       <c r="M44">
         <v>14</v>
       </c>
       <c r="N44" s="1">
-        <v>1760</v>
+        <v>1906</v>
       </c>
       <c r="O44" s="2">
         <v>0.9080558396006508</v>
@@ -3000,43 +3000,43 @@
         <v>340</v>
       </c>
       <c r="E45" s="2">
-        <v>0.8881371459883856</v>
+        <v>0.8877423222120192</v>
       </c>
       <c r="F45" s="2">
-        <v>0.8896079030766169</v>
+        <v>0.8904269118708189</v>
       </c>
       <c r="G45" s="3">
-        <v>-0.14707570882313</v>
+        <v>-0.2684589658799696</v>
       </c>
       <c r="H45">
         <v>2</v>
       </c>
       <c r="I45" s="1">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="J45" s="2">
-        <v>0.8928750313047832</v>
+        <v>0.8928750313047834</v>
       </c>
       <c r="K45" s="2">
         <v>0.8797797975461918</v>
       </c>
       <c r="L45" s="3">
-        <v>1.309523375859134</v>
+        <v>1.309523375859156</v>
       </c>
       <c r="M45">
         <v>2</v>
       </c>
       <c r="N45" s="1">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="O45" s="2">
-        <v>0.8833992606719878</v>
+        <v>0.8833992606719879</v>
       </c>
       <c r="P45" s="2">
         <v>0.8994360086070419</v>
       </c>
       <c r="Q45" s="3">
-        <v>-1.603674793505405</v>
+        <v>-1.603674793505394</v>
       </c>
     </row>
     <row r="46" spans="1:17">
@@ -3050,28 +3050,28 @@
         <v>12</v>
       </c>
       <c r="D46" s="1">
-        <v>2869</v>
+        <v>2872</v>
       </c>
       <c r="E46" s="2">
-        <v>0.866034093501505</v>
+        <v>0.8704321489919538</v>
       </c>
       <c r="F46" s="2">
-        <v>0.8901845880970316</v>
+        <v>0.8916101253733195</v>
       </c>
       <c r="G46" s="3">
-        <v>-2.415049459552665</v>
+        <v>-2.117797638136576</v>
       </c>
       <c r="H46">
         <v>12</v>
       </c>
       <c r="I46" s="1">
-        <v>1417</v>
+        <v>1299</v>
       </c>
       <c r="J46" s="2">
-        <v>0.8158870585045082</v>
+        <v>0.8158870585045083</v>
       </c>
       <c r="K46" s="2">
-        <v>0.8731126143424988</v>
+        <v>0.8731126143424989</v>
       </c>
       <c r="L46" s="3">
         <v>-5.72255558379906</v>
@@ -3080,16 +3080,16 @@
         <v>11</v>
       </c>
       <c r="N46" s="1">
-        <v>1453</v>
+        <v>1574</v>
       </c>
       <c r="O46" s="2">
         <v>0.9212612411742847</v>
       </c>
       <c r="P46" s="2">
-        <v>0.9073203142788924</v>
+        <v>0.9073203142788925</v>
       </c>
       <c r="Q46" s="3">
-        <v>1.394092689539228</v>
+        <v>1.394092689539217</v>
       </c>
     </row>
     <row r="47" spans="1:17">
@@ -3103,46 +3103,46 @@
         <v>1</v>
       </c>
       <c r="D47" s="1">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E47" s="2">
-        <v>0.7223892940631138</v>
+        <v>0.7325504689238594</v>
       </c>
       <c r="F47" s="2">
-        <v>0.8901845880970316</v>
+        <v>0.8916101253733195</v>
       </c>
       <c r="G47" s="3">
-        <v>-16.77952940339178</v>
+        <v>-15.90596564494601</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47" s="1">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J47" s="2">
         <v>0.6004551957341656</v>
       </c>
       <c r="K47" s="2">
-        <v>0.8731126143424988</v>
+        <v>0.8731126143424989</v>
       </c>
       <c r="L47" s="3">
-        <v>-27.26574186083332</v>
+        <v>-27.26574186083333</v>
       </c>
       <c r="M47">
         <v>1</v>
       </c>
       <c r="N47" s="1">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="O47" s="2">
-        <v>0.844323392392062</v>
+        <v>0.8443233923920619</v>
       </c>
       <c r="P47" s="2">
-        <v>0.9073203142788924</v>
+        <v>0.9073203142788925</v>
       </c>
       <c r="Q47" s="3">
-        <v>-6.299692188683037</v>
+        <v>-6.299692188683059</v>
       </c>
     </row>
     <row r="48" spans="1:17">
@@ -3156,46 +3156,46 @@
         <v>14</v>
       </c>
       <c r="D48" s="1">
-        <v>3444</v>
+        <v>3448</v>
       </c>
       <c r="E48" s="2">
-        <v>0.9233149690798519</v>
+        <v>0.9213447249166987</v>
       </c>
       <c r="F48" s="2">
-        <v>0.8901845880970316</v>
+        <v>0.8916101253733195</v>
       </c>
       <c r="G48" s="3">
-        <v>3.313038098282028</v>
+        <v>2.97345995433792</v>
       </c>
       <c r="H48">
         <v>13</v>
       </c>
       <c r="I48" s="1">
-        <v>1699</v>
+        <v>1558</v>
       </c>
       <c r="J48" s="2">
         <v>0.9479953082803935</v>
       </c>
       <c r="K48" s="2">
-        <v>0.8731126143424988</v>
+        <v>0.8731126143424989</v>
       </c>
       <c r="L48" s="3">
-        <v>7.488269393789471</v>
+        <v>7.48826939378946</v>
       </c>
       <c r="M48">
         <v>14</v>
       </c>
       <c r="N48" s="1">
-        <v>1745</v>
+        <v>1890</v>
       </c>
       <c r="O48" s="2">
         <v>0.9004840678189734</v>
       </c>
       <c r="P48" s="2">
-        <v>0.9073203142788924</v>
+        <v>0.9073203142788925</v>
       </c>
       <c r="Q48" s="3">
-        <v>-0.6836246459918982</v>
+        <v>-0.6836246459919093</v>
       </c>
     </row>
     <row r="49" spans="1:17">
@@ -3212,43 +3212,43 @@
         <v>358</v>
       </c>
       <c r="E49" s="2">
-        <v>0.9363880380409306</v>
+        <v>0.9351698806244261</v>
       </c>
       <c r="F49" s="2">
-        <v>0.8901845880970316</v>
+        <v>0.8916101253733195</v>
       </c>
       <c r="G49" s="3">
-        <v>4.620344994389902</v>
+        <v>4.355975525110656</v>
       </c>
       <c r="H49">
         <v>2</v>
       </c>
       <c r="I49" s="1">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="J49" s="2">
         <v>0.9510059270389848</v>
       </c>
       <c r="K49" s="2">
-        <v>0.8731126143424988</v>
+        <v>0.8731126143424989</v>
       </c>
       <c r="L49" s="3">
-        <v>7.789331269648603</v>
+        <v>7.789331269648592</v>
       </c>
       <c r="M49">
         <v>2</v>
       </c>
       <c r="N49" s="1">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="O49" s="2">
         <v>0.9217701490428762</v>
       </c>
       <c r="P49" s="2">
-        <v>0.9073203142788924</v>
+        <v>0.9073203142788925</v>
       </c>
       <c r="Q49" s="3">
-        <v>1.444983476398387</v>
+        <v>1.444983476398376</v>
       </c>
     </row>
     <row r="50" spans="1:17">
@@ -3262,46 +3262,46 @@
         <v>12</v>
       </c>
       <c r="D50" s="1">
-        <v>3015</v>
+        <v>3020</v>
       </c>
       <c r="E50" s="2">
-        <v>0.8680563109303734</v>
+        <v>0.8695394861897033</v>
       </c>
       <c r="F50" s="2">
-        <v>0.8911929620742598</v>
+        <v>0.8919409061730958</v>
       </c>
       <c r="G50" s="3">
-        <v>-2.313665114388641</v>
+        <v>-2.240141998339251</v>
       </c>
       <c r="H50">
         <v>12</v>
       </c>
       <c r="I50" s="1">
-        <v>1476</v>
+        <v>1353</v>
       </c>
       <c r="J50" s="2">
-        <v>0.850258207818413</v>
+        <v>0.8502582078184132</v>
       </c>
       <c r="K50" s="2">
         <v>0.8822176328882262</v>
       </c>
       <c r="L50" s="3">
-        <v>-3.19594250698132</v>
+        <v>-3.195942506981297</v>
       </c>
       <c r="M50">
         <v>12</v>
       </c>
       <c r="N50" s="1">
-        <v>1538</v>
+        <v>1666</v>
       </c>
       <c r="O50" s="2">
         <v>0.8858544140423334</v>
       </c>
       <c r="P50" s="2">
-        <v>0.9001682912602934</v>
+        <v>0.9001682912602933</v>
       </c>
       <c r="Q50" s="3">
-        <v>-1.431387721795996</v>
+        <v>-1.431387721795985</v>
       </c>
     </row>
     <row r="51" spans="1:17">
@@ -3318,40 +3318,40 @@
         <v>285</v>
       </c>
       <c r="E51" s="2">
-        <v>0.7803220384765451</v>
+        <v>0.7800925925925927</v>
       </c>
       <c r="F51" s="2">
-        <v>0.8911929620742598</v>
+        <v>0.8919409061730958</v>
       </c>
       <c r="G51" s="3">
-        <v>-11.08709235977147</v>
+        <v>-11.18483135805032</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51" s="1">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J51" s="2">
-        <v>0.7830753890839729</v>
+        <v>0.7830753890839728</v>
       </c>
       <c r="K51" s="2">
         <v>0.8822176328882262</v>
       </c>
       <c r="L51" s="3">
-        <v>-9.914224380425329</v>
+        <v>-9.91422438042534</v>
       </c>
       <c r="M51">
         <v>1</v>
       </c>
       <c r="N51" s="1">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="O51" s="2">
-        <v>0.7775686878691171</v>
+        <v>0.777568687869117</v>
       </c>
       <c r="P51" s="2">
-        <v>0.9001682912602934</v>
+        <v>0.9001682912602933</v>
       </c>
       <c r="Q51" s="3">
         <v>-12.25996033911763</v>
@@ -3368,22 +3368,22 @@
         <v>13</v>
       </c>
       <c r="D52" s="1">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="E52" s="2">
-        <v>0.9508504687262365</v>
+        <v>0.9505710717090947</v>
       </c>
       <c r="F52" s="2">
-        <v>0.8911929620742598</v>
+        <v>0.8919409061730958</v>
       </c>
       <c r="G52" s="3">
-        <v>5.965750665197667</v>
+        <v>5.863016553599887</v>
       </c>
       <c r="H52">
         <v>13</v>
       </c>
       <c r="I52" s="1">
-        <v>1710</v>
+        <v>1568</v>
       </c>
       <c r="J52" s="2">
         <v>0.9542032329319385</v>
@@ -3398,16 +3398,16 @@
         <v>13</v>
       </c>
       <c r="N52" s="1">
-        <v>1698</v>
+        <v>1840</v>
       </c>
       <c r="O52" s="2">
         <v>0.9474977045205345</v>
       </c>
       <c r="P52" s="2">
-        <v>0.9001682912602934</v>
+        <v>0.9001682912602933</v>
       </c>
       <c r="Q52" s="3">
-        <v>4.732941326024109</v>
+        <v>4.73294132602412</v>
       </c>
     </row>
     <row r="53" spans="1:17">
@@ -3421,46 +3421,46 @@
         <v>2</v>
       </c>
       <c r="D53" s="1">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E53" s="2">
-        <v>0.6481435995898805</v>
+        <v>0.6527745893276197</v>
       </c>
       <c r="F53" s="2">
-        <v>0.8911929620742598</v>
+        <v>0.8919409061730958</v>
       </c>
       <c r="G53" s="3">
-        <v>-24.30493624843793</v>
+        <v>-23.91663168454762</v>
       </c>
       <c r="H53">
         <v>2</v>
       </c>
       <c r="I53" s="1">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="J53" s="2">
-        <v>0.5925717227370119</v>
+        <v>0.5925717227370121</v>
       </c>
       <c r="K53" s="2">
         <v>0.8822176328882262</v>
       </c>
       <c r="L53" s="3">
-        <v>-28.96459101512143</v>
+        <v>-28.96459101512141</v>
       </c>
       <c r="M53">
         <v>2</v>
       </c>
       <c r="N53" s="1">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="O53" s="2">
         <v>0.7037154764427491</v>
       </c>
       <c r="P53" s="2">
-        <v>0.9001682912602934</v>
+        <v>0.9001682912602933</v>
       </c>
       <c r="Q53" s="3">
-        <v>-19.64528148175443</v>
+        <v>-19.64528148175442</v>
       </c>
     </row>
     <row r="54" spans="1:17">
@@ -3474,46 +3474,46 @@
         <v>12</v>
       </c>
       <c r="D54" s="1">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="E54" s="2">
-        <v>0.9104591727963224</v>
+        <v>0.9103590019154567</v>
       </c>
       <c r="F54" s="2">
-        <v>0.9228596929801954</v>
+        <v>0.9231384495294301</v>
       </c>
       <c r="G54" s="3">
-        <v>-1.240052018387305</v>
+        <v>-1.277944761397343</v>
       </c>
       <c r="H54">
         <v>12</v>
       </c>
       <c r="I54" s="1">
-        <v>1583</v>
+        <v>1451</v>
       </c>
       <c r="J54" s="2">
         <v>0.911661223366711</v>
       </c>
       <c r="K54" s="2">
-        <v>0.9195146143893789</v>
+        <v>0.9195146143893788</v>
       </c>
       <c r="L54" s="3">
-        <v>-0.785339102266791</v>
+        <v>-0.7853391022667799</v>
       </c>
       <c r="M54">
         <v>12</v>
       </c>
       <c r="N54" s="1">
-        <v>1579</v>
+        <v>1710</v>
       </c>
       <c r="O54" s="2">
-        <v>0.9092571222259339</v>
+        <v>0.909257122225934</v>
       </c>
       <c r="P54" s="2">
         <v>0.9262047715710119</v>
       </c>
       <c r="Q54" s="3">
-        <v>-1.694764934507798</v>
+        <v>-1.694764934507786</v>
       </c>
     </row>
     <row r="55" spans="1:17">
@@ -3530,25 +3530,25 @@
         <v>314</v>
       </c>
       <c r="E55" s="2">
-        <v>0.8597196794621688</v>
+        <v>0.8611150850421238</v>
       </c>
       <c r="F55" s="2">
-        <v>0.9228596929801954</v>
+        <v>0.9231384495294301</v>
       </c>
       <c r="G55" s="3">
-        <v>-6.314001351802667</v>
+        <v>-6.202336448730639</v>
       </c>
       <c r="H55">
         <v>1</v>
       </c>
       <c r="I55" s="1">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="J55" s="2">
-        <v>0.8429748125027097</v>
+        <v>0.8429748125027096</v>
       </c>
       <c r="K55" s="2">
-        <v>0.9195146143893789</v>
+        <v>0.9195146143893788</v>
       </c>
       <c r="L55" s="3">
         <v>-7.65398018866692</v>
@@ -3557,7 +3557,7 @@
         <v>1</v>
       </c>
       <c r="N55" s="1">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="O55" s="2">
         <v>0.876464546421628</v>
@@ -3580,46 +3580,46 @@
         <v>13</v>
       </c>
       <c r="D56" s="1">
-        <v>3364</v>
+        <v>3366</v>
       </c>
       <c r="E56" s="2">
-        <v>0.9384065590607483</v>
+        <v>0.9389221262924763</v>
       </c>
       <c r="F56" s="2">
-        <v>0.9228596929801954</v>
+        <v>0.9231384495294301</v>
       </c>
       <c r="G56" s="3">
-        <v>1.554686608055289</v>
+        <v>1.578367676304615</v>
       </c>
       <c r="H56">
         <v>13</v>
       </c>
       <c r="I56" s="1">
-        <v>1671</v>
+        <v>1532</v>
       </c>
       <c r="J56" s="2">
-        <v>0.9322197522800142</v>
+        <v>0.9322197522800143</v>
       </c>
       <c r="K56" s="2">
-        <v>0.9195146143893789</v>
+        <v>0.9195146143893788</v>
       </c>
       <c r="L56" s="3">
-        <v>1.270513789063532</v>
+        <v>1.270513789063554</v>
       </c>
       <c r="M56">
         <v>13</v>
       </c>
       <c r="N56" s="1">
-        <v>1693</v>
+        <v>1834</v>
       </c>
       <c r="O56" s="2">
-        <v>0.9445933658414826</v>
+        <v>0.9445933658414827</v>
       </c>
       <c r="P56" s="2">
         <v>0.9262047715710119</v>
       </c>
       <c r="Q56" s="3">
-        <v>1.838859427047068</v>
+        <v>1.838859427047079</v>
       </c>
     </row>
     <row r="57" spans="1:17">
@@ -3636,43 +3636,43 @@
         <v>364</v>
       </c>
       <c r="E57" s="2">
-        <v>0.9499738324118489</v>
+        <v>0.9504074839302112</v>
       </c>
       <c r="F57" s="2">
-        <v>0.9228596929801954</v>
+        <v>0.9231384495294301</v>
       </c>
       <c r="G57" s="3">
-        <v>2.711413943165342</v>
+        <v>2.72690344007811</v>
       </c>
       <c r="H57">
         <v>2</v>
       </c>
       <c r="I57" s="1">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="J57" s="2">
-        <v>0.9447700141915018</v>
+        <v>0.944770014191502</v>
       </c>
       <c r="K57" s="2">
-        <v>0.9195146143893789</v>
+        <v>0.9195146143893788</v>
       </c>
       <c r="L57" s="3">
-        <v>2.525539980212288</v>
+        <v>2.525539980212321</v>
       </c>
       <c r="M57">
         <v>2</v>
       </c>
       <c r="N57" s="1">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="O57" s="2">
-        <v>0.9551776506321961</v>
+        <v>0.955177650632196</v>
       </c>
       <c r="P57" s="2">
         <v>0.9262047715710119</v>
       </c>
       <c r="Q57" s="3">
-        <v>2.897287906118418</v>
+        <v>2.897287906118406</v>
       </c>
     </row>
     <row r="58" spans="1:17">
@@ -3686,46 +3686,46 @@
         <v>12</v>
       </c>
       <c r="D58" s="1">
-        <v>3062</v>
+        <v>3060</v>
       </c>
       <c r="E58" s="2">
-        <v>0.8817272991078755</v>
+        <v>0.8810449291573452</v>
       </c>
       <c r="F58" s="2">
-        <v>0.8832011896592704</v>
+        <v>0.8818391330542817</v>
       </c>
       <c r="G58" s="3">
-        <v>-0.1473890551394907</v>
+        <v>-0.07942038969365184</v>
       </c>
       <c r="H58">
         <v>12</v>
       </c>
       <c r="I58" s="1">
-        <v>1545</v>
+        <v>1416</v>
       </c>
       <c r="J58" s="2">
-        <v>0.8899157385142382</v>
+        <v>0.8899157385142384</v>
       </c>
       <c r="K58" s="2">
-        <v>0.8998879811680002</v>
+        <v>0.8998879811680001</v>
       </c>
       <c r="L58" s="3">
-        <v>-0.9972242653761954</v>
+        <v>-0.997224265376162</v>
       </c>
       <c r="M58">
         <v>12</v>
       </c>
       <c r="N58" s="1">
-        <v>1517</v>
+        <v>1643</v>
       </c>
       <c r="O58" s="2">
-        <v>0.8735388597015126</v>
+        <v>0.8735388597015127</v>
       </c>
       <c r="P58" s="2">
-        <v>0.8671352200822801</v>
+        <v>0.8671352200822799</v>
       </c>
       <c r="Q58" s="3">
-        <v>0.6403639619232515</v>
+        <v>0.6403639619232737</v>
       </c>
     </row>
     <row r="59" spans="1:17">
@@ -3739,43 +3739,43 @@
         <v>1</v>
       </c>
       <c r="D59" s="1">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E59" s="2">
-        <v>0.8404462252101738</v>
+        <v>0.8390180416467968</v>
       </c>
       <c r="F59" s="2">
-        <v>0.8832011896592704</v>
+        <v>0.8818391330542817</v>
       </c>
       <c r="G59" s="3">
-        <v>-4.275496444909665</v>
+        <v>-4.282109140748491</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59" s="1">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="J59" s="2">
-        <v>0.8575844279706941</v>
+        <v>0.8575844279706939</v>
       </c>
       <c r="K59" s="2">
-        <v>0.8998879811680002</v>
+        <v>0.8998879811680001</v>
       </c>
       <c r="L59" s="3">
-        <v>-4.230355319730606</v>
+        <v>-4.230355319730617</v>
       </c>
       <c r="M59">
         <v>1</v>
       </c>
       <c r="N59" s="1">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="O59" s="2">
-        <v>0.8233080224496533</v>
+        <v>0.8233080224496532</v>
       </c>
       <c r="P59" s="2">
-        <v>0.8671352200822801</v>
+        <v>0.8671352200822799</v>
       </c>
       <c r="Q59" s="3">
         <v>-4.382719763262677</v>
@@ -3792,46 +3792,46 @@
         <v>13</v>
       </c>
       <c r="D60" s="1">
-        <v>3030</v>
+        <v>3033</v>
       </c>
       <c r="E60" s="2">
-        <v>0.8807695193467282</v>
+        <v>0.8786854690824963</v>
       </c>
       <c r="F60" s="2">
-        <v>0.8832011896592704</v>
+        <v>0.8818391330542817</v>
       </c>
       <c r="G60" s="3">
-        <v>-0.2431670312542211</v>
+        <v>-0.3153663971785403</v>
       </c>
       <c r="H60">
         <v>12</v>
       </c>
       <c r="I60" s="1">
-        <v>1494</v>
+        <v>1370</v>
       </c>
       <c r="J60" s="2">
-        <v>0.9069721808246398</v>
+        <v>0.9069721808246399</v>
       </c>
       <c r="K60" s="2">
-        <v>0.8998879811680002</v>
+        <v>0.8998879811680001</v>
       </c>
       <c r="L60" s="3">
-        <v>0.7084199656639645</v>
+        <v>0.7084199656639867</v>
       </c>
       <c r="M60">
         <v>13</v>
       </c>
       <c r="N60" s="1">
-        <v>1536</v>
+        <v>1664</v>
       </c>
       <c r="O60" s="2">
-        <v>0.8566894283141819</v>
+        <v>0.856689428314182</v>
       </c>
       <c r="P60" s="2">
-        <v>0.8671352200822801</v>
+        <v>0.8671352200822799</v>
       </c>
       <c r="Q60" s="3">
-        <v>-1.044579176809812</v>
+        <v>-1.04457917680979</v>
       </c>
     </row>
     <row r="61" spans="1:17">
@@ -3848,43 +3848,43 @@
         <v>367</v>
       </c>
       <c r="E61" s="2">
-        <v>0.9591932248957041</v>
+        <v>0.9583154780124478</v>
       </c>
       <c r="F61" s="2">
-        <v>0.8832011896592704</v>
+        <v>0.8818391330542817</v>
       </c>
       <c r="G61" s="3">
-        <v>7.599203523643371</v>
+        <v>7.647634495816602</v>
       </c>
       <c r="H61">
         <v>2</v>
       </c>
       <c r="I61" s="1">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="J61" s="2">
-        <v>0.9697261874947825</v>
+        <v>0.9697261874947826</v>
       </c>
       <c r="K61" s="2">
-        <v>0.8998879811680002</v>
+        <v>0.8998879811680001</v>
       </c>
       <c r="L61" s="3">
-        <v>6.983820632678228</v>
+        <v>6.983820632678251</v>
       </c>
       <c r="M61">
         <v>2</v>
       </c>
       <c r="N61" s="1">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="O61" s="2">
-        <v>0.9486602622966257</v>
+        <v>0.9486602622966258</v>
       </c>
       <c r="P61" s="2">
-        <v>0.8671352200822801</v>
+        <v>0.8671352200822799</v>
       </c>
       <c r="Q61" s="3">
-        <v>8.152504221434565</v>
+        <v>8.152504221434587</v>
       </c>
     </row>
     <row r="62" spans="1:17">
@@ -3898,46 +3898,46 @@
         <v>12</v>
       </c>
       <c r="D62" s="1">
-        <v>2871</v>
+        <v>2893</v>
       </c>
       <c r="E62" s="2">
-        <v>0.8266992022321671</v>
+        <v>0.8329921882996301</v>
       </c>
       <c r="F62" s="2">
-        <v>0.8751218241573298</v>
+        <v>0.878462470772397</v>
       </c>
       <c r="G62" s="3">
-        <v>-4.842262192516267</v>
+        <v>-4.547028247276696</v>
       </c>
       <c r="H62">
         <v>12</v>
       </c>
       <c r="I62" s="1">
-        <v>1304</v>
+        <v>1196</v>
       </c>
       <c r="J62" s="2">
-        <v>0.7511833694226113</v>
+        <v>0.7511833694226114</v>
       </c>
       <c r="K62" s="2">
         <v>0.8350340647765211</v>
       </c>
       <c r="L62" s="3">
-        <v>-8.385069535390976</v>
+        <v>-8.385069535390965</v>
       </c>
       <c r="M62">
         <v>12</v>
       </c>
       <c r="N62" s="1">
-        <v>1567</v>
+        <v>1697</v>
       </c>
       <c r="O62" s="2">
-        <v>0.9022150350417226</v>
+        <v>0.9022150350417228</v>
       </c>
       <c r="P62" s="2">
-        <v>0.9152095835381384</v>
+        <v>0.9152095835381383</v>
       </c>
       <c r="Q62" s="3">
-        <v>-1.299454849641579</v>
+        <v>-1.299454849641546</v>
       </c>
     </row>
     <row r="63" spans="1:17">
@@ -3951,22 +3951,22 @@
         <v>1</v>
       </c>
       <c r="D63" s="1">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E63" s="2">
-        <v>0.7680162469862041</v>
+        <v>0.7700484819583532</v>
       </c>
       <c r="F63" s="2">
-        <v>0.8751218241573298</v>
+        <v>0.878462470772397</v>
       </c>
       <c r="G63" s="3">
-        <v>-10.71055771711257</v>
+        <v>-10.84139888140438</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63" s="1">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J63" s="2">
         <v>0.7436294273204145</v>
@@ -3981,16 +3981,16 @@
         <v>1</v>
       </c>
       <c r="N63" s="1">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="O63" s="2">
         <v>0.7924030666519937</v>
       </c>
       <c r="P63" s="2">
-        <v>0.9152095835381384</v>
+        <v>0.9152095835381383</v>
       </c>
       <c r="Q63" s="3">
-        <v>-12.28065168861447</v>
+        <v>-12.28065168861446</v>
       </c>
     </row>
     <row r="64" spans="1:17">
@@ -4004,46 +4004,46 @@
         <v>12</v>
       </c>
       <c r="D64" s="1">
-        <v>3079</v>
+        <v>3080</v>
       </c>
       <c r="E64" s="2">
-        <v>0.9345711087987254</v>
+        <v>0.9349950084068936</v>
       </c>
       <c r="F64" s="2">
-        <v>0.8751218241573298</v>
+        <v>0.878462470772397</v>
       </c>
       <c r="G64" s="3">
-        <v>5.944928464139565</v>
+        <v>5.653253763449662</v>
       </c>
       <c r="H64">
         <v>12</v>
       </c>
       <c r="I64" s="1">
-        <v>1531</v>
+        <v>1404</v>
       </c>
       <c r="J64" s="2">
-        <v>0.9294843135007068</v>
+        <v>0.929484313500707</v>
       </c>
       <c r="K64" s="2">
         <v>0.8350340647765211</v>
       </c>
       <c r="L64" s="3">
-        <v>9.445024872418573</v>
+        <v>9.445024872418594</v>
       </c>
       <c r="M64">
         <v>12</v>
       </c>
       <c r="N64" s="1">
-        <v>1548</v>
+        <v>1677</v>
       </c>
       <c r="O64" s="2">
         <v>0.9396579040967439</v>
       </c>
       <c r="P64" s="2">
-        <v>0.9152095835381384</v>
+        <v>0.9152095835381383</v>
       </c>
       <c r="Q64" s="3">
-        <v>2.444832055860546</v>
+        <v>2.444832055860557</v>
       </c>
     </row>
     <row r="65" spans="1:17">
@@ -4057,46 +4057,46 @@
         <v>2</v>
       </c>
       <c r="D65" s="1">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E65" s="2">
-        <v>0.9049063425096482</v>
+        <v>0.9078142536475869</v>
       </c>
       <c r="F65" s="2">
-        <v>0.8751218241573298</v>
+        <v>0.878462470772397</v>
       </c>
       <c r="G65" s="3">
-        <v>2.978451835231843</v>
+        <v>2.935178287518991</v>
       </c>
       <c r="H65">
         <v>2</v>
       </c>
       <c r="I65" s="1">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="J65" s="2">
-        <v>0.870011408854384</v>
+        <v>0.8700114088543841</v>
       </c>
       <c r="K65" s="2">
         <v>0.8350340647765211</v>
       </c>
       <c r="L65" s="3">
-        <v>3.49773440778629</v>
+        <v>3.497734407786302</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65" s="1">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="O65" s="2">
         <v>0.9398012761649124</v>
       </c>
       <c r="P65" s="2">
-        <v>0.9152095835381384</v>
+        <v>0.9152095835381383</v>
       </c>
       <c r="Q65" s="3">
-        <v>2.459169262677396</v>
+        <v>2.459169262677408</v>
       </c>
     </row>
     <row r="66" spans="1:17">
@@ -4110,46 +4110,46 @@
         <v>12</v>
       </c>
       <c r="D66" s="1">
-        <v>2283</v>
+        <v>2326</v>
       </c>
       <c r="E66" s="2">
-        <v>0.6573617219294281</v>
+        <v>0.6699163632641721</v>
       </c>
       <c r="F66" s="2">
-        <v>0.6913538250570118</v>
+        <v>0.7050154264312666</v>
       </c>
       <c r="G66" s="3">
-        <v>-3.399210312758372</v>
+        <v>-3.509906316709444</v>
       </c>
       <c r="H66">
         <v>12</v>
       </c>
       <c r="I66" s="1">
-        <v>880</v>
+        <v>807</v>
       </c>
       <c r="J66" s="2">
-        <v>0.5067060259125004</v>
+        <v>0.5067060259125005</v>
       </c>
       <c r="K66" s="2">
         <v>0.5315285559222972</v>
       </c>
       <c r="L66" s="3">
-        <v>-2.482253000979684</v>
+        <v>-2.482253000979673</v>
       </c>
       <c r="M66">
         <v>12</v>
       </c>
       <c r="N66" s="1">
-        <v>1403</v>
+        <v>1520</v>
       </c>
       <c r="O66" s="2">
-        <v>0.8080174179463558</v>
+        <v>0.808017417946356</v>
       </c>
       <c r="P66" s="2">
         <v>0.8589431775079349</v>
       </c>
       <c r="Q66" s="3">
-        <v>-5.092575956157908</v>
+        <v>-5.092575956157896</v>
       </c>
     </row>
     <row r="67" spans="1:17">
@@ -4163,22 +4163,22 @@
         <v>2</v>
       </c>
       <c r="D67" s="1">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E67" s="2">
-        <v>0.5906869954080255</v>
+        <v>0.6020723482526057</v>
       </c>
       <c r="F67" s="2">
-        <v>0.6913538250570118</v>
+        <v>0.7050154264312666</v>
       </c>
       <c r="G67" s="3">
-        <v>-10.06668296489863</v>
+        <v>-10.29430781786609</v>
       </c>
       <c r="H67">
         <v>2</v>
       </c>
       <c r="I67" s="1">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="J67" s="2">
         <v>0.4910651580179477</v>
@@ -4193,16 +4193,16 @@
         <v>1</v>
       </c>
       <c r="N67" s="1">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="O67" s="2">
-        <v>0.789930670188181</v>
+        <v>0.7899306701881808</v>
       </c>
       <c r="P67" s="2">
         <v>0.8589431775079349</v>
       </c>
       <c r="Q67" s="3">
-        <v>-6.901250731975395</v>
+        <v>-6.901250731975416</v>
       </c>
     </row>
     <row r="68" spans="1:17">
@@ -4216,37 +4216,37 @@
         <v>12</v>
       </c>
       <c r="D68" s="1">
-        <v>2445</v>
+        <v>2493</v>
       </c>
       <c r="E68" s="2">
-        <v>0.7421922444936315</v>
+        <v>0.7567654476670871</v>
       </c>
       <c r="F68" s="2">
-        <v>0.6913538250570118</v>
+        <v>0.7050154264312666</v>
       </c>
       <c r="G68" s="3">
-        <v>5.083841943661971</v>
+        <v>5.17500212358205</v>
       </c>
       <c r="H68">
         <v>12</v>
       </c>
       <c r="I68" s="1">
-        <v>935</v>
+        <v>857</v>
       </c>
       <c r="J68" s="2">
-        <v>0.567313806412167</v>
+        <v>0.5673138064121671</v>
       </c>
       <c r="K68" s="2">
         <v>0.5315285559222972</v>
       </c>
       <c r="L68" s="3">
-        <v>3.57852504898698</v>
+        <v>3.578525048986991</v>
       </c>
       <c r="M68">
         <v>12</v>
       </c>
       <c r="N68" s="1">
-        <v>1511</v>
+        <v>1637</v>
       </c>
       <c r="O68" s="2">
         <v>0.9170706825750962</v>
@@ -4269,46 +4269,46 @@
         <v>2</v>
       </c>
       <c r="D69" s="1">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E69" s="2">
-        <v>0.7061979725202865</v>
+        <v>0.7212216865625958</v>
       </c>
       <c r="F69" s="2">
-        <v>0.6913538250570118</v>
+        <v>0.7050154264312666</v>
       </c>
       <c r="G69" s="3">
-        <v>1.484414746327467</v>
+        <v>1.62062601313292</v>
       </c>
       <c r="H69">
         <v>2</v>
       </c>
       <c r="I69" s="1">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="J69" s="2">
-        <v>0.5259134040125775</v>
+        <v>0.5259134040125777</v>
       </c>
       <c r="K69" s="2">
         <v>0.5315285559222972</v>
       </c>
       <c r="L69" s="3">
-        <v>-0.5615151909719729</v>
+        <v>-0.5615151909719507</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69" s="1">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="O69" s="2">
-        <v>0.8864825410279955</v>
+        <v>0.8864825410279954</v>
       </c>
       <c r="P69" s="2">
         <v>0.8589431775079349</v>
       </c>
       <c r="Q69" s="3">
-        <v>2.753936352006059</v>
+        <v>2.753936352006048</v>
       </c>
     </row>
     <row r="70" spans="1:17">
@@ -4322,37 +4322,37 @@
         <v>11</v>
       </c>
       <c r="D70" s="1">
-        <v>2863</v>
+        <v>2867</v>
       </c>
       <c r="E70" s="2">
-        <v>0.8964080781839797</v>
+        <v>0.8977507075621701</v>
       </c>
       <c r="F70" s="2">
-        <v>0.9089425774522214</v>
+        <v>0.9097412475239556</v>
       </c>
       <c r="G70" s="3">
-        <v>-1.253449926824168</v>
+        <v>-1.199053996178545</v>
       </c>
       <c r="H70">
         <v>11</v>
       </c>
       <c r="I70" s="1">
-        <v>1406</v>
+        <v>1288</v>
       </c>
       <c r="J70" s="2">
-        <v>0.8802965256456955</v>
+        <v>0.8802965256456957</v>
       </c>
       <c r="K70" s="2">
         <v>0.8993585365914101</v>
       </c>
       <c r="L70" s="3">
-        <v>-1.906201094571458</v>
+        <v>-1.906201094571436</v>
       </c>
       <c r="M70">
         <v>11</v>
       </c>
       <c r="N70" s="1">
-        <v>1457</v>
+        <v>1578</v>
       </c>
       <c r="O70" s="2">
         <v>0.9125196307222637</v>
@@ -4375,46 +4375,46 @@
         <v>2</v>
       </c>
       <c r="D71" s="1">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E71" s="2">
-        <v>0.8008252715334261</v>
+        <v>0.8047995151804165</v>
       </c>
       <c r="F71" s="2">
-        <v>0.9089425774522214</v>
+        <v>0.9097412475239556</v>
       </c>
       <c r="G71" s="3">
-        <v>-10.81173059187953</v>
+        <v>-10.49417323435391</v>
       </c>
       <c r="H71">
         <v>2</v>
       </c>
       <c r="I71" s="1">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="J71" s="2">
-        <v>0.753134347769541</v>
+        <v>0.7531343477695408</v>
       </c>
       <c r="K71" s="2">
         <v>0.8993585365914101</v>
       </c>
       <c r="L71" s="3">
-        <v>-14.6224188821869</v>
+        <v>-14.62241888218693</v>
       </c>
       <c r="M71">
         <v>2</v>
       </c>
       <c r="N71" s="1">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="O71" s="2">
-        <v>0.8485161952973113</v>
+        <v>0.8485161952973111</v>
       </c>
       <c r="P71" s="2">
         <v>0.9185266183130327</v>
       </c>
       <c r="Q71" s="3">
-        <v>-7.001042301572147</v>
+        <v>-7.001042301572157</v>
       </c>
     </row>
     <row r="72" spans="1:17">
@@ -4428,46 +4428,46 @@
         <v>12</v>
       </c>
       <c r="D72" s="1">
-        <v>3115</v>
+        <v>3113</v>
       </c>
       <c r="E72" s="2">
-        <v>0.9454178828737466</v>
+        <v>0.9450226810985008</v>
       </c>
       <c r="F72" s="2">
-        <v>0.9089425774522214</v>
+        <v>0.9097412475239556</v>
       </c>
       <c r="G72" s="3">
-        <v>3.647530542152522</v>
+        <v>3.528143357454527</v>
       </c>
       <c r="H72">
         <v>12</v>
       </c>
       <c r="I72" s="1">
-        <v>1565</v>
+        <v>1435</v>
       </c>
       <c r="J72" s="2">
-        <v>0.9501603041766975</v>
+        <v>0.9501603041766977</v>
       </c>
       <c r="K72" s="2">
         <v>0.8993585365914101</v>
       </c>
       <c r="L72" s="3">
-        <v>5.080176758528743</v>
+        <v>5.080176758528765</v>
       </c>
       <c r="M72">
         <v>12</v>
       </c>
       <c r="N72" s="1">
-        <v>1550</v>
+        <v>1679</v>
       </c>
       <c r="O72" s="2">
-        <v>0.9406754615707957</v>
+        <v>0.9406754615707958</v>
       </c>
       <c r="P72" s="2">
         <v>0.9185266183130327</v>
       </c>
       <c r="Q72" s="3">
-        <v>2.214884325776301</v>
+        <v>2.214884325776312</v>
       </c>
     </row>
     <row r="73" spans="1:17">
@@ -4484,34 +4484,34 @@
         <v>542</v>
       </c>
       <c r="E73" s="2">
-        <v>0.9069374057315234</v>
+        <v>0.907531045751634</v>
       </c>
       <c r="F73" s="2">
-        <v>0.9089425774522214</v>
+        <v>0.9097412475239556</v>
       </c>
       <c r="G73" s="3">
-        <v>-0.2005171720698029</v>
+        <v>-0.2210201772321563</v>
       </c>
       <c r="H73">
         <v>3</v>
       </c>
       <c r="I73" s="1">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="J73" s="2">
-        <v>0.899813725490196</v>
+        <v>0.8998137254901962</v>
       </c>
       <c r="K73" s="2">
         <v>0.8993585365914101</v>
       </c>
       <c r="L73" s="3">
-        <v>0.04551888987859298</v>
+        <v>0.04551888987861519</v>
       </c>
       <c r="M73">
         <v>3</v>
       </c>
       <c r="N73" s="1">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="O73" s="2">
         <v>0.9140610859728506</v>
@@ -57598,10 +57598,10 @@
         <v>8000</v>
       </c>
       <c r="F2">
-        <v>4006</v>
+        <v>4007</v>
       </c>
       <c r="G2" s="5">
-        <v>3994</v>
+        <v>3993</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -57621,10 +57621,10 @@
         <v>7650</v>
       </c>
       <c r="F3">
-        <v>4064</v>
+        <v>4070</v>
       </c>
       <c r="G3" s="5">
-        <v>3586</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -57644,10 +57644,10 @@
         <v>7700</v>
       </c>
       <c r="F4">
-        <v>1823</v>
+        <v>1830</v>
       </c>
       <c r="G4" s="5">
-        <v>5877</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -57667,10 +57667,10 @@
         <v>6800</v>
       </c>
       <c r="F5">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G5" s="5">
-        <v>6272</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -57736,10 +57736,10 @@
         <v>8000</v>
       </c>
       <c r="F8">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="G8" s="5">
-        <v>6168</v>
+        <v>6159</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -57759,10 +57759,10 @@
         <v>6400</v>
       </c>
       <c r="F9">
-        <v>5131</v>
+        <v>5135</v>
       </c>
       <c r="G9" s="5">
-        <v>1269</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -57782,10 +57782,10 @@
         <v>7700</v>
       </c>
       <c r="F10">
-        <v>4133</v>
+        <v>4132</v>
       </c>
       <c r="G10" s="5">
-        <v>3567</v>
+        <v>3568</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -57805,10 +57805,10 @@
         <v>5300</v>
       </c>
       <c r="F11">
-        <v>5110</v>
+        <v>5112</v>
       </c>
       <c r="G11" s="5">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -57828,10 +57828,10 @@
         <v>7750</v>
       </c>
       <c r="F12">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="G12" s="5">
-        <v>6131</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -57851,10 +57851,10 @@
         <v>8000</v>
       </c>
       <c r="F13">
-        <v>4096</v>
+        <v>4114</v>
       </c>
       <c r="G13" s="5">
-        <v>3904</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -57874,10 +57874,10 @@
         <v>8000</v>
       </c>
       <c r="F14">
-        <v>3115</v>
+        <v>3124</v>
       </c>
       <c r="G14" s="5">
-        <v>4885</v>
+        <v>4876</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -57897,10 +57897,10 @@
         <v>8000</v>
       </c>
       <c r="F15">
-        <v>5154</v>
+        <v>5156</v>
       </c>
       <c r="G15" s="5">
-        <v>2846</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -57920,10 +57920,10 @@
         <v>7700</v>
       </c>
       <c r="F16">
-        <v>4333</v>
+        <v>4334</v>
       </c>
       <c r="G16" s="5">
-        <v>3367</v>
+        <v>3366</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -57943,10 +57943,10 @@
         <v>8000</v>
       </c>
       <c r="F17">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="G17" s="5">
-        <v>5853</v>
+        <v>5851</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -57966,10 +57966,10 @@
         <v>9600</v>
       </c>
       <c r="F18">
-        <v>1552</v>
+        <v>1561</v>
       </c>
       <c r="G18" s="5">
-        <v>8048</v>
+        <v>8039</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -57989,10 +57989,10 @@
         <v>9600</v>
       </c>
       <c r="F19">
-        <v>4583</v>
+        <v>4595</v>
       </c>
       <c r="G19" s="5">
-        <v>5017</v>
+        <v>5005</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -58012,10 +58012,10 @@
         <v>9600</v>
       </c>
       <c r="F20">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="G20" s="5">
-        <v>7183</v>
+        <v>7181</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -58058,10 +58058,10 @@
         <v>8000</v>
       </c>
       <c r="F22">
-        <v>1918</v>
+        <v>1922</v>
       </c>
       <c r="G22" s="5">
-        <v>6082</v>
+        <v>6078</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -58081,10 +58081,10 @@
         <v>6750</v>
       </c>
       <c r="F23">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="G23" s="5">
-        <v>6428</v>
+        <v>6423</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -58104,10 +58104,10 @@
         <v>7700</v>
       </c>
       <c r="F24">
-        <v>3096</v>
+        <v>3093</v>
       </c>
       <c r="G24" s="5">
-        <v>4604</v>
+        <v>4607</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -58127,10 +58127,10 @@
         <v>8000</v>
       </c>
       <c r="F25">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G25" s="5">
-        <v>7815</v>
+        <v>7814</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -58150,10 +58150,10 @@
         <v>13350</v>
       </c>
       <c r="F26">
-        <v>5430</v>
+        <v>5431</v>
       </c>
       <c r="G26" s="5">
-        <v>7920</v>
+        <v>7919</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -58196,10 +58196,10 @@
         <v>9600</v>
       </c>
       <c r="F28">
-        <v>4695</v>
+        <v>4699</v>
       </c>
       <c r="G28" s="5">
-        <v>4905</v>
+        <v>4901</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -58232,7 +58232,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" style="6" customWidth="1"/>
@@ -58260,7 +58260,7 @@
         <v>115</v>
       </c>
       <c r="C2" s="6">
-        <v>501.5591931023519</v>
+        <v>507.3850170454548</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>40</v>
@@ -58274,7 +58274,7 @@
         <v>121</v>
       </c>
       <c r="C3" s="6">
-        <v>439.530612762238</v>
+        <v>431.8586076388883</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>36</v>
@@ -58282,13 +58282,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="6">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C4" s="6">
-        <v>2019.249991491841</v>
+        <v>444.0350255952385</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>36</v>
@@ -58296,13 +58296,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B5" s="6">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C5" s="6">
-        <v>1399.573670154844</v>
+        <v>2027.414290277778</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>36</v>
@@ -58310,13 +58310,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="B6" s="6">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C6" s="6">
-        <v>9600</v>
+        <v>1399.381603273809</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>36</v>
@@ -58324,10 +58324,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B7" s="6">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C7" s="6">
         <v>9600</v>
@@ -58338,27 +58338,27 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B8" s="6">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C8" s="6">
-        <v>8000</v>
+        <v>9600</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B9" s="6">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C9" s="6">
-        <v>7750</v>
+        <v>8000</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>40</v>
@@ -58366,15 +58366,29 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="6">
+        <v>152</v>
+      </c>
+      <c r="C10" s="6">
+        <v>7750</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B11" s="6">
         <v>155</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C11" s="6">
         <v>6800</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D11" s="6" t="s">
         <v>37</v>
       </c>
     </row>

--- a/Waterjet Efficiency Shiftwise.xlsx
+++ b/Waterjet Efficiency Shiftwise.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8855" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8847" uniqueCount="80">
   <si>
     <t>DATE</t>
   </si>
@@ -718,22 +718,22 @@
         <v>6</v>
       </c>
       <c r="D2" s="1">
-        <v>1244</v>
+        <v>1259</v>
       </c>
       <c r="E2" s="2">
-        <v>0.8533013385569703</v>
+        <v>0.84939271728015</v>
       </c>
       <c r="F2" s="2">
-        <v>0.8744496686743556</v>
+        <v>0.8748758910158874</v>
       </c>
       <c r="G2" s="3">
-        <v>-2.114833011738526</v>
+        <v>-2.548317373573739</v>
       </c>
       <c r="H2">
         <v>6</v>
       </c>
       <c r="I2" s="1">
-        <v>656</v>
+        <v>716</v>
       </c>
       <c r="J2" s="2">
         <v>0.8106730957701204</v>
@@ -748,7 +748,7 @@
         <v>4</v>
       </c>
       <c r="N2" s="1">
-        <v>588</v>
+        <v>543</v>
       </c>
       <c r="O2" s="2">
         <v>0.9065115482481895</v>
@@ -771,22 +771,22 @@
         <v>3</v>
       </c>
       <c r="D3" s="1">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E3" s="2">
-        <v>0.9316641260162603</v>
+        <v>0.9334555688214223</v>
       </c>
       <c r="F3" s="2">
-        <v>0.8744496686743556</v>
+        <v>0.8748758910158874</v>
       </c>
       <c r="G3" s="3">
-        <v>5.721445734190467</v>
+        <v>5.857967780553497</v>
       </c>
       <c r="H3">
         <v>3</v>
       </c>
       <c r="I3" s="1">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="J3" s="2">
         <v>0.9549528824833702</v>
@@ -801,16 +801,16 @@
         <v>3</v>
       </c>
       <c r="N3" s="1">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="O3" s="2">
-        <v>0.9119582551594746</v>
+        <v>0.9119582551594745</v>
       </c>
       <c r="P3" s="2">
         <v>0.8697857416341145</v>
       </c>
       <c r="Q3" s="3">
-        <v>4.217251352536011</v>
+        <v>4.217251352536</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -824,46 +824,46 @@
         <v>4</v>
       </c>
       <c r="D4" s="1">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="E4" s="2">
-        <v>0.5584273277439331</v>
+        <v>0.5616304095145965</v>
       </c>
       <c r="F4" s="2">
-        <v>0.8744496686743556</v>
+        <v>0.8748758910158874</v>
       </c>
       <c r="G4" s="3">
-        <v>-31.60223409304225</v>
+        <v>-31.32454815012908</v>
       </c>
       <c r="H4">
         <v>2</v>
       </c>
       <c r="I4" s="1">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="J4" s="2">
-        <v>0.6186088351324404</v>
+        <v>0.6186088351324402</v>
       </c>
       <c r="K4" s="2">
         <v>0.8800198420557523</v>
       </c>
       <c r="L4" s="3">
-        <v>-26.1411006923312</v>
+        <v>-26.14110069233121</v>
       </c>
       <c r="M4">
         <v>4</v>
       </c>
       <c r="N4" s="1">
-        <v>397</v>
+        <v>367</v>
       </c>
       <c r="O4" s="2">
-        <v>0.531491991423887</v>
+        <v>0.5314919914238869</v>
       </c>
       <c r="P4" s="2">
         <v>0.8697857416341145</v>
       </c>
       <c r="Q4" s="3">
-        <v>-33.82937502102274</v>
+        <v>-33.82937502102276</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -877,37 +877,37 @@
         <v>17</v>
       </c>
       <c r="D5" s="1">
-        <v>4377</v>
+        <v>4374</v>
       </c>
       <c r="E5" s="2">
-        <v>0.948070827959247</v>
+        <v>0.9473372393825916</v>
       </c>
       <c r="F5" s="2">
-        <v>0.8744496686743556</v>
+        <v>0.8748758910158874</v>
       </c>
       <c r="G5" s="3">
-        <v>7.362115928489144</v>
+        <v>7.246134836670426</v>
       </c>
       <c r="H5">
         <v>17</v>
       </c>
       <c r="I5" s="1">
-        <v>1986</v>
+        <v>2167</v>
       </c>
       <c r="J5" s="2">
-        <v>0.9385341764627286</v>
+        <v>0.9385341764627285</v>
       </c>
       <c r="K5" s="2">
         <v>0.8800198420557523</v>
       </c>
       <c r="L5" s="3">
-        <v>5.851433440697629</v>
+        <v>5.851433440697617</v>
       </c>
       <c r="M5">
         <v>17</v>
       </c>
       <c r="N5" s="1">
-        <v>2391</v>
+        <v>2207</v>
       </c>
       <c r="O5" s="2">
         <v>0.9561403023024546</v>
@@ -930,46 +930,46 @@
         <v>7</v>
       </c>
       <c r="D6" s="1">
-        <v>1621</v>
+        <v>1626</v>
       </c>
       <c r="E6" s="2">
-        <v>0.8615203595178088</v>
+        <v>0.8597175401801566</v>
       </c>
       <c r="F6" s="2">
-        <v>0.8378258964871993</v>
+        <v>0.8379308364375717</v>
       </c>
       <c r="G6" s="3">
-        <v>2.369446303060951</v>
+        <v>2.178670374258485</v>
       </c>
       <c r="H6">
         <v>7</v>
       </c>
       <c r="I6" s="1">
-        <v>776</v>
+        <v>847</v>
       </c>
       <c r="J6" s="2">
         <v>0.8395411981161869</v>
       </c>
       <c r="K6" s="2">
-        <v>0.8391880909312648</v>
+        <v>0.8391880909312647</v>
       </c>
       <c r="L6" s="3">
-        <v>0.03531071849220968</v>
+        <v>0.03531071849222078</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6" s="1">
-        <v>845</v>
+        <v>780</v>
       </c>
       <c r="O6" s="2">
-        <v>0.8827598102630443</v>
+        <v>0.8827598102630445</v>
       </c>
       <c r="P6" s="2">
         <v>0.8366698385455618</v>
       </c>
       <c r="Q6" s="3">
-        <v>4.608997171748253</v>
+        <v>4.608997171748275</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -983,28 +983,28 @@
         <v>18</v>
       </c>
       <c r="D7" s="1">
-        <v>4356</v>
+        <v>4349</v>
       </c>
       <c r="E7" s="2">
-        <v>0.9190045408616682</v>
+        <v>0.9194427520485838</v>
       </c>
       <c r="F7" s="2">
-        <v>0.8378258964871993</v>
+        <v>0.8379308364375717</v>
       </c>
       <c r="G7" s="3">
-        <v>8.117864437446887</v>
+        <v>8.151191561101212</v>
       </c>
       <c r="H7">
         <v>17</v>
       </c>
       <c r="I7" s="1">
-        <v>1957</v>
+        <v>2135</v>
       </c>
       <c r="J7" s="2">
-        <v>0.9248412315360934</v>
+        <v>0.9248412315360933</v>
       </c>
       <c r="K7" s="2">
-        <v>0.8391880909312648</v>
+        <v>0.8391880909312647</v>
       </c>
       <c r="L7" s="3">
         <v>8.565314060482866</v>
@@ -1013,7 +1013,7 @@
         <v>18</v>
       </c>
       <c r="N7" s="1">
-        <v>2399</v>
+        <v>2214</v>
       </c>
       <c r="O7" s="2">
         <v>0.9142970875366448</v>
@@ -1036,28 +1036,28 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E8" s="2">
-        <v>0.6043295325986093</v>
+        <v>0.6097984243064334</v>
       </c>
       <c r="F8" s="2">
-        <v>0.8378258964871993</v>
+        <v>0.8379308364375717</v>
       </c>
       <c r="G8" s="3">
-        <v>-23.349636388859</v>
+        <v>-22.81324121311383</v>
       </c>
       <c r="H8">
         <v>2</v>
       </c>
       <c r="I8" s="1">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="J8" s="2">
-        <v>0.6755228730939089</v>
+        <v>0.6755228730939088</v>
       </c>
       <c r="K8" s="2">
-        <v>0.8391880909312648</v>
+        <v>0.8391880909312647</v>
       </c>
       <c r="L8" s="3">
         <v>-16.36652178373559</v>
@@ -1066,7 +1066,7 @@
         <v>2</v>
       </c>
       <c r="N8" s="1">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="O8" s="2">
         <v>0.5442542070969859</v>
@@ -1089,37 +1089,37 @@
         <v>2</v>
       </c>
       <c r="D9" s="1">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E9" s="2">
-        <v>0.3726340208233985</v>
+        <v>0.3733987698043492</v>
       </c>
       <c r="F9" s="2">
-        <v>0.8378258964871993</v>
+        <v>0.8379308364375717</v>
       </c>
       <c r="G9" s="3">
-        <v>-46.51918756638008</v>
+        <v>-46.45320666332226</v>
       </c>
       <c r="H9">
         <v>2</v>
       </c>
       <c r="I9" s="1">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="J9" s="2">
         <v>0.3825757575757576</v>
       </c>
       <c r="K9" s="2">
-        <v>0.8391880909312648</v>
+        <v>0.8391880909312647</v>
       </c>
       <c r="L9" s="3">
-        <v>-45.66123333555072</v>
+        <v>-45.6612333355507</v>
       </c>
       <c r="M9">
         <v>2</v>
       </c>
       <c r="N9" s="1">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="O9" s="2">
         <v>0.3642217820329408</v>
@@ -1142,43 +1142,43 @@
         <v>8</v>
       </c>
       <c r="D10" s="1">
-        <v>2028</v>
+        <v>2040</v>
       </c>
       <c r="E10" s="2">
-        <v>0.867717908598996</v>
+        <v>0.8730495920403999</v>
       </c>
       <c r="F10" s="2">
-        <v>0.8877963428508072</v>
+        <v>0.8892476183952933</v>
       </c>
       <c r="G10" s="3">
-        <v>-2.007843425181122</v>
+        <v>-1.619802635489342</v>
       </c>
       <c r="H10">
         <v>8</v>
       </c>
       <c r="I10" s="1">
-        <v>1004</v>
+        <v>1095</v>
       </c>
       <c r="J10" s="2">
         <v>0.937029793337245</v>
       </c>
       <c r="K10" s="2">
-        <v>0.9067056666109793</v>
+        <v>0.9067056666109792</v>
       </c>
       <c r="L10" s="3">
-        <v>3.032412672626572</v>
+        <v>3.032412672626583</v>
       </c>
       <c r="M10">
         <v>8</v>
       </c>
       <c r="N10" s="1">
-        <v>1024</v>
+        <v>945</v>
       </c>
       <c r="O10" s="2">
-        <v>0.8090693907435546</v>
+        <v>0.8090693907435547</v>
       </c>
       <c r="P10" s="2">
-        <v>0.8718683147728951</v>
+        <v>0.8718683147728952</v>
       </c>
       <c r="Q10" s="3">
         <v>-6.279892402934051</v>
@@ -1195,46 +1195,46 @@
         <v>18</v>
       </c>
       <c r="D11" s="1">
-        <v>4382</v>
+        <v>4380</v>
       </c>
       <c r="E11" s="2">
-        <v>0.9245344703748343</v>
+        <v>0.9259057303431975</v>
       </c>
       <c r="F11" s="2">
-        <v>0.8877963428508072</v>
+        <v>0.8892476183952933</v>
       </c>
       <c r="G11" s="3">
-        <v>3.673812752402705</v>
+        <v>3.665811194790414</v>
       </c>
       <c r="H11">
         <v>17</v>
       </c>
       <c r="I11" s="1">
-        <v>1995</v>
+        <v>2176</v>
       </c>
       <c r="J11" s="2">
-        <v>0.9427987696637027</v>
+        <v>0.9427987696637025</v>
       </c>
       <c r="K11" s="2">
-        <v>0.9067056666109793</v>
+        <v>0.9067056666109792</v>
       </c>
       <c r="L11" s="3">
-        <v>3.60931030527234</v>
+        <v>3.609310305272329</v>
       </c>
       <c r="M11">
         <v>18</v>
       </c>
       <c r="N11" s="1">
-        <v>2387</v>
+        <v>2203</v>
       </c>
       <c r="O11" s="2">
         <v>0.9098038051378817</v>
       </c>
       <c r="P11" s="2">
-        <v>0.8718683147728951</v>
+        <v>0.8718683147728952</v>
       </c>
       <c r="Q11" s="3">
-        <v>3.793549036498667</v>
+        <v>3.793549036498656</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1251,43 +1251,43 @@
         <v>145</v>
       </c>
       <c r="E12" s="2">
-        <v>0.5192243878584651</v>
+        <v>0.505867756937439</v>
       </c>
       <c r="F12" s="2">
-        <v>0.8877963428508072</v>
+        <v>0.8892476183952933</v>
       </c>
       <c r="G12" s="3">
-        <v>-36.85719549923421</v>
+        <v>-38.33798614578543</v>
       </c>
       <c r="H12">
         <v>2</v>
       </c>
       <c r="I12" s="1">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="J12" s="2">
-        <v>0.3890370246923867</v>
+        <v>0.3890370246923868</v>
       </c>
       <c r="K12" s="2">
-        <v>0.9067056666109793</v>
+        <v>0.9067056666109792</v>
       </c>
       <c r="L12" s="3">
-        <v>-51.76686419185926</v>
+        <v>-51.76686419185924</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
       <c r="N12" s="1">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="O12" s="2">
-        <v>0.7397435897435898</v>
+        <v>0.7397435897435897</v>
       </c>
       <c r="P12" s="2">
-        <v>0.8718683147728951</v>
+        <v>0.8718683147728952</v>
       </c>
       <c r="Q12" s="3">
-        <v>-13.21247250293053</v>
+        <v>-13.21247250293055</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1301,46 +1301,46 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E13" s="2">
-        <v>0.8215704975361628</v>
+        <v>0.8199112284949194</v>
       </c>
       <c r="F13" s="2">
-        <v>0.8877963428508072</v>
+        <v>0.8892476183952933</v>
       </c>
       <c r="G13" s="3">
-        <v>-6.622584531464437</v>
+        <v>-6.933638990037394</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="I13" s="1">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="J13" s="2">
-        <v>0.7999999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="K13" s="2">
-        <v>0.9067056666109793</v>
+        <v>0.9067056666109792</v>
       </c>
       <c r="L13" s="3">
-        <v>-10.67056666109794</v>
+        <v>-10.67056666109791</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13" s="1">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="O13" s="2">
         <v>0.839822456989839</v>
       </c>
       <c r="P13" s="2">
-        <v>0.8718683147728951</v>
+        <v>0.8718683147728952</v>
       </c>
       <c r="Q13" s="3">
-        <v>-3.204585778305602</v>
+        <v>-3.204585778305613</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1354,28 +1354,28 @@
         <v>9</v>
       </c>
       <c r="D14" s="1">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="E14" s="2">
-        <v>0.8334285107518109</v>
+        <v>0.8308405718627611</v>
       </c>
       <c r="F14" s="2">
-        <v>0.8820441438344169</v>
+        <v>0.8832310106190311</v>
       </c>
       <c r="G14" s="3">
-        <v>-4.861563308260597</v>
+        <v>-5.239043875627003</v>
       </c>
       <c r="H14">
         <v>9</v>
       </c>
       <c r="I14" s="1">
-        <v>950</v>
+        <v>1036</v>
       </c>
       <c r="J14" s="2">
-        <v>0.8014056257163362</v>
+        <v>0.8014056257163361</v>
       </c>
       <c r="K14" s="2">
-        <v>0.8974165249242003</v>
+        <v>0.8974165249242002</v>
       </c>
       <c r="L14" s="3">
         <v>-9.601089920786411</v>
@@ -1384,16 +1384,16 @@
         <v>8</v>
       </c>
       <c r="N14" s="1">
-        <v>1093</v>
+        <v>1009</v>
       </c>
       <c r="O14" s="2">
-        <v>0.8634130196031231</v>
+        <v>0.8634130196031233</v>
       </c>
       <c r="P14" s="2">
-        <v>0.8689401163742245</v>
+        <v>0.8689401163742244</v>
       </c>
       <c r="Q14" s="3">
-        <v>-0.5527096771101414</v>
+        <v>-0.5527096771101081</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1407,43 +1407,43 @@
         <v>18</v>
       </c>
       <c r="D15" s="1">
-        <v>4502</v>
+        <v>4513</v>
       </c>
       <c r="E15" s="2">
-        <v>0.9294131381574559</v>
+        <v>0.9317578224731498</v>
       </c>
       <c r="F15" s="2">
-        <v>0.8820441438344169</v>
+        <v>0.8832310106190311</v>
       </c>
       <c r="G15" s="3">
-        <v>4.736899432303899</v>
+        <v>4.852681185411867</v>
       </c>
       <c r="H15">
         <v>18</v>
       </c>
       <c r="I15" s="1">
-        <v>2131</v>
+        <v>2325</v>
       </c>
       <c r="J15" s="2">
         <v>0.9598940342614757</v>
       </c>
       <c r="K15" s="2">
-        <v>0.8974165249242003</v>
+        <v>0.8974165249242002</v>
       </c>
       <c r="L15" s="3">
-        <v>6.247750933727536</v>
+        <v>6.247750933727547</v>
       </c>
       <c r="M15">
         <v>18</v>
       </c>
       <c r="N15" s="1">
-        <v>2371</v>
+        <v>2188</v>
       </c>
       <c r="O15" s="2">
-        <v>0.9036216106848237</v>
+        <v>0.9036216106848236</v>
       </c>
       <c r="P15" s="2">
-        <v>0.8689401163742245</v>
+        <v>0.8689401163742244</v>
       </c>
       <c r="Q15" s="3">
         <v>3.468149431059919</v>
@@ -1460,16 +1460,16 @@
         <v>1</v>
       </c>
       <c r="D16" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E16" s="2">
-        <v>0.2833333333333334</v>
+        <v>0.2833333333333333</v>
       </c>
       <c r="F16" s="2">
-        <v>0.8820441438344169</v>
+        <v>0.8832310106190311</v>
       </c>
       <c r="G16" s="3">
-        <v>-59.87108105010834</v>
+        <v>-59.98976772856979</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -1490,13 +1490,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O16" s="2">
-        <v>0.2833333333333334</v>
+        <v>0.2833333333333333</v>
       </c>
       <c r="P16" s="2">
-        <v>0.8689401163742245</v>
+        <v>0.8689401163742244</v>
       </c>
       <c r="Q16" s="3">
         <v>-58.56067830408911</v>
@@ -1516,43 +1516,43 @@
         <v>274</v>
       </c>
       <c r="E17" s="2">
-        <v>0.7501112700683514</v>
+        <v>0.7499861607157744</v>
       </c>
       <c r="F17" s="2">
-        <v>0.8820441438344169</v>
+        <v>0.8832310106190311</v>
       </c>
       <c r="G17" s="3">
-        <v>-13.19328737660654</v>
+        <v>-13.32448499032567</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="I17" s="1">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="J17" s="2">
-        <v>0.7484848484848484</v>
+        <v>0.7484848484848485</v>
       </c>
       <c r="K17" s="2">
-        <v>0.8974165249242003</v>
+        <v>0.8974165249242002</v>
       </c>
       <c r="L17" s="3">
-        <v>-14.89316764393519</v>
+        <v>-14.89316764393517</v>
       </c>
       <c r="M17">
         <v>1</v>
       </c>
       <c r="N17" s="1">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="O17" s="2">
         <v>0.7514874729467003</v>
       </c>
       <c r="P17" s="2">
-        <v>0.8689401163742245</v>
+        <v>0.8689401163742244</v>
       </c>
       <c r="Q17" s="3">
-        <v>-11.74526434275243</v>
+        <v>-11.74526434275242</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1566,37 +1566,37 @@
         <v>10</v>
       </c>
       <c r="D18" s="1">
-        <v>2244</v>
+        <v>2263</v>
       </c>
       <c r="E18" s="2">
-        <v>0.8211863127057473</v>
+        <v>0.8242827196385248</v>
       </c>
       <c r="F18" s="2">
-        <v>0.8830321953349407</v>
+        <v>0.8854281330823822</v>
       </c>
       <c r="G18" s="3">
-        <v>-6.184588262919344</v>
+        <v>-6.114541344385738</v>
       </c>
       <c r="H18">
         <v>10</v>
       </c>
       <c r="I18" s="1">
-        <v>1144</v>
+        <v>1248</v>
       </c>
       <c r="J18" s="2">
-        <v>0.8592265267111894</v>
+        <v>0.8592265267111892</v>
       </c>
       <c r="K18" s="2">
         <v>0.9142711014561837</v>
       </c>
       <c r="L18" s="3">
-        <v>-5.504457474499436</v>
+        <v>-5.504457474499458</v>
       </c>
       <c r="M18">
         <v>9</v>
       </c>
       <c r="N18" s="1">
-        <v>1099</v>
+        <v>1015</v>
       </c>
       <c r="O18" s="2">
         <v>0.7850218886804252</v>
@@ -1622,19 +1622,19 @@
         <v>4584</v>
       </c>
       <c r="E19" s="2">
-        <v>0.9463879239690844</v>
+        <v>0.9464569374360094</v>
       </c>
       <c r="F19" s="2">
-        <v>0.8830321953349407</v>
+        <v>0.8854281330823822</v>
       </c>
       <c r="G19" s="3">
-        <v>6.335572863414374</v>
+        <v>6.102880435362723</v>
       </c>
       <c r="H19">
         <v>18</v>
       </c>
       <c r="I19" s="1">
-        <v>2103</v>
+        <v>2294</v>
       </c>
       <c r="J19" s="2">
         <v>0.9472850990391087</v>
@@ -1649,16 +1649,16 @@
         <v>18</v>
       </c>
       <c r="N19" s="1">
-        <v>2481</v>
+        <v>2290</v>
       </c>
       <c r="O19" s="2">
-        <v>0.9456287758329101</v>
+        <v>0.9456287758329098</v>
       </c>
       <c r="P19" s="2">
         <v>0.8567540311007951</v>
       </c>
       <c r="Q19" s="3">
-        <v>8.887474473211498</v>
+        <v>8.887474473211476</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1672,16 +1672,16 @@
         <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2">
         <v>0.1856314882065955</v>
       </c>
       <c r="F20" s="2">
-        <v>0.8830321953349407</v>
+        <v>0.8854281330823822</v>
       </c>
       <c r="G20" s="3">
-        <v>-69.74007071283452</v>
+        <v>-69.97966448757866</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1702,7 +1702,7 @@
         <v>1</v>
       </c>
       <c r="N20" s="1">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="O20" s="2">
         <v>0.1856314882065955</v>
@@ -1725,37 +1725,37 @@
         <v>10</v>
       </c>
       <c r="D21" s="1">
-        <v>2567</v>
+        <v>2575</v>
       </c>
       <c r="E21" s="2">
-        <v>0.8835069171342177</v>
+        <v>0.8864505493457829</v>
       </c>
       <c r="F21" s="2">
-        <v>0.900363951394849</v>
+        <v>0.900596320229565</v>
       </c>
       <c r="G21" s="3">
-        <v>-1.685703426063134</v>
+        <v>-1.414577088378211</v>
       </c>
       <c r="H21">
         <v>10</v>
       </c>
       <c r="I21" s="1">
-        <v>1227</v>
+        <v>1339</v>
       </c>
       <c r="J21" s="2">
         <v>0.9217741358845654</v>
       </c>
       <c r="K21" s="2">
-        <v>0.9033915164078745</v>
+        <v>0.9033915164078746</v>
       </c>
       <c r="L21" s="3">
-        <v>1.838261947669084</v>
+        <v>1.838261947669073</v>
       </c>
       <c r="M21">
         <v>10</v>
       </c>
       <c r="N21" s="1">
-        <v>1339</v>
+        <v>1236</v>
       </c>
       <c r="O21" s="2">
         <v>0.8511269628070005</v>
@@ -1778,46 +1778,46 @@
         <v>18</v>
       </c>
       <c r="D22" s="1">
-        <v>4325</v>
+        <v>4311</v>
       </c>
       <c r="E22" s="2">
-        <v>0.9123725801641929</v>
+        <v>0.911121537870012</v>
       </c>
       <c r="F22" s="2">
-        <v>0.900363951394849</v>
+        <v>0.900596320229565</v>
       </c>
       <c r="G22" s="3">
-        <v>1.200862876934383</v>
+        <v>1.0525217640447</v>
       </c>
       <c r="H22">
         <v>17</v>
       </c>
       <c r="I22" s="1">
-        <v>1896</v>
+        <v>2069</v>
       </c>
       <c r="J22" s="2">
-        <v>0.8957133395476624</v>
+        <v>0.8957133395476622</v>
       </c>
       <c r="K22" s="2">
-        <v>0.9033915164078745</v>
+        <v>0.9033915164078746</v>
       </c>
       <c r="L22" s="3">
-        <v>-0.7678176860212105</v>
+        <v>-0.7678176860212438</v>
       </c>
       <c r="M22">
         <v>18</v>
       </c>
       <c r="N22" s="1">
-        <v>2429</v>
+        <v>2242</v>
       </c>
       <c r="O22" s="2">
-        <v>0.9258147661870108</v>
+        <v>0.9258147661870106</v>
       </c>
       <c r="P22" s="2">
         <v>0.8978135972482332</v>
       </c>
       <c r="Q22" s="3">
-        <v>2.800116893877758</v>
+        <v>2.800116893877747</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -1831,31 +1831,31 @@
         <v>1</v>
       </c>
       <c r="D23" s="1">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E23" s="2">
-        <v>0.8090685038929034</v>
+        <v>0.8090685038929032</v>
       </c>
       <c r="F23" s="2">
-        <v>0.900363951394849</v>
+        <v>0.900596320229565</v>
       </c>
       <c r="G23" s="3">
-        <v>-9.129544750194562</v>
+        <v>-9.152781633666185</v>
       </c>
       <c r="H23">
         <v>1</v>
       </c>
       <c r="I23" s="1">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J23" s="2">
-        <v>0.8090685038929034</v>
+        <v>0.8090685038929032</v>
       </c>
       <c r="K23" s="2">
-        <v>0.9033915164078745</v>
+        <v>0.9033915164078746</v>
       </c>
       <c r="L23" s="3">
-        <v>-9.43230125149711</v>
+        <v>-9.432301251497144</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -1887,43 +1887,43 @@
         <v>2666</v>
       </c>
       <c r="E24" s="2">
-        <v>0.9177074047856255</v>
+        <v>0.9178438558452716</v>
       </c>
       <c r="F24" s="2">
-        <v>0.897420995390633</v>
+        <v>0.8976433816886573</v>
       </c>
       <c r="G24" s="3">
-        <v>2.028640939499249</v>
+        <v>2.02004741566143</v>
       </c>
       <c r="H24">
         <v>10</v>
       </c>
       <c r="I24" s="1">
-        <v>1224</v>
+        <v>1336</v>
       </c>
       <c r="J24" s="2">
         <v>0.9194812685610232</v>
       </c>
       <c r="K24" s="2">
-        <v>0.9003120172649496</v>
+        <v>0.9003120172649495</v>
       </c>
       <c r="L24" s="3">
-        <v>1.916925129607361</v>
+        <v>1.916925129607372</v>
       </c>
       <c r="M24">
         <v>10</v>
       </c>
       <c r="N24" s="1">
-        <v>1442</v>
+        <v>1331</v>
       </c>
       <c r="O24" s="2">
-        <v>0.91620644312952</v>
+        <v>0.9162064431295202</v>
       </c>
       <c r="P24" s="2">
-        <v>0.8949747461123654</v>
+        <v>0.8949747461123653</v>
       </c>
       <c r="Q24" s="3">
-        <v>2.123169701715466</v>
+        <v>2.123169701715488</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -1937,28 +1937,28 @@
         <v>17</v>
       </c>
       <c r="D25" s="1">
-        <v>4078</v>
+        <v>4079</v>
       </c>
       <c r="E25" s="2">
-        <v>0.8827683711099118</v>
+        <v>0.8829938672288915</v>
       </c>
       <c r="F25" s="2">
-        <v>0.897420995390633</v>
+        <v>0.8976433816886573</v>
       </c>
       <c r="G25" s="3">
-        <v>-1.465262428072123</v>
+        <v>-1.464951445976581</v>
       </c>
       <c r="H25">
         <v>17</v>
       </c>
       <c r="I25" s="1">
-        <v>1875</v>
+        <v>2046</v>
       </c>
       <c r="J25" s="2">
-        <v>0.8856998206566475</v>
+        <v>0.8856998206566474</v>
       </c>
       <c r="K25" s="2">
-        <v>0.9003120172649496</v>
+        <v>0.9003120172649495</v>
       </c>
       <c r="L25" s="3">
         <v>-1.461219660830204</v>
@@ -1967,16 +1967,16 @@
         <v>17</v>
       </c>
       <c r="N25" s="1">
-        <v>2202</v>
+        <v>2033</v>
       </c>
       <c r="O25" s="2">
         <v>0.8802879138011356</v>
       </c>
       <c r="P25" s="2">
-        <v>0.8949747461123654</v>
+        <v>0.8949747461123653</v>
       </c>
       <c r="Q25" s="3">
-        <v>-1.46868323112298</v>
+        <v>-1.468683231122969</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -1990,46 +1990,46 @@
         <v>1</v>
       </c>
       <c r="D26" s="1">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E26" s="2">
-        <v>0.9434072704867532</v>
+        <v>0.9448668398760819</v>
       </c>
       <c r="F26" s="2">
-        <v>0.897420995390633</v>
+        <v>0.8976433816886573</v>
       </c>
       <c r="G26" s="3">
-        <v>4.598627509612019</v>
+        <v>4.722345818742458</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26" s="1">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J26" s="2">
-        <v>0.9623816725480314</v>
+        <v>0.962381672548031</v>
       </c>
       <c r="K26" s="2">
-        <v>0.9003120172649496</v>
+        <v>0.9003120172649495</v>
       </c>
       <c r="L26" s="3">
-        <v>6.206965528308183</v>
+        <v>6.20696552830815</v>
       </c>
       <c r="M26">
         <v>1</v>
       </c>
       <c r="N26" s="1">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="O26" s="2">
-        <v>0.927352007204133</v>
+        <v>0.9273520072041328</v>
       </c>
       <c r="P26" s="2">
-        <v>0.8949747461123654</v>
+        <v>0.8949747461123653</v>
       </c>
       <c r="Q26" s="3">
-        <v>3.237726109176764</v>
+        <v>3.237726109176753</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -2043,43 +2043,43 @@
         <v>10</v>
       </c>
       <c r="D27" s="1">
-        <v>2559</v>
+        <v>2553</v>
       </c>
       <c r="E27" s="2">
-        <v>0.8808554218446855</v>
+        <v>0.8786414348589903</v>
       </c>
       <c r="F27" s="2">
-        <v>0.9107816193810581</v>
+        <v>0.9089816498597452</v>
       </c>
       <c r="G27" s="3">
-        <v>-2.99261975363726</v>
+        <v>-3.03402150007549</v>
       </c>
       <c r="H27">
         <v>10</v>
       </c>
       <c r="I27" s="1">
-        <v>1135</v>
+        <v>1238</v>
       </c>
       <c r="J27" s="2">
-        <v>0.8520735910306463</v>
+        <v>0.8520735910306462</v>
       </c>
       <c r="K27" s="2">
         <v>0.8873820156039891</v>
       </c>
       <c r="L27" s="3">
-        <v>-3.530842457334282</v>
+        <v>-3.530842457334293</v>
       </c>
       <c r="M27">
         <v>10</v>
       </c>
       <c r="N27" s="1">
-        <v>1424</v>
+        <v>1315</v>
       </c>
       <c r="O27" s="2">
-        <v>0.9052092786873344</v>
+        <v>0.9052092786873343</v>
       </c>
       <c r="P27" s="2">
-        <v>0.9305812841155012</v>
+        <v>0.9305812841155011</v>
       </c>
       <c r="Q27" s="3">
         <v>-2.537200542816687</v>
@@ -2096,22 +2096,22 @@
         <v>17</v>
       </c>
       <c r="D28" s="1">
-        <v>4290</v>
+        <v>4283</v>
       </c>
       <c r="E28" s="2">
-        <v>0.9287760963202814</v>
+        <v>0.927226114564215</v>
       </c>
       <c r="F28" s="2">
-        <v>0.9107816193810581</v>
+        <v>0.9089816498597452</v>
       </c>
       <c r="G28" s="3">
-        <v>1.799447693922329</v>
+        <v>1.824446470446983</v>
       </c>
       <c r="H28">
         <v>17</v>
       </c>
       <c r="I28" s="1">
-        <v>1924</v>
+        <v>2098</v>
       </c>
       <c r="J28" s="2">
         <v>0.9086263334914172</v>
@@ -2126,16 +2126,16 @@
         <v>17</v>
       </c>
       <c r="N28" s="1">
-        <v>2366</v>
+        <v>2184</v>
       </c>
       <c r="O28" s="2">
         <v>0.9458258956370127</v>
       </c>
       <c r="P28" s="2">
-        <v>0.9305812841155012</v>
+        <v>0.9305812841155011</v>
       </c>
       <c r="Q28" s="3">
-        <v>1.524461152151146</v>
+        <v>1.524461152151158</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2152,43 +2152,43 @@
         <v>177</v>
       </c>
       <c r="E29" s="2">
-        <v>0.9308841651263093</v>
+        <v>0.9293370215736204</v>
       </c>
       <c r="F29" s="2">
-        <v>0.9107816193810581</v>
+        <v>0.9089816498597452</v>
       </c>
       <c r="G29" s="3">
-        <v>2.010254574525128</v>
+        <v>2.035537171387525</v>
       </c>
       <c r="H29">
         <v>1</v>
       </c>
       <c r="I29" s="1">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J29" s="2">
-        <v>0.9107712989413546</v>
+        <v>0.9107712989413542</v>
       </c>
       <c r="K29" s="2">
         <v>0.8873820156039891</v>
       </c>
       <c r="L29" s="3">
-        <v>2.338928333736545</v>
+        <v>2.338928333736512</v>
       </c>
       <c r="M29">
         <v>1</v>
       </c>
       <c r="N29" s="1">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="O29" s="2">
         <v>0.9479027442058864</v>
       </c>
       <c r="P29" s="2">
-        <v>0.9305812841155012</v>
+        <v>0.9305812841155011</v>
       </c>
       <c r="Q29" s="3">
-        <v>1.732146009038515</v>
+        <v>1.732146009038527</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2202,46 +2202,46 @@
         <v>10</v>
       </c>
       <c r="D30" s="1">
-        <v>2618</v>
+        <v>2624</v>
       </c>
       <c r="E30" s="2">
-        <v>0.9012379179557094</v>
+        <v>0.903181871350819</v>
       </c>
       <c r="F30" s="2">
-        <v>0.8892359879245889</v>
+        <v>0.8899624718866596</v>
       </c>
       <c r="G30" s="3">
-        <v>1.200193003112049</v>
+        <v>1.32193994641594</v>
       </c>
       <c r="H30">
         <v>10</v>
       </c>
       <c r="I30" s="1">
-        <v>1234</v>
+        <v>1346</v>
       </c>
       <c r="J30" s="2">
-        <v>0.9265093120921343</v>
+        <v>0.9265093120921341</v>
       </c>
       <c r="K30" s="2">
-        <v>0.8987016100814506</v>
+        <v>0.8987016100814504</v>
       </c>
       <c r="L30" s="3">
-        <v>2.780770201068372</v>
+        <v>2.780770201068361</v>
       </c>
       <c r="M30">
         <v>10</v>
       </c>
       <c r="N30" s="1">
-        <v>1385</v>
+        <v>1278</v>
       </c>
       <c r="O30" s="2">
         <v>0.8798544306095037</v>
       </c>
       <c r="P30" s="2">
-        <v>0.8812626321898005</v>
+        <v>0.8812626321898004</v>
       </c>
       <c r="Q30" s="3">
-        <v>-0.1408201580296753</v>
+        <v>-0.1408201580296642</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2255,28 +2255,28 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E31" s="2">
-        <v>0.6823299157526626</v>
+        <v>0.6968224669941409</v>
       </c>
       <c r="F31" s="2">
-        <v>0.8892359879245889</v>
+        <v>0.8899624718866596</v>
       </c>
       <c r="G31" s="3">
-        <v>-20.69060721719264</v>
+        <v>-19.31400048925187</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31" s="1">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="J31" s="2">
-        <v>0.8707330818918804</v>
+        <v>0.8707330818918803</v>
       </c>
       <c r="K31" s="2">
-        <v>0.8987016100814506</v>
+        <v>0.8987016100814504</v>
       </c>
       <c r="L31" s="3">
         <v>-2.796852818957019</v>
@@ -2285,16 +2285,16 @@
         <v>1</v>
       </c>
       <c r="N31" s="1">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="O31" s="2">
-        <v>0.5229118520964013</v>
+        <v>0.5229118520964015</v>
       </c>
       <c r="P31" s="2">
-        <v>0.8812626321898005</v>
+        <v>0.8812626321898004</v>
       </c>
       <c r="Q31" s="3">
-        <v>-35.83507800933992</v>
+        <v>-35.8350780093399</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2308,46 +2308,46 @@
         <v>16</v>
       </c>
       <c r="D32" s="1">
-        <v>3820</v>
+        <v>3809</v>
       </c>
       <c r="E32" s="2">
-        <v>0.9042387895378126</v>
+        <v>0.9037525403789572</v>
       </c>
       <c r="F32" s="2">
-        <v>0.8892359879245889</v>
+        <v>0.8899624718866596</v>
       </c>
       <c r="G32" s="3">
-        <v>1.500280161322365</v>
+        <v>1.379006849229769</v>
       </c>
       <c r="H32">
         <v>15</v>
       </c>
       <c r="I32" s="1">
-        <v>1687</v>
+        <v>1841</v>
       </c>
       <c r="J32" s="2">
-        <v>0.8977420850179435</v>
+        <v>0.8977420850179436</v>
       </c>
       <c r="K32" s="2">
-        <v>0.8987016100814506</v>
+        <v>0.8987016100814504</v>
       </c>
       <c r="L32" s="3">
-        <v>-0.09595250635070496</v>
+        <v>-0.09595250635068275</v>
       </c>
       <c r="M32">
         <v>16</v>
       </c>
       <c r="N32" s="1">
-        <v>2132</v>
+        <v>1968</v>
       </c>
       <c r="O32" s="2">
         <v>0.9094468685168369</v>
       </c>
       <c r="P32" s="2">
-        <v>0.8812626321898005</v>
+        <v>0.8812626321898004</v>
       </c>
       <c r="Q32" s="3">
-        <v>2.818423632703637</v>
+        <v>2.818423632703648</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2361,43 +2361,43 @@
         <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E33" s="2">
-        <v>0.8076977698295813</v>
+        <v>0.7991594806011983</v>
       </c>
       <c r="F33" s="2">
-        <v>0.8892359879245889</v>
+        <v>0.8899624718866596</v>
       </c>
       <c r="G33" s="3">
-        <v>-8.15382180950076</v>
+        <v>-9.080299128546121</v>
       </c>
       <c r="H33">
         <v>2</v>
       </c>
       <c r="I33" s="1">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="J33" s="2">
         <v>0.7246278209088127</v>
       </c>
       <c r="K33" s="2">
-        <v>0.8987016100814506</v>
+        <v>0.8987016100814504</v>
       </c>
       <c r="L33" s="3">
-        <v>-17.40737891726378</v>
+        <v>-17.40737891726377</v>
       </c>
       <c r="M33">
         <v>1</v>
       </c>
       <c r="N33" s="1">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="O33" s="2">
-        <v>0.9491871652684961</v>
+        <v>0.949187165268496</v>
       </c>
       <c r="P33" s="2">
-        <v>0.8812626321898005</v>
+        <v>0.8812626321898004</v>
       </c>
       <c r="Q33" s="3">
         <v>6.792453307869561</v>
@@ -2414,37 +2414,37 @@
         <v>11</v>
       </c>
       <c r="D34" s="1">
-        <v>2850</v>
+        <v>2846</v>
       </c>
       <c r="E34" s="2">
-        <v>0.9036828703703704</v>
+        <v>0.9026263386372083</v>
       </c>
       <c r="F34" s="2">
-        <v>0.8987230663251737</v>
+        <v>0.8989994739016479</v>
       </c>
       <c r="G34" s="3">
-        <v>0.4959804045196692</v>
+        <v>0.3626864735560398</v>
       </c>
       <c r="H34">
         <v>11</v>
       </c>
       <c r="I34" s="1">
-        <v>1286</v>
+        <v>1403</v>
       </c>
       <c r="J34" s="2">
-        <v>0.8899479578392623</v>
+        <v>0.8899479578392622</v>
       </c>
       <c r="K34" s="2">
-        <v>0.9023163648193397</v>
+        <v>0.9023163648193399</v>
       </c>
       <c r="L34" s="3">
-        <v>-1.236840698007746</v>
+        <v>-1.236840698007768</v>
       </c>
       <c r="M34">
         <v>11</v>
       </c>
       <c r="N34" s="1">
-        <v>1563</v>
+        <v>1443</v>
       </c>
       <c r="O34" s="2">
         <v>0.9153047194351542</v>
@@ -2467,37 +2467,37 @@
         <v>1</v>
       </c>
       <c r="D35" s="1">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E35" s="2">
-        <v>0.9146836750914006</v>
+        <v>0.9134381117213735</v>
       </c>
       <c r="F35" s="2">
-        <v>0.8987230663251737</v>
+        <v>0.8989994739016479</v>
       </c>
       <c r="G35" s="3">
-        <v>1.596060876622685</v>
+        <v>1.443863781972554</v>
       </c>
       <c r="H35">
         <v>1</v>
       </c>
       <c r="I35" s="1">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="J35" s="2">
-        <v>0.898491351281051</v>
+        <v>0.8984913512810507</v>
       </c>
       <c r="K35" s="2">
-        <v>0.9023163648193397</v>
+        <v>0.9023163648193399</v>
       </c>
       <c r="L35" s="3">
-        <v>-0.3825013538288791</v>
+        <v>-0.3825013538289124</v>
       </c>
       <c r="M35">
         <v>1</v>
       </c>
       <c r="N35" s="1">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="O35" s="2">
         <v>0.9283848721616962</v>
@@ -2520,37 +2520,37 @@
         <v>14</v>
       </c>
       <c r="D36" s="1">
-        <v>3457</v>
+        <v>3463</v>
       </c>
       <c r="E36" s="2">
-        <v>0.8920566960882409</v>
+        <v>0.893674513558197</v>
       </c>
       <c r="F36" s="2">
-        <v>0.8987230663251737</v>
+        <v>0.8989994739016479</v>
       </c>
       <c r="G36" s="3">
-        <v>-0.6666370236932839</v>
+        <v>-0.5324960343450869</v>
       </c>
       <c r="H36">
         <v>14</v>
       </c>
       <c r="I36" s="1">
-        <v>1622</v>
+        <v>1769</v>
       </c>
       <c r="J36" s="2">
-        <v>0.9130883231976714</v>
+        <v>0.9130883231976713</v>
       </c>
       <c r="K36" s="2">
-        <v>0.9023163648193397</v>
+        <v>0.9023163648193399</v>
       </c>
       <c r="L36" s="3">
-        <v>1.077195837833167</v>
+        <v>1.077195837833145</v>
       </c>
       <c r="M36">
         <v>14</v>
       </c>
       <c r="N36" s="1">
-        <v>1835</v>
+        <v>1694</v>
       </c>
       <c r="O36" s="2">
         <v>0.8742607039187227</v>
@@ -2576,34 +2576,34 @@
         <v>348</v>
       </c>
       <c r="E37" s="2">
-        <v>0.9101328946025917</v>
+        <v>0.9092608646327653</v>
       </c>
       <c r="F37" s="2">
-        <v>0.8987230663251737</v>
+        <v>0.8989994739016479</v>
       </c>
       <c r="G37" s="3">
-        <v>1.140982827741799</v>
+        <v>1.026139073111743</v>
       </c>
       <c r="H37">
         <v>2</v>
       </c>
       <c r="I37" s="1">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="J37" s="2">
-        <v>0.8987965049948522</v>
+        <v>0.8987965049948521</v>
       </c>
       <c r="K37" s="2">
-        <v>0.9023163648193397</v>
+        <v>0.9023163648193399</v>
       </c>
       <c r="L37" s="3">
-        <v>-0.3519859824487548</v>
+        <v>-0.351985982448777</v>
       </c>
       <c r="M37">
         <v>2</v>
       </c>
       <c r="N37" s="1">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="O37" s="2">
         <v>0.9197252242706788</v>
@@ -2626,46 +2626,46 @@
         <v>11</v>
       </c>
       <c r="D38" s="1">
-        <v>2700</v>
+        <v>2711</v>
       </c>
       <c r="E38" s="2">
-        <v>0.8561875</v>
+        <v>0.8597541214823824</v>
       </c>
       <c r="F38" s="2">
-        <v>0.9004013768967175</v>
+        <v>0.9011232026280093</v>
       </c>
       <c r="G38" s="3">
-        <v>-4.421387689671752</v>
+        <v>-4.136908114562687</v>
       </c>
       <c r="H38">
         <v>11</v>
       </c>
       <c r="I38" s="1">
-        <v>1304</v>
+        <v>1423</v>
       </c>
       <c r="J38" s="2">
         <v>0.9025535792709706</v>
       </c>
       <c r="K38" s="2">
-        <v>0.909785111403513</v>
+        <v>0.9097851114035129</v>
       </c>
       <c r="L38" s="3">
-        <v>-0.7231532132542462</v>
+        <v>-0.7231532132542351</v>
       </c>
       <c r="M38">
         <v>11</v>
       </c>
       <c r="N38" s="1">
-        <v>1395</v>
+        <v>1288</v>
       </c>
       <c r="O38" s="2">
         <v>0.8169546636937941</v>
       </c>
       <c r="P38" s="2">
-        <v>0.8924612938525057</v>
+        <v>0.8924612938525056</v>
       </c>
       <c r="Q38" s="3">
-        <v>-7.550663015871162</v>
+        <v>-7.550663015871151</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -2679,46 +2679,46 @@
         <v>1</v>
       </c>
       <c r="D39" s="1">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E39" s="2">
-        <v>0.8932562390716896</v>
+        <v>0.8914113068619506</v>
       </c>
       <c r="F39" s="2">
-        <v>0.9004013768967175</v>
+        <v>0.9011232026280093</v>
       </c>
       <c r="G39" s="3">
-        <v>-0.7145137825027903</v>
+        <v>-0.9711895766058687</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39" s="1">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="J39" s="2">
         <v>0.8692721203450816</v>
       </c>
       <c r="K39" s="2">
-        <v>0.909785111403513</v>
+        <v>0.9097851114035129</v>
       </c>
       <c r="L39" s="3">
-        <v>-4.051299105843142</v>
+        <v>-4.051299105843132</v>
       </c>
       <c r="M39">
         <v>1</v>
       </c>
       <c r="N39" s="1">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="O39" s="2">
-        <v>0.9135504933788196</v>
+        <v>0.9135504933788197</v>
       </c>
       <c r="P39" s="2">
-        <v>0.8924612938525057</v>
+        <v>0.8924612938525056</v>
       </c>
       <c r="Q39" s="3">
-        <v>2.108919952631383</v>
+        <v>2.108919952631405</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -2732,46 +2732,46 @@
         <v>14</v>
       </c>
       <c r="D40" s="1">
-        <v>3631</v>
+        <v>3627</v>
       </c>
       <c r="E40" s="2">
-        <v>0.9370332898561082</v>
+        <v>0.9358336194608706</v>
       </c>
       <c r="F40" s="2">
-        <v>0.9004013768967175</v>
+        <v>0.9011232026280093</v>
       </c>
       <c r="G40" s="3">
-        <v>3.663191295939072</v>
+        <v>3.471041683286136</v>
       </c>
       <c r="H40">
         <v>14</v>
       </c>
       <c r="I40" s="1">
-        <v>1637</v>
+        <v>1785</v>
       </c>
       <c r="J40" s="2">
         <v>0.9214375747180207</v>
       </c>
       <c r="K40" s="2">
-        <v>0.909785111403513</v>
+        <v>0.9097851114035129</v>
       </c>
       <c r="L40" s="3">
-        <v>1.165246331450764</v>
+        <v>1.165246331450775</v>
       </c>
       <c r="M40">
         <v>14</v>
       </c>
       <c r="N40" s="1">
-        <v>1995</v>
+        <v>1841</v>
       </c>
       <c r="O40" s="2">
         <v>0.9502296642037207</v>
       </c>
       <c r="P40" s="2">
-        <v>0.8924612938525057</v>
+        <v>0.8924612938525056</v>
       </c>
       <c r="Q40" s="3">
-        <v>5.776837035121495</v>
+        <v>5.776837035121507</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -2785,46 +2785,46 @@
         <v>2</v>
       </c>
       <c r="D41" s="1">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E41" s="2">
-        <v>0.900574558718498</v>
+        <v>0.8997632074078353</v>
       </c>
       <c r="F41" s="2">
-        <v>0.9004013768967175</v>
+        <v>0.9011232026280093</v>
       </c>
       <c r="G41" s="3">
-        <v>0.01731818217804992</v>
+        <v>-0.1359995220173937</v>
       </c>
       <c r="H41">
         <v>2</v>
       </c>
       <c r="I41" s="1">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="J41" s="2">
-        <v>0.8900269916798843</v>
+        <v>0.8900269916798841</v>
       </c>
       <c r="K41" s="2">
-        <v>0.909785111403513</v>
+        <v>0.9097851114035129</v>
       </c>
       <c r="L41" s="3">
-        <v>-1.975811972362873</v>
+        <v>-1.975811972362884</v>
       </c>
       <c r="M41">
         <v>2</v>
       </c>
       <c r="N41" s="1">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="O41" s="2">
         <v>0.9094994231357866</v>
       </c>
       <c r="P41" s="2">
-        <v>0.8924612938525057</v>
+        <v>0.8924612938525056</v>
       </c>
       <c r="Q41" s="3">
-        <v>1.703812928328086</v>
+        <v>1.703812928328097</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -2838,46 +2838,46 @@
         <v>11</v>
       </c>
       <c r="D42" s="1">
-        <v>2800</v>
+        <v>2798</v>
       </c>
       <c r="E42" s="2">
-        <v>0.8879067028985507</v>
+        <v>0.8874809381439817</v>
       </c>
       <c r="F42" s="2">
-        <v>0.8904269118708189</v>
+        <v>0.8896079030766169</v>
       </c>
       <c r="G42" s="3">
-        <v>-0.2520208972268234</v>
+        <v>-0.21269649326352</v>
       </c>
       <c r="H42">
         <v>11</v>
       </c>
       <c r="I42" s="1">
-        <v>1275</v>
+        <v>1391</v>
       </c>
       <c r="J42" s="2">
-        <v>0.8823717610891524</v>
+        <v>0.8823717610891525</v>
       </c>
       <c r="K42" s="2">
         <v>0.8797797975461918</v>
       </c>
       <c r="L42" s="3">
-        <v>0.259196354296054</v>
+        <v>0.2591963542960651</v>
       </c>
       <c r="M42">
         <v>11</v>
       </c>
       <c r="N42" s="1">
-        <v>1525</v>
+        <v>1407</v>
       </c>
       <c r="O42" s="2">
-        <v>0.8925901151988108</v>
+        <v>0.8925901151988109</v>
       </c>
       <c r="P42" s="2">
         <v>0.8994360086070419</v>
       </c>
       <c r="Q42" s="3">
-        <v>-0.6845893408231052</v>
+        <v>-0.6845893408230941</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -2891,46 +2891,46 @@
         <v>1</v>
       </c>
       <c r="D43" s="1">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E43" s="2">
-        <v>0.8550886186615799</v>
+        <v>0.8524710625568995</v>
       </c>
       <c r="F43" s="2">
-        <v>0.8904269118708189</v>
+        <v>0.8896079030766169</v>
       </c>
       <c r="G43" s="3">
-        <v>-3.533829320923898</v>
+        <v>-3.713684051971733</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43" s="1">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="J43" s="2">
-        <v>0.8210603893007326</v>
+        <v>0.8210603893007328</v>
       </c>
       <c r="K43" s="2">
         <v>0.8797797975461918</v>
       </c>
       <c r="L43" s="3">
-        <v>-5.871940824545929</v>
+        <v>-5.871940824545907</v>
       </c>
       <c r="M43">
         <v>1</v>
       </c>
       <c r="N43" s="1">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="O43" s="2">
-        <v>0.8838817358130662</v>
+        <v>0.8838817358130663</v>
       </c>
       <c r="P43" s="2">
         <v>0.8994360086070419</v>
       </c>
       <c r="Q43" s="3">
-        <v>-1.55542727939757</v>
+        <v>-1.555427279397559</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -2944,37 +2944,37 @@
         <v>14</v>
       </c>
       <c r="D44" s="1">
-        <v>3473</v>
+        <v>3468</v>
       </c>
       <c r="E44" s="2">
-        <v>0.8960717880455499</v>
+        <v>0.8949823288132678</v>
       </c>
       <c r="F44" s="2">
-        <v>0.8904269118708189</v>
+        <v>0.8896079030766169</v>
       </c>
       <c r="G44" s="3">
-        <v>0.5644876174730973</v>
+        <v>0.5374425736650923</v>
       </c>
       <c r="H44">
         <v>14</v>
       </c>
       <c r="I44" s="1">
-        <v>1566</v>
+        <v>1709</v>
       </c>
       <c r="J44" s="2">
-        <v>0.8819088180258849</v>
+        <v>0.8819088180258848</v>
       </c>
       <c r="K44" s="2">
         <v>0.8797797975461918</v>
       </c>
       <c r="L44" s="3">
-        <v>0.21290204796931</v>
+        <v>0.2129020479692989</v>
       </c>
       <c r="M44">
         <v>14</v>
       </c>
       <c r="N44" s="1">
-        <v>1906</v>
+        <v>1760</v>
       </c>
       <c r="O44" s="2">
         <v>0.9080558396006508</v>
@@ -3000,43 +3000,43 @@
         <v>340</v>
       </c>
       <c r="E45" s="2">
-        <v>0.8877423222120192</v>
+        <v>0.8881371459883856</v>
       </c>
       <c r="F45" s="2">
-        <v>0.8904269118708189</v>
+        <v>0.8896079030766169</v>
       </c>
       <c r="G45" s="3">
-        <v>-0.2684589658799696</v>
+        <v>-0.14707570882313</v>
       </c>
       <c r="H45">
         <v>2</v>
       </c>
       <c r="I45" s="1">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="J45" s="2">
-        <v>0.8928750313047834</v>
+        <v>0.8928750313047832</v>
       </c>
       <c r="K45" s="2">
         <v>0.8797797975461918</v>
       </c>
       <c r="L45" s="3">
-        <v>1.309523375859156</v>
+        <v>1.309523375859134</v>
       </c>
       <c r="M45">
         <v>2</v>
       </c>
       <c r="N45" s="1">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="O45" s="2">
-        <v>0.8833992606719879</v>
+        <v>0.8833992606719878</v>
       </c>
       <c r="P45" s="2">
         <v>0.8994360086070419</v>
       </c>
       <c r="Q45" s="3">
-        <v>-1.603674793505394</v>
+        <v>-1.603674793505405</v>
       </c>
     </row>
     <row r="46" spans="1:17">
@@ -3050,28 +3050,28 @@
         <v>12</v>
       </c>
       <c r="D46" s="1">
-        <v>2872</v>
+        <v>2869</v>
       </c>
       <c r="E46" s="2">
-        <v>0.8704321489919538</v>
+        <v>0.866034093501505</v>
       </c>
       <c r="F46" s="2">
-        <v>0.8916101253733195</v>
+        <v>0.8901845880970316</v>
       </c>
       <c r="G46" s="3">
-        <v>-2.117797638136576</v>
+        <v>-2.415049459552665</v>
       </c>
       <c r="H46">
         <v>12</v>
       </c>
       <c r="I46" s="1">
-        <v>1299</v>
+        <v>1417</v>
       </c>
       <c r="J46" s="2">
-        <v>0.8158870585045083</v>
+        <v>0.8158870585045082</v>
       </c>
       <c r="K46" s="2">
-        <v>0.8731126143424989</v>
+        <v>0.8731126143424988</v>
       </c>
       <c r="L46" s="3">
         <v>-5.72255558379906</v>
@@ -3080,16 +3080,16 @@
         <v>11</v>
       </c>
       <c r="N46" s="1">
-        <v>1574</v>
+        <v>1453</v>
       </c>
       <c r="O46" s="2">
         <v>0.9212612411742847</v>
       </c>
       <c r="P46" s="2">
-        <v>0.9073203142788925</v>
+        <v>0.9073203142788924</v>
       </c>
       <c r="Q46" s="3">
-        <v>1.394092689539217</v>
+        <v>1.394092689539228</v>
       </c>
     </row>
     <row r="47" spans="1:17">
@@ -3103,46 +3103,46 @@
         <v>1</v>
       </c>
       <c r="D47" s="1">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E47" s="2">
-        <v>0.7325504689238594</v>
+        <v>0.7223892940631138</v>
       </c>
       <c r="F47" s="2">
-        <v>0.8916101253733195</v>
+        <v>0.8901845880970316</v>
       </c>
       <c r="G47" s="3">
-        <v>-15.90596564494601</v>
+        <v>-16.77952940339178</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J47" s="2">
         <v>0.6004551957341656</v>
       </c>
       <c r="K47" s="2">
-        <v>0.8731126143424989</v>
+        <v>0.8731126143424988</v>
       </c>
       <c r="L47" s="3">
-        <v>-27.26574186083333</v>
+        <v>-27.26574186083332</v>
       </c>
       <c r="M47">
         <v>1</v>
       </c>
       <c r="N47" s="1">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="O47" s="2">
-        <v>0.8443233923920619</v>
+        <v>0.844323392392062</v>
       </c>
       <c r="P47" s="2">
-        <v>0.9073203142788925</v>
+        <v>0.9073203142788924</v>
       </c>
       <c r="Q47" s="3">
-        <v>-6.299692188683059</v>
+        <v>-6.299692188683037</v>
       </c>
     </row>
     <row r="48" spans="1:17">
@@ -3156,46 +3156,46 @@
         <v>14</v>
       </c>
       <c r="D48" s="1">
-        <v>3448</v>
+        <v>3444</v>
       </c>
       <c r="E48" s="2">
-        <v>0.9213447249166987</v>
+        <v>0.9233149690798519</v>
       </c>
       <c r="F48" s="2">
-        <v>0.8916101253733195</v>
+        <v>0.8901845880970316</v>
       </c>
       <c r="G48" s="3">
-        <v>2.97345995433792</v>
+        <v>3.313038098282028</v>
       </c>
       <c r="H48">
         <v>13</v>
       </c>
       <c r="I48" s="1">
-        <v>1558</v>
+        <v>1699</v>
       </c>
       <c r="J48" s="2">
         <v>0.9479953082803935</v>
       </c>
       <c r="K48" s="2">
-        <v>0.8731126143424989</v>
+        <v>0.8731126143424988</v>
       </c>
       <c r="L48" s="3">
-        <v>7.48826939378946</v>
+        <v>7.488269393789471</v>
       </c>
       <c r="M48">
         <v>14</v>
       </c>
       <c r="N48" s="1">
-        <v>1890</v>
+        <v>1745</v>
       </c>
       <c r="O48" s="2">
         <v>0.9004840678189734</v>
       </c>
       <c r="P48" s="2">
-        <v>0.9073203142788925</v>
+        <v>0.9073203142788924</v>
       </c>
       <c r="Q48" s="3">
-        <v>-0.6836246459919093</v>
+        <v>-0.6836246459918982</v>
       </c>
     </row>
     <row r="49" spans="1:17">
@@ -3212,43 +3212,43 @@
         <v>358</v>
       </c>
       <c r="E49" s="2">
-        <v>0.9351698806244261</v>
+        <v>0.9363880380409306</v>
       </c>
       <c r="F49" s="2">
-        <v>0.8916101253733195</v>
+        <v>0.8901845880970316</v>
       </c>
       <c r="G49" s="3">
-        <v>4.355975525110656</v>
+        <v>4.620344994389902</v>
       </c>
       <c r="H49">
         <v>2</v>
       </c>
       <c r="I49" s="1">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="J49" s="2">
         <v>0.9510059270389848</v>
       </c>
       <c r="K49" s="2">
-        <v>0.8731126143424989</v>
+        <v>0.8731126143424988</v>
       </c>
       <c r="L49" s="3">
-        <v>7.789331269648592</v>
+        <v>7.789331269648603</v>
       </c>
       <c r="M49">
         <v>2</v>
       </c>
       <c r="N49" s="1">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="O49" s="2">
         <v>0.9217701490428762</v>
       </c>
       <c r="P49" s="2">
-        <v>0.9073203142788925</v>
+        <v>0.9073203142788924</v>
       </c>
       <c r="Q49" s="3">
-        <v>1.444983476398376</v>
+        <v>1.444983476398387</v>
       </c>
     </row>
     <row r="50" spans="1:17">
@@ -3262,46 +3262,46 @@
         <v>12</v>
       </c>
       <c r="D50" s="1">
-        <v>3020</v>
+        <v>3015</v>
       </c>
       <c r="E50" s="2">
-        <v>0.8695394861897033</v>
+        <v>0.8680563109303734</v>
       </c>
       <c r="F50" s="2">
-        <v>0.8919409061730958</v>
+        <v>0.8911929620742598</v>
       </c>
       <c r="G50" s="3">
-        <v>-2.240141998339251</v>
+        <v>-2.313665114388641</v>
       </c>
       <c r="H50">
         <v>12</v>
       </c>
       <c r="I50" s="1">
-        <v>1353</v>
+        <v>1476</v>
       </c>
       <c r="J50" s="2">
-        <v>0.8502582078184132</v>
+        <v>0.850258207818413</v>
       </c>
       <c r="K50" s="2">
         <v>0.8822176328882262</v>
       </c>
       <c r="L50" s="3">
-        <v>-3.195942506981297</v>
+        <v>-3.19594250698132</v>
       </c>
       <c r="M50">
         <v>12</v>
       </c>
       <c r="N50" s="1">
-        <v>1666</v>
+        <v>1538</v>
       </c>
       <c r="O50" s="2">
         <v>0.8858544140423334</v>
       </c>
       <c r="P50" s="2">
-        <v>0.9001682912602933</v>
+        <v>0.9001682912602934</v>
       </c>
       <c r="Q50" s="3">
-        <v>-1.431387721795985</v>
+        <v>-1.431387721795996</v>
       </c>
     </row>
     <row r="51" spans="1:17">
@@ -3318,40 +3318,40 @@
         <v>285</v>
       </c>
       <c r="E51" s="2">
-        <v>0.7800925925925927</v>
+        <v>0.7803220384765451</v>
       </c>
       <c r="F51" s="2">
-        <v>0.8919409061730958</v>
+        <v>0.8911929620742598</v>
       </c>
       <c r="G51" s="3">
-        <v>-11.18483135805032</v>
+        <v>-11.08709235977147</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51" s="1">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J51" s="2">
-        <v>0.7830753890839728</v>
+        <v>0.7830753890839729</v>
       </c>
       <c r="K51" s="2">
         <v>0.8822176328882262</v>
       </c>
       <c r="L51" s="3">
-        <v>-9.91422438042534</v>
+        <v>-9.914224380425329</v>
       </c>
       <c r="M51">
         <v>1</v>
       </c>
       <c r="N51" s="1">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="O51" s="2">
-        <v>0.777568687869117</v>
+        <v>0.7775686878691171</v>
       </c>
       <c r="P51" s="2">
-        <v>0.9001682912602933</v>
+        <v>0.9001682912602934</v>
       </c>
       <c r="Q51" s="3">
         <v>-12.25996033911763</v>
@@ -3368,22 +3368,22 @@
         <v>13</v>
       </c>
       <c r="D52" s="1">
-        <v>3408</v>
+        <v>3409</v>
       </c>
       <c r="E52" s="2">
-        <v>0.9505710717090947</v>
+        <v>0.9508504687262365</v>
       </c>
       <c r="F52" s="2">
-        <v>0.8919409061730958</v>
+        <v>0.8911929620742598</v>
       </c>
       <c r="G52" s="3">
-        <v>5.863016553599887</v>
+        <v>5.965750665197667</v>
       </c>
       <c r="H52">
         <v>13</v>
       </c>
       <c r="I52" s="1">
-        <v>1568</v>
+        <v>1710</v>
       </c>
       <c r="J52" s="2">
         <v>0.9542032329319385</v>
@@ -3398,16 +3398,16 @@
         <v>13</v>
       </c>
       <c r="N52" s="1">
-        <v>1840</v>
+        <v>1698</v>
       </c>
       <c r="O52" s="2">
         <v>0.9474977045205345</v>
       </c>
       <c r="P52" s="2">
-        <v>0.9001682912602933</v>
+        <v>0.9001682912602934</v>
       </c>
       <c r="Q52" s="3">
-        <v>4.73294132602412</v>
+        <v>4.732941326024109</v>
       </c>
     </row>
     <row r="53" spans="1:17">
@@ -3421,46 +3421,46 @@
         <v>2</v>
       </c>
       <c r="D53" s="1">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E53" s="2">
-        <v>0.6527745893276197</v>
+        <v>0.6481435995898805</v>
       </c>
       <c r="F53" s="2">
-        <v>0.8919409061730958</v>
+        <v>0.8911929620742598</v>
       </c>
       <c r="G53" s="3">
-        <v>-23.91663168454762</v>
+        <v>-24.30493624843793</v>
       </c>
       <c r="H53">
         <v>2</v>
       </c>
       <c r="I53" s="1">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="J53" s="2">
-        <v>0.5925717227370121</v>
+        <v>0.5925717227370119</v>
       </c>
       <c r="K53" s="2">
         <v>0.8822176328882262</v>
       </c>
       <c r="L53" s="3">
-        <v>-28.96459101512141</v>
+        <v>-28.96459101512143</v>
       </c>
       <c r="M53">
         <v>2</v>
       </c>
       <c r="N53" s="1">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="O53" s="2">
         <v>0.7037154764427491</v>
       </c>
       <c r="P53" s="2">
-        <v>0.9001682912602933</v>
+        <v>0.9001682912602934</v>
       </c>
       <c r="Q53" s="3">
-        <v>-19.64528148175442</v>
+        <v>-19.64528148175443</v>
       </c>
     </row>
     <row r="54" spans="1:17">
@@ -3474,46 +3474,46 @@
         <v>12</v>
       </c>
       <c r="D54" s="1">
-        <v>3161</v>
+        <v>3162</v>
       </c>
       <c r="E54" s="2">
-        <v>0.9103590019154567</v>
+        <v>0.9104591727963224</v>
       </c>
       <c r="F54" s="2">
-        <v>0.9231384495294301</v>
+        <v>0.9228596929801954</v>
       </c>
       <c r="G54" s="3">
-        <v>-1.277944761397343</v>
+        <v>-1.240052018387305</v>
       </c>
       <c r="H54">
         <v>12</v>
       </c>
       <c r="I54" s="1">
-        <v>1451</v>
+        <v>1583</v>
       </c>
       <c r="J54" s="2">
         <v>0.911661223366711</v>
       </c>
       <c r="K54" s="2">
-        <v>0.9195146143893788</v>
+        <v>0.9195146143893789</v>
       </c>
       <c r="L54" s="3">
-        <v>-0.7853391022667799</v>
+        <v>-0.785339102266791</v>
       </c>
       <c r="M54">
         <v>12</v>
       </c>
       <c r="N54" s="1">
-        <v>1710</v>
+        <v>1579</v>
       </c>
       <c r="O54" s="2">
-        <v>0.909257122225934</v>
+        <v>0.9092571222259339</v>
       </c>
       <c r="P54" s="2">
         <v>0.9262047715710119</v>
       </c>
       <c r="Q54" s="3">
-        <v>-1.694764934507786</v>
+        <v>-1.694764934507798</v>
       </c>
     </row>
     <row r="55" spans="1:17">
@@ -3530,25 +3530,25 @@
         <v>314</v>
       </c>
       <c r="E55" s="2">
-        <v>0.8611150850421238</v>
+        <v>0.8597196794621688</v>
       </c>
       <c r="F55" s="2">
-        <v>0.9231384495294301</v>
+        <v>0.9228596929801954</v>
       </c>
       <c r="G55" s="3">
-        <v>-6.202336448730639</v>
+        <v>-6.314001351802667</v>
       </c>
       <c r="H55">
         <v>1</v>
       </c>
       <c r="I55" s="1">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="J55" s="2">
-        <v>0.8429748125027096</v>
+        <v>0.8429748125027097</v>
       </c>
       <c r="K55" s="2">
-        <v>0.9195146143893788</v>
+        <v>0.9195146143893789</v>
       </c>
       <c r="L55" s="3">
         <v>-7.65398018866692</v>
@@ -3557,7 +3557,7 @@
         <v>1</v>
       </c>
       <c r="N55" s="1">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="O55" s="2">
         <v>0.876464546421628</v>
@@ -3580,46 +3580,46 @@
         <v>13</v>
       </c>
       <c r="D56" s="1">
-        <v>3366</v>
+        <v>3364</v>
       </c>
       <c r="E56" s="2">
-        <v>0.9389221262924763</v>
+        <v>0.9384065590607483</v>
       </c>
       <c r="F56" s="2">
-        <v>0.9231384495294301</v>
+        <v>0.9228596929801954</v>
       </c>
       <c r="G56" s="3">
-        <v>1.578367676304615</v>
+        <v>1.554686608055289</v>
       </c>
       <c r="H56">
         <v>13</v>
       </c>
       <c r="I56" s="1">
-        <v>1532</v>
+        <v>1671</v>
       </c>
       <c r="J56" s="2">
-        <v>0.9322197522800143</v>
+        <v>0.9322197522800142</v>
       </c>
       <c r="K56" s="2">
-        <v>0.9195146143893788</v>
+        <v>0.9195146143893789</v>
       </c>
       <c r="L56" s="3">
-        <v>1.270513789063554</v>
+        <v>1.270513789063532</v>
       </c>
       <c r="M56">
         <v>13</v>
       </c>
       <c r="N56" s="1">
-        <v>1834</v>
+        <v>1693</v>
       </c>
       <c r="O56" s="2">
-        <v>0.9445933658414827</v>
+        <v>0.9445933658414826</v>
       </c>
       <c r="P56" s="2">
         <v>0.9262047715710119</v>
       </c>
       <c r="Q56" s="3">
-        <v>1.838859427047079</v>
+        <v>1.838859427047068</v>
       </c>
     </row>
     <row r="57" spans="1:17">
@@ -3636,43 +3636,43 @@
         <v>364</v>
       </c>
       <c r="E57" s="2">
-        <v>0.9504074839302112</v>
+        <v>0.9499738324118489</v>
       </c>
       <c r="F57" s="2">
-        <v>0.9231384495294301</v>
+        <v>0.9228596929801954</v>
       </c>
       <c r="G57" s="3">
-        <v>2.72690344007811</v>
+        <v>2.711413943165342</v>
       </c>
       <c r="H57">
         <v>2</v>
       </c>
       <c r="I57" s="1">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="J57" s="2">
-        <v>0.944770014191502</v>
+        <v>0.9447700141915018</v>
       </c>
       <c r="K57" s="2">
-        <v>0.9195146143893788</v>
+        <v>0.9195146143893789</v>
       </c>
       <c r="L57" s="3">
-        <v>2.525539980212321</v>
+        <v>2.525539980212288</v>
       </c>
       <c r="M57">
         <v>2</v>
       </c>
       <c r="N57" s="1">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="O57" s="2">
-        <v>0.955177650632196</v>
+        <v>0.9551776506321961</v>
       </c>
       <c r="P57" s="2">
         <v>0.9262047715710119</v>
       </c>
       <c r="Q57" s="3">
-        <v>2.897287906118406</v>
+        <v>2.897287906118418</v>
       </c>
     </row>
     <row r="58" spans="1:17">
@@ -3686,46 +3686,46 @@
         <v>12</v>
       </c>
       <c r="D58" s="1">
-        <v>3060</v>
+        <v>3062</v>
       </c>
       <c r="E58" s="2">
-        <v>0.8810449291573452</v>
+        <v>0.8817272991078755</v>
       </c>
       <c r="F58" s="2">
-        <v>0.8818391330542817</v>
+        <v>0.8832011896592704</v>
       </c>
       <c r="G58" s="3">
-        <v>-0.07942038969365184</v>
+        <v>-0.1473890551394907</v>
       </c>
       <c r="H58">
         <v>12</v>
       </c>
       <c r="I58" s="1">
-        <v>1416</v>
+        <v>1545</v>
       </c>
       <c r="J58" s="2">
-        <v>0.8899157385142384</v>
+        <v>0.8899157385142382</v>
       </c>
       <c r="K58" s="2">
-        <v>0.8998879811680001</v>
+        <v>0.8998879811680002</v>
       </c>
       <c r="L58" s="3">
-        <v>-0.997224265376162</v>
+        <v>-0.9972242653761954</v>
       </c>
       <c r="M58">
         <v>12</v>
       </c>
       <c r="N58" s="1">
-        <v>1643</v>
+        <v>1517</v>
       </c>
       <c r="O58" s="2">
-        <v>0.8735388597015127</v>
+        <v>0.8735388597015126</v>
       </c>
       <c r="P58" s="2">
-        <v>0.8671352200822799</v>
+        <v>0.8671352200822801</v>
       </c>
       <c r="Q58" s="3">
-        <v>0.6403639619232737</v>
+        <v>0.6403639619232515</v>
       </c>
     </row>
     <row r="59" spans="1:17">
@@ -3739,43 +3739,43 @@
         <v>1</v>
       </c>
       <c r="D59" s="1">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E59" s="2">
-        <v>0.8390180416467968</v>
+        <v>0.8404462252101738</v>
       </c>
       <c r="F59" s="2">
-        <v>0.8818391330542817</v>
+        <v>0.8832011896592704</v>
       </c>
       <c r="G59" s="3">
-        <v>-4.282109140748491</v>
+        <v>-4.275496444909665</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59" s="1">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="J59" s="2">
-        <v>0.8575844279706939</v>
+        <v>0.8575844279706941</v>
       </c>
       <c r="K59" s="2">
-        <v>0.8998879811680001</v>
+        <v>0.8998879811680002</v>
       </c>
       <c r="L59" s="3">
-        <v>-4.230355319730617</v>
+        <v>-4.230355319730606</v>
       </c>
       <c r="M59">
         <v>1</v>
       </c>
       <c r="N59" s="1">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="O59" s="2">
-        <v>0.8233080224496532</v>
+        <v>0.8233080224496533</v>
       </c>
       <c r="P59" s="2">
-        <v>0.8671352200822799</v>
+        <v>0.8671352200822801</v>
       </c>
       <c r="Q59" s="3">
         <v>-4.382719763262677</v>
@@ -3792,46 +3792,46 @@
         <v>13</v>
       </c>
       <c r="D60" s="1">
-        <v>3033</v>
+        <v>3030</v>
       </c>
       <c r="E60" s="2">
-        <v>0.8786854690824963</v>
+        <v>0.8807695193467282</v>
       </c>
       <c r="F60" s="2">
-        <v>0.8818391330542817</v>
+        <v>0.8832011896592704</v>
       </c>
       <c r="G60" s="3">
-        <v>-0.3153663971785403</v>
+        <v>-0.2431670312542211</v>
       </c>
       <c r="H60">
         <v>12</v>
       </c>
       <c r="I60" s="1">
-        <v>1370</v>
+        <v>1494</v>
       </c>
       <c r="J60" s="2">
-        <v>0.9069721808246399</v>
+        <v>0.9069721808246398</v>
       </c>
       <c r="K60" s="2">
-        <v>0.8998879811680001</v>
+        <v>0.8998879811680002</v>
       </c>
       <c r="L60" s="3">
-        <v>0.7084199656639867</v>
+        <v>0.7084199656639645</v>
       </c>
       <c r="M60">
         <v>13</v>
       </c>
       <c r="N60" s="1">
-        <v>1664</v>
+        <v>1536</v>
       </c>
       <c r="O60" s="2">
-        <v>0.856689428314182</v>
+        <v>0.8566894283141819</v>
       </c>
       <c r="P60" s="2">
-        <v>0.8671352200822799</v>
+        <v>0.8671352200822801</v>
       </c>
       <c r="Q60" s="3">
-        <v>-1.04457917680979</v>
+        <v>-1.044579176809812</v>
       </c>
     </row>
     <row r="61" spans="1:17">
@@ -3848,43 +3848,43 @@
         <v>367</v>
       </c>
       <c r="E61" s="2">
-        <v>0.9583154780124478</v>
+        <v>0.9591932248957041</v>
       </c>
       <c r="F61" s="2">
-        <v>0.8818391330542817</v>
+        <v>0.8832011896592704</v>
       </c>
       <c r="G61" s="3">
-        <v>7.647634495816602</v>
+        <v>7.599203523643371</v>
       </c>
       <c r="H61">
         <v>2</v>
       </c>
       <c r="I61" s="1">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J61" s="2">
-        <v>0.9697261874947826</v>
+        <v>0.9697261874947825</v>
       </c>
       <c r="K61" s="2">
-        <v>0.8998879811680001</v>
+        <v>0.8998879811680002</v>
       </c>
       <c r="L61" s="3">
-        <v>6.983820632678251</v>
+        <v>6.983820632678228</v>
       </c>
       <c r="M61">
         <v>2</v>
       </c>
       <c r="N61" s="1">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="O61" s="2">
-        <v>0.9486602622966258</v>
+        <v>0.9486602622966257</v>
       </c>
       <c r="P61" s="2">
-        <v>0.8671352200822799</v>
+        <v>0.8671352200822801</v>
       </c>
       <c r="Q61" s="3">
-        <v>8.152504221434587</v>
+        <v>8.152504221434565</v>
       </c>
     </row>
     <row r="62" spans="1:17">
@@ -3898,46 +3898,46 @@
         <v>12</v>
       </c>
       <c r="D62" s="1">
-        <v>2893</v>
+        <v>2871</v>
       </c>
       <c r="E62" s="2">
-        <v>0.8329921882996301</v>
+        <v>0.8266992022321671</v>
       </c>
       <c r="F62" s="2">
-        <v>0.878462470772397</v>
+        <v>0.8751218241573298</v>
       </c>
       <c r="G62" s="3">
-        <v>-4.547028247276696</v>
+        <v>-4.842262192516267</v>
       </c>
       <c r="H62">
         <v>12</v>
       </c>
       <c r="I62" s="1">
-        <v>1196</v>
+        <v>1304</v>
       </c>
       <c r="J62" s="2">
-        <v>0.7511833694226114</v>
+        <v>0.7511833694226113</v>
       </c>
       <c r="K62" s="2">
         <v>0.8350340647765211</v>
       </c>
       <c r="L62" s="3">
-        <v>-8.385069535390965</v>
+        <v>-8.385069535390976</v>
       </c>
       <c r="M62">
         <v>12</v>
       </c>
       <c r="N62" s="1">
-        <v>1697</v>
+        <v>1567</v>
       </c>
       <c r="O62" s="2">
-        <v>0.9022150350417228</v>
+        <v>0.9022150350417226</v>
       </c>
       <c r="P62" s="2">
-        <v>0.9152095835381383</v>
+        <v>0.9152095835381384</v>
       </c>
       <c r="Q62" s="3">
-        <v>-1.299454849641546</v>
+        <v>-1.299454849641579</v>
       </c>
     </row>
     <row r="63" spans="1:17">
@@ -3951,22 +3951,22 @@
         <v>1</v>
       </c>
       <c r="D63" s="1">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E63" s="2">
-        <v>0.7700484819583532</v>
+        <v>0.7680162469862041</v>
       </c>
       <c r="F63" s="2">
-        <v>0.878462470772397</v>
+        <v>0.8751218241573298</v>
       </c>
       <c r="G63" s="3">
-        <v>-10.84139888140438</v>
+        <v>-10.71055771711257</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63" s="1">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="J63" s="2">
         <v>0.7436294273204145</v>
@@ -3981,16 +3981,16 @@
         <v>1</v>
       </c>
       <c r="N63" s="1">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="O63" s="2">
         <v>0.7924030666519937</v>
       </c>
       <c r="P63" s="2">
-        <v>0.9152095835381383</v>
+        <v>0.9152095835381384</v>
       </c>
       <c r="Q63" s="3">
-        <v>-12.28065168861446</v>
+        <v>-12.28065168861447</v>
       </c>
     </row>
     <row r="64" spans="1:17">
@@ -4004,46 +4004,46 @@
         <v>12</v>
       </c>
       <c r="D64" s="1">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="E64" s="2">
-        <v>0.9349950084068936</v>
+        <v>0.9345711087987254</v>
       </c>
       <c r="F64" s="2">
-        <v>0.878462470772397</v>
+        <v>0.8751218241573298</v>
       </c>
       <c r="G64" s="3">
-        <v>5.653253763449662</v>
+        <v>5.944928464139565</v>
       </c>
       <c r="H64">
         <v>12</v>
       </c>
       <c r="I64" s="1">
-        <v>1404</v>
+        <v>1531</v>
       </c>
       <c r="J64" s="2">
-        <v>0.929484313500707</v>
+        <v>0.9294843135007068</v>
       </c>
       <c r="K64" s="2">
         <v>0.8350340647765211</v>
       </c>
       <c r="L64" s="3">
-        <v>9.445024872418594</v>
+        <v>9.445024872418573</v>
       </c>
       <c r="M64">
         <v>12</v>
       </c>
       <c r="N64" s="1">
-        <v>1677</v>
+        <v>1548</v>
       </c>
       <c r="O64" s="2">
         <v>0.9396579040967439</v>
       </c>
       <c r="P64" s="2">
-        <v>0.9152095835381383</v>
+        <v>0.9152095835381384</v>
       </c>
       <c r="Q64" s="3">
-        <v>2.444832055860557</v>
+        <v>2.444832055860546</v>
       </c>
     </row>
     <row r="65" spans="1:17">
@@ -4057,46 +4057,46 @@
         <v>2</v>
       </c>
       <c r="D65" s="1">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E65" s="2">
-        <v>0.9078142536475869</v>
+        <v>0.9049063425096482</v>
       </c>
       <c r="F65" s="2">
-        <v>0.878462470772397</v>
+        <v>0.8751218241573298</v>
       </c>
       <c r="G65" s="3">
-        <v>2.935178287518991</v>
+        <v>2.978451835231843</v>
       </c>
       <c r="H65">
         <v>2</v>
       </c>
       <c r="I65" s="1">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="J65" s="2">
-        <v>0.8700114088543841</v>
+        <v>0.870011408854384</v>
       </c>
       <c r="K65" s="2">
         <v>0.8350340647765211</v>
       </c>
       <c r="L65" s="3">
-        <v>3.497734407786302</v>
+        <v>3.49773440778629</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65" s="1">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="O65" s="2">
         <v>0.9398012761649124</v>
       </c>
       <c r="P65" s="2">
-        <v>0.9152095835381383</v>
+        <v>0.9152095835381384</v>
       </c>
       <c r="Q65" s="3">
-        <v>2.459169262677408</v>
+        <v>2.459169262677396</v>
       </c>
     </row>
     <row r="66" spans="1:17">
@@ -4110,46 +4110,46 @@
         <v>12</v>
       </c>
       <c r="D66" s="1">
-        <v>2326</v>
+        <v>2283</v>
       </c>
       <c r="E66" s="2">
-        <v>0.6699163632641721</v>
+        <v>0.6573617219294281</v>
       </c>
       <c r="F66" s="2">
-        <v>0.7050154264312666</v>
+        <v>0.6913538250570118</v>
       </c>
       <c r="G66" s="3">
-        <v>-3.509906316709444</v>
+        <v>-3.399210312758372</v>
       </c>
       <c r="H66">
         <v>12</v>
       </c>
       <c r="I66" s="1">
-        <v>807</v>
+        <v>880</v>
       </c>
       <c r="J66" s="2">
-        <v>0.5067060259125005</v>
+        <v>0.5067060259125004</v>
       </c>
       <c r="K66" s="2">
         <v>0.5315285559222972</v>
       </c>
       <c r="L66" s="3">
-        <v>-2.482253000979673</v>
+        <v>-2.482253000979684</v>
       </c>
       <c r="M66">
         <v>12</v>
       </c>
       <c r="N66" s="1">
-        <v>1520</v>
+        <v>1403</v>
       </c>
       <c r="O66" s="2">
-        <v>0.808017417946356</v>
+        <v>0.8080174179463558</v>
       </c>
       <c r="P66" s="2">
         <v>0.8589431775079349</v>
       </c>
       <c r="Q66" s="3">
-        <v>-5.092575956157896</v>
+        <v>-5.092575956157908</v>
       </c>
     </row>
     <row r="67" spans="1:17">
@@ -4163,22 +4163,22 @@
         <v>2</v>
       </c>
       <c r="D67" s="1">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E67" s="2">
-        <v>0.6020723482526057</v>
+        <v>0.5906869954080255</v>
       </c>
       <c r="F67" s="2">
-        <v>0.7050154264312666</v>
+        <v>0.6913538250570118</v>
       </c>
       <c r="G67" s="3">
-        <v>-10.29430781786609</v>
+        <v>-10.06668296489863</v>
       </c>
       <c r="H67">
         <v>2</v>
       </c>
       <c r="I67" s="1">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="J67" s="2">
         <v>0.4910651580179477</v>
@@ -4193,16 +4193,16 @@
         <v>1</v>
       </c>
       <c r="N67" s="1">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="O67" s="2">
-        <v>0.7899306701881808</v>
+        <v>0.789930670188181</v>
       </c>
       <c r="P67" s="2">
         <v>0.8589431775079349</v>
       </c>
       <c r="Q67" s="3">
-        <v>-6.901250731975416</v>
+        <v>-6.901250731975395</v>
       </c>
     </row>
     <row r="68" spans="1:17">
@@ -4216,37 +4216,37 @@
         <v>12</v>
       </c>
       <c r="D68" s="1">
-        <v>2493</v>
+        <v>2445</v>
       </c>
       <c r="E68" s="2">
-        <v>0.7567654476670871</v>
+        <v>0.7421922444936315</v>
       </c>
       <c r="F68" s="2">
-        <v>0.7050154264312666</v>
+        <v>0.6913538250570118</v>
       </c>
       <c r="G68" s="3">
-        <v>5.17500212358205</v>
+        <v>5.083841943661971</v>
       </c>
       <c r="H68">
         <v>12</v>
       </c>
       <c r="I68" s="1">
-        <v>857</v>
+        <v>935</v>
       </c>
       <c r="J68" s="2">
-        <v>0.5673138064121671</v>
+        <v>0.567313806412167</v>
       </c>
       <c r="K68" s="2">
         <v>0.5315285559222972</v>
       </c>
       <c r="L68" s="3">
-        <v>3.578525048986991</v>
+        <v>3.57852504898698</v>
       </c>
       <c r="M68">
         <v>12</v>
       </c>
       <c r="N68" s="1">
-        <v>1637</v>
+        <v>1511</v>
       </c>
       <c r="O68" s="2">
         <v>0.9170706825750962</v>
@@ -4269,46 +4269,46 @@
         <v>2</v>
       </c>
       <c r="D69" s="1">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E69" s="2">
-        <v>0.7212216865625958</v>
+        <v>0.7061979725202865</v>
       </c>
       <c r="F69" s="2">
-        <v>0.7050154264312666</v>
+        <v>0.6913538250570118</v>
       </c>
       <c r="G69" s="3">
-        <v>1.62062601313292</v>
+        <v>1.484414746327467</v>
       </c>
       <c r="H69">
         <v>2</v>
       </c>
       <c r="I69" s="1">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="J69" s="2">
-        <v>0.5259134040125777</v>
+        <v>0.5259134040125775</v>
       </c>
       <c r="K69" s="2">
         <v>0.5315285559222972</v>
       </c>
       <c r="L69" s="3">
-        <v>-0.5615151909719507</v>
+        <v>-0.5615151909719729</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69" s="1">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="O69" s="2">
-        <v>0.8864825410279954</v>
+        <v>0.8864825410279955</v>
       </c>
       <c r="P69" s="2">
         <v>0.8589431775079349</v>
       </c>
       <c r="Q69" s="3">
-        <v>2.753936352006048</v>
+        <v>2.753936352006059</v>
       </c>
     </row>
     <row r="70" spans="1:17">
@@ -4322,37 +4322,37 @@
         <v>11</v>
       </c>
       <c r="D70" s="1">
-        <v>2867</v>
+        <v>2863</v>
       </c>
       <c r="E70" s="2">
-        <v>0.8977507075621701</v>
+        <v>0.8964080781839797</v>
       </c>
       <c r="F70" s="2">
-        <v>0.9097412475239556</v>
+        <v>0.9089425774522214</v>
       </c>
       <c r="G70" s="3">
-        <v>-1.199053996178545</v>
+        <v>-1.253449926824168</v>
       </c>
       <c r="H70">
         <v>11</v>
       </c>
       <c r="I70" s="1">
-        <v>1288</v>
+        <v>1406</v>
       </c>
       <c r="J70" s="2">
-        <v>0.8802965256456957</v>
+        <v>0.8802965256456955</v>
       </c>
       <c r="K70" s="2">
         <v>0.8993585365914101</v>
       </c>
       <c r="L70" s="3">
-        <v>-1.906201094571436</v>
+        <v>-1.906201094571458</v>
       </c>
       <c r="M70">
         <v>11</v>
       </c>
       <c r="N70" s="1">
-        <v>1578</v>
+        <v>1457</v>
       </c>
       <c r="O70" s="2">
         <v>0.9125196307222637</v>
@@ -4375,46 +4375,46 @@
         <v>2</v>
       </c>
       <c r="D71" s="1">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E71" s="2">
-        <v>0.8047995151804165</v>
+        <v>0.8008252715334261</v>
       </c>
       <c r="F71" s="2">
-        <v>0.9097412475239556</v>
+        <v>0.9089425774522214</v>
       </c>
       <c r="G71" s="3">
-        <v>-10.49417323435391</v>
+        <v>-10.81173059187953</v>
       </c>
       <c r="H71">
         <v>2</v>
       </c>
       <c r="I71" s="1">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="J71" s="2">
-        <v>0.7531343477695408</v>
+        <v>0.753134347769541</v>
       </c>
       <c r="K71" s="2">
         <v>0.8993585365914101</v>
       </c>
       <c r="L71" s="3">
-        <v>-14.62241888218693</v>
+        <v>-14.6224188821869</v>
       </c>
       <c r="M71">
         <v>2</v>
       </c>
       <c r="N71" s="1">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="O71" s="2">
-        <v>0.8485161952973111</v>
+        <v>0.8485161952973113</v>
       </c>
       <c r="P71" s="2">
         <v>0.9185266183130327</v>
       </c>
       <c r="Q71" s="3">
-        <v>-7.001042301572157</v>
+        <v>-7.001042301572147</v>
       </c>
     </row>
     <row r="72" spans="1:17">
@@ -4428,46 +4428,46 @@
         <v>12</v>
       </c>
       <c r="D72" s="1">
-        <v>3113</v>
+        <v>3115</v>
       </c>
       <c r="E72" s="2">
-        <v>0.9450226810985008</v>
+        <v>0.9454178828737466</v>
       </c>
       <c r="F72" s="2">
-        <v>0.9097412475239556</v>
+        <v>0.9089425774522214</v>
       </c>
       <c r="G72" s="3">
-        <v>3.528143357454527</v>
+        <v>3.647530542152522</v>
       </c>
       <c r="H72">
         <v>12</v>
       </c>
       <c r="I72" s="1">
-        <v>1435</v>
+        <v>1565</v>
       </c>
       <c r="J72" s="2">
-        <v>0.9501603041766977</v>
+        <v>0.9501603041766975</v>
       </c>
       <c r="K72" s="2">
         <v>0.8993585365914101</v>
       </c>
       <c r="L72" s="3">
-        <v>5.080176758528765</v>
+        <v>5.080176758528743</v>
       </c>
       <c r="M72">
         <v>12</v>
       </c>
       <c r="N72" s="1">
-        <v>1679</v>
+        <v>1550</v>
       </c>
       <c r="O72" s="2">
-        <v>0.9406754615707958</v>
+        <v>0.9406754615707957</v>
       </c>
       <c r="P72" s="2">
         <v>0.9185266183130327</v>
       </c>
       <c r="Q72" s="3">
-        <v>2.214884325776312</v>
+        <v>2.214884325776301</v>
       </c>
     </row>
     <row r="73" spans="1:17">
@@ -4484,34 +4484,34 @@
         <v>542</v>
       </c>
       <c r="E73" s="2">
-        <v>0.907531045751634</v>
+        <v>0.9069374057315234</v>
       </c>
       <c r="F73" s="2">
-        <v>0.9097412475239556</v>
+        <v>0.9089425774522214</v>
       </c>
       <c r="G73" s="3">
-        <v>-0.2210201772321563</v>
+        <v>-0.2005171720698029</v>
       </c>
       <c r="H73">
         <v>3</v>
       </c>
       <c r="I73" s="1">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="J73" s="2">
-        <v>0.8998137254901962</v>
+        <v>0.899813725490196</v>
       </c>
       <c r="K73" s="2">
         <v>0.8993585365914101</v>
       </c>
       <c r="L73" s="3">
-        <v>0.04551888987861519</v>
+        <v>0.04551888987859298</v>
       </c>
       <c r="M73">
         <v>3</v>
       </c>
       <c r="N73" s="1">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="O73" s="2">
         <v>0.9140610859728506</v>
@@ -57598,10 +57598,10 @@
         <v>8000</v>
       </c>
       <c r="F2">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="G2" s="5">
-        <v>3993</v>
+        <v>3994</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -57621,10 +57621,10 @@
         <v>7650</v>
       </c>
       <c r="F3">
-        <v>4070</v>
+        <v>4064</v>
       </c>
       <c r="G3" s="5">
-        <v>3580</v>
+        <v>3586</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -57644,10 +57644,10 @@
         <v>7700</v>
       </c>
       <c r="F4">
-        <v>1830</v>
+        <v>1823</v>
       </c>
       <c r="G4" s="5">
-        <v>5870</v>
+        <v>5877</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -57667,10 +57667,10 @@
         <v>6800</v>
       </c>
       <c r="F5">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G5" s="5">
-        <v>6271</v>
+        <v>6272</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -57736,10 +57736,10 @@
         <v>8000</v>
       </c>
       <c r="F8">
-        <v>1841</v>
+        <v>1832</v>
       </c>
       <c r="G8" s="5">
-        <v>6159</v>
+        <v>6168</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -57759,10 +57759,10 @@
         <v>6400</v>
       </c>
       <c r="F9">
-        <v>5135</v>
+        <v>5131</v>
       </c>
       <c r="G9" s="5">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -57782,10 +57782,10 @@
         <v>7700</v>
       </c>
       <c r="F10">
-        <v>4132</v>
+        <v>4133</v>
       </c>
       <c r="G10" s="5">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -57805,10 +57805,10 @@
         <v>5300</v>
       </c>
       <c r="F11">
-        <v>5112</v>
+        <v>5110</v>
       </c>
       <c r="G11" s="5">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -57828,10 +57828,10 @@
         <v>7750</v>
       </c>
       <c r="F12">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="G12" s="5">
-        <v>6132</v>
+        <v>6131</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -57851,10 +57851,10 @@
         <v>8000</v>
       </c>
       <c r="F13">
-        <v>4114</v>
+        <v>4096</v>
       </c>
       <c r="G13" s="5">
-        <v>3886</v>
+        <v>3904</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -57874,10 +57874,10 @@
         <v>8000</v>
       </c>
       <c r="F14">
-        <v>3124</v>
+        <v>3115</v>
       </c>
       <c r="G14" s="5">
-        <v>4876</v>
+        <v>4885</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -57897,10 +57897,10 @@
         <v>8000</v>
       </c>
       <c r="F15">
-        <v>5156</v>
+        <v>5154</v>
       </c>
       <c r="G15" s="5">
-        <v>2844</v>
+        <v>2846</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -57920,10 +57920,10 @@
         <v>7700</v>
       </c>
       <c r="F16">
-        <v>4334</v>
+        <v>4333</v>
       </c>
       <c r="G16" s="5">
-        <v>3366</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -57943,10 +57943,10 @@
         <v>8000</v>
       </c>
       <c r="F17">
-        <v>2149</v>
+        <v>2147</v>
       </c>
       <c r="G17" s="5">
-        <v>5851</v>
+        <v>5853</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -57966,10 +57966,10 @@
         <v>9600</v>
       </c>
       <c r="F18">
-        <v>1561</v>
+        <v>1552</v>
       </c>
       <c r="G18" s="5">
-        <v>8039</v>
+        <v>8048</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -57989,10 +57989,10 @@
         <v>9600</v>
       </c>
       <c r="F19">
-        <v>4595</v>
+        <v>4583</v>
       </c>
       <c r="G19" s="5">
-        <v>5005</v>
+        <v>5017</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -58012,10 +58012,10 @@
         <v>9600</v>
       </c>
       <c r="F20">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="G20" s="5">
-        <v>7181</v>
+        <v>7183</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -58058,10 +58058,10 @@
         <v>8000</v>
       </c>
       <c r="F22">
-        <v>1922</v>
+        <v>1918</v>
       </c>
       <c r="G22" s="5">
-        <v>6078</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -58081,10 +58081,10 @@
         <v>6750</v>
       </c>
       <c r="F23">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="G23" s="5">
-        <v>6423</v>
+        <v>6428</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -58104,10 +58104,10 @@
         <v>7700</v>
       </c>
       <c r="F24">
-        <v>3093</v>
+        <v>3096</v>
       </c>
       <c r="G24" s="5">
-        <v>4607</v>
+        <v>4604</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -58127,10 +58127,10 @@
         <v>8000</v>
       </c>
       <c r="F25">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G25" s="5">
-        <v>7814</v>
+        <v>7815</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -58150,10 +58150,10 @@
         <v>13350</v>
       </c>
       <c r="F26">
-        <v>5431</v>
+        <v>5430</v>
       </c>
       <c r="G26" s="5">
-        <v>7919</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -58196,10 +58196,10 @@
         <v>9600</v>
       </c>
       <c r="F28">
-        <v>4699</v>
+        <v>4695</v>
       </c>
       <c r="G28" s="5">
-        <v>4901</v>
+        <v>4905</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -58232,7 +58232,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" style="6" customWidth="1"/>
@@ -58254,27 +58254,27 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B2" s="6">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C2" s="6">
-        <v>507.3850170454548</v>
+        <v>1399.573670154844</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B3" s="6">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="C3" s="6">
-        <v>431.8586076388883</v>
+        <v>9600</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>36</v>
@@ -58282,13 +58282,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B4" s="6">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="C4" s="6">
-        <v>444.0350255952385</v>
+        <v>9600</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>36</v>
@@ -58296,99 +58296,43 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B5" s="6">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="C5" s="6">
-        <v>2027.414290277778</v>
+        <v>8000</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B6" s="6">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="C6" s="6">
-        <v>1399.381603273809</v>
+        <v>7750</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B7" s="6">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="C7" s="6">
-        <v>9600</v>
+        <v>6800</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="6">
-        <v>144</v>
-      </c>
-      <c r="C8" s="6">
-        <v>9600</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="6">
-        <v>151</v>
-      </c>
-      <c r="C9" s="6">
-        <v>8000</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="6">
-        <v>152</v>
-      </c>
-      <c r="C10" s="6">
-        <v>7750</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="6">
-        <v>155</v>
-      </c>
-      <c r="C11" s="6">
-        <v>6800</v>
-      </c>
-      <c r="D11" s="6" t="s">
         <v>37</v>
       </c>
     </row>

--- a/Waterjet Efficiency Shiftwise.xlsx
+++ b/Waterjet Efficiency Shiftwise.xlsx
@@ -718,22 +718,22 @@
         <v>6</v>
       </c>
       <c r="D2" s="1">
-        <v>1259</v>
+        <v>1244</v>
       </c>
       <c r="E2" s="2">
-        <v>0.84939271728015</v>
+        <v>0.8533013385569703</v>
       </c>
       <c r="F2" s="2">
-        <v>0.8748758910158874</v>
+        <v>0.8744496686743556</v>
       </c>
       <c r="G2" s="3">
-        <v>-2.548317373573739</v>
+        <v>-2.114833011738526</v>
       </c>
       <c r="H2">
         <v>6</v>
       </c>
       <c r="I2" s="1">
-        <v>716</v>
+        <v>656</v>
       </c>
       <c r="J2" s="2">
         <v>0.8106730957701204</v>
@@ -748,7 +748,7 @@
         <v>4</v>
       </c>
       <c r="N2" s="1">
-        <v>543</v>
+        <v>588</v>
       </c>
       <c r="O2" s="2">
         <v>0.9065115482481895</v>
@@ -771,22 +771,22 @@
         <v>3</v>
       </c>
       <c r="D3" s="1">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E3" s="2">
-        <v>0.9334555688214223</v>
+        <v>0.9316641260162603</v>
       </c>
       <c r="F3" s="2">
-        <v>0.8748758910158874</v>
+        <v>0.8744496686743556</v>
       </c>
       <c r="G3" s="3">
-        <v>5.857967780553497</v>
+        <v>5.721445734190467</v>
       </c>
       <c r="H3">
         <v>3</v>
       </c>
       <c r="I3" s="1">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="J3" s="2">
         <v>0.9549528824833702</v>
@@ -801,16 +801,16 @@
         <v>3</v>
       </c>
       <c r="N3" s="1">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="O3" s="2">
-        <v>0.9119582551594745</v>
+        <v>0.9119582551594746</v>
       </c>
       <c r="P3" s="2">
         <v>0.8697857416341145</v>
       </c>
       <c r="Q3" s="3">
-        <v>4.217251352536</v>
+        <v>4.217251352536011</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -824,46 +824,46 @@
         <v>4</v>
       </c>
       <c r="D4" s="1">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="E4" s="2">
-        <v>0.5616304095145965</v>
+        <v>0.5584273277439331</v>
       </c>
       <c r="F4" s="2">
-        <v>0.8748758910158874</v>
+        <v>0.8744496686743556</v>
       </c>
       <c r="G4" s="3">
-        <v>-31.32454815012908</v>
+        <v>-31.60223409304225</v>
       </c>
       <c r="H4">
         <v>2</v>
       </c>
       <c r="I4" s="1">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="J4" s="2">
-        <v>0.6186088351324402</v>
+        <v>0.6186088351324404</v>
       </c>
       <c r="K4" s="2">
         <v>0.8800198420557523</v>
       </c>
       <c r="L4" s="3">
-        <v>-26.14110069233121</v>
+        <v>-26.1411006923312</v>
       </c>
       <c r="M4">
         <v>4</v>
       </c>
       <c r="N4" s="1">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="O4" s="2">
-        <v>0.5314919914238869</v>
+        <v>0.531491991423887</v>
       </c>
       <c r="P4" s="2">
         <v>0.8697857416341145</v>
       </c>
       <c r="Q4" s="3">
-        <v>-33.82937502102276</v>
+        <v>-33.82937502102274</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -877,37 +877,37 @@
         <v>17</v>
       </c>
       <c r="D5" s="1">
-        <v>4374</v>
+        <v>4377</v>
       </c>
       <c r="E5" s="2">
-        <v>0.9473372393825916</v>
+        <v>0.948070827959247</v>
       </c>
       <c r="F5" s="2">
-        <v>0.8748758910158874</v>
+        <v>0.8744496686743556</v>
       </c>
       <c r="G5" s="3">
-        <v>7.246134836670426</v>
+        <v>7.362115928489144</v>
       </c>
       <c r="H5">
         <v>17</v>
       </c>
       <c r="I5" s="1">
-        <v>2167</v>
+        <v>1986</v>
       </c>
       <c r="J5" s="2">
-        <v>0.9385341764627285</v>
+        <v>0.9385341764627286</v>
       </c>
       <c r="K5" s="2">
         <v>0.8800198420557523</v>
       </c>
       <c r="L5" s="3">
-        <v>5.851433440697617</v>
+        <v>5.851433440697629</v>
       </c>
       <c r="M5">
         <v>17</v>
       </c>
       <c r="N5" s="1">
-        <v>2207</v>
+        <v>2391</v>
       </c>
       <c r="O5" s="2">
         <v>0.9561403023024546</v>
@@ -930,46 +930,46 @@
         <v>7</v>
       </c>
       <c r="D6" s="1">
-        <v>1626</v>
+        <v>1621</v>
       </c>
       <c r="E6" s="2">
-        <v>0.8597175401801566</v>
+        <v>0.8615203595178088</v>
       </c>
       <c r="F6" s="2">
-        <v>0.8379308364375717</v>
+        <v>0.8378258964871993</v>
       </c>
       <c r="G6" s="3">
-        <v>2.178670374258485</v>
+        <v>2.369446303060951</v>
       </c>
       <c r="H6">
         <v>7</v>
       </c>
       <c r="I6" s="1">
-        <v>847</v>
+        <v>776</v>
       </c>
       <c r="J6" s="2">
         <v>0.8395411981161869</v>
       </c>
       <c r="K6" s="2">
-        <v>0.8391880909312647</v>
+        <v>0.8391880909312648</v>
       </c>
       <c r="L6" s="3">
-        <v>0.03531071849222078</v>
+        <v>0.03531071849220968</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6" s="1">
-        <v>780</v>
+        <v>845</v>
       </c>
       <c r="O6" s="2">
-        <v>0.8827598102630445</v>
+        <v>0.8827598102630443</v>
       </c>
       <c r="P6" s="2">
         <v>0.8366698385455618</v>
       </c>
       <c r="Q6" s="3">
-        <v>4.608997171748275</v>
+        <v>4.608997171748253</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -983,28 +983,28 @@
         <v>18</v>
       </c>
       <c r="D7" s="1">
-        <v>4349</v>
+        <v>4356</v>
       </c>
       <c r="E7" s="2">
-        <v>0.9194427520485838</v>
+        <v>0.9190045408616682</v>
       </c>
       <c r="F7" s="2">
-        <v>0.8379308364375717</v>
+        <v>0.8378258964871993</v>
       </c>
       <c r="G7" s="3">
-        <v>8.151191561101212</v>
+        <v>8.117864437446887</v>
       </c>
       <c r="H7">
         <v>17</v>
       </c>
       <c r="I7" s="1">
-        <v>2135</v>
+        <v>1957</v>
       </c>
       <c r="J7" s="2">
-        <v>0.9248412315360933</v>
+        <v>0.9248412315360934</v>
       </c>
       <c r="K7" s="2">
-        <v>0.8391880909312647</v>
+        <v>0.8391880909312648</v>
       </c>
       <c r="L7" s="3">
         <v>8.565314060482866</v>
@@ -1013,7 +1013,7 @@
         <v>18</v>
       </c>
       <c r="N7" s="1">
-        <v>2214</v>
+        <v>2399</v>
       </c>
       <c r="O7" s="2">
         <v>0.9142970875366448</v>
@@ -1036,28 +1036,28 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E8" s="2">
-        <v>0.6097984243064334</v>
+        <v>0.6043295325986093</v>
       </c>
       <c r="F8" s="2">
-        <v>0.8379308364375717</v>
+        <v>0.8378258964871993</v>
       </c>
       <c r="G8" s="3">
-        <v>-22.81324121311383</v>
+        <v>-23.349636388859</v>
       </c>
       <c r="H8">
         <v>2</v>
       </c>
       <c r="I8" s="1">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="J8" s="2">
-        <v>0.6755228730939088</v>
+        <v>0.6755228730939089</v>
       </c>
       <c r="K8" s="2">
-        <v>0.8391880909312647</v>
+        <v>0.8391880909312648</v>
       </c>
       <c r="L8" s="3">
         <v>-16.36652178373559</v>
@@ -1066,7 +1066,7 @@
         <v>2</v>
       </c>
       <c r="N8" s="1">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="O8" s="2">
         <v>0.5442542070969859</v>
@@ -1089,37 +1089,37 @@
         <v>2</v>
       </c>
       <c r="D9" s="1">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E9" s="2">
-        <v>0.3733987698043492</v>
+        <v>0.3726340208233985</v>
       </c>
       <c r="F9" s="2">
-        <v>0.8379308364375717</v>
+        <v>0.8378258964871993</v>
       </c>
       <c r="G9" s="3">
-        <v>-46.45320666332226</v>
+        <v>-46.51918756638008</v>
       </c>
       <c r="H9">
         <v>2</v>
       </c>
       <c r="I9" s="1">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J9" s="2">
         <v>0.3825757575757576</v>
       </c>
       <c r="K9" s="2">
-        <v>0.8391880909312647</v>
+        <v>0.8391880909312648</v>
       </c>
       <c r="L9" s="3">
-        <v>-45.6612333355507</v>
+        <v>-45.66123333555072</v>
       </c>
       <c r="M9">
         <v>2</v>
       </c>
       <c r="N9" s="1">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="O9" s="2">
         <v>0.3642217820329408</v>
@@ -1142,43 +1142,43 @@
         <v>8</v>
       </c>
       <c r="D10" s="1">
-        <v>2040</v>
+        <v>2028</v>
       </c>
       <c r="E10" s="2">
-        <v>0.8730495920403999</v>
+        <v>0.867717908598996</v>
       </c>
       <c r="F10" s="2">
-        <v>0.8892476183952933</v>
+        <v>0.8877963428508072</v>
       </c>
       <c r="G10" s="3">
-        <v>-1.619802635489342</v>
+        <v>-2.007843425181122</v>
       </c>
       <c r="H10">
         <v>8</v>
       </c>
       <c r="I10" s="1">
-        <v>1095</v>
+        <v>1004</v>
       </c>
       <c r="J10" s="2">
         <v>0.937029793337245</v>
       </c>
       <c r="K10" s="2">
-        <v>0.9067056666109792</v>
+        <v>0.9067056666109793</v>
       </c>
       <c r="L10" s="3">
-        <v>3.032412672626583</v>
+        <v>3.032412672626572</v>
       </c>
       <c r="M10">
         <v>8</v>
       </c>
       <c r="N10" s="1">
-        <v>945</v>
+        <v>1024</v>
       </c>
       <c r="O10" s="2">
-        <v>0.8090693907435547</v>
+        <v>0.8090693907435546</v>
       </c>
       <c r="P10" s="2">
-        <v>0.8718683147728952</v>
+        <v>0.8718683147728951</v>
       </c>
       <c r="Q10" s="3">
         <v>-6.279892402934051</v>
@@ -1195,46 +1195,46 @@
         <v>18</v>
       </c>
       <c r="D11" s="1">
-        <v>4380</v>
+        <v>4382</v>
       </c>
       <c r="E11" s="2">
-        <v>0.9259057303431975</v>
+        <v>0.9245344703748343</v>
       </c>
       <c r="F11" s="2">
-        <v>0.8892476183952933</v>
+        <v>0.8877963428508072</v>
       </c>
       <c r="G11" s="3">
-        <v>3.665811194790414</v>
+        <v>3.673812752402705</v>
       </c>
       <c r="H11">
         <v>17</v>
       </c>
       <c r="I11" s="1">
-        <v>2176</v>
+        <v>1995</v>
       </c>
       <c r="J11" s="2">
-        <v>0.9427987696637025</v>
+        <v>0.9427987696637027</v>
       </c>
       <c r="K11" s="2">
-        <v>0.9067056666109792</v>
+        <v>0.9067056666109793</v>
       </c>
       <c r="L11" s="3">
-        <v>3.609310305272329</v>
+        <v>3.60931030527234</v>
       </c>
       <c r="M11">
         <v>18</v>
       </c>
       <c r="N11" s="1">
-        <v>2203</v>
+        <v>2387</v>
       </c>
       <c r="O11" s="2">
         <v>0.9098038051378817</v>
       </c>
       <c r="P11" s="2">
-        <v>0.8718683147728952</v>
+        <v>0.8718683147728951</v>
       </c>
       <c r="Q11" s="3">
-        <v>3.793549036498656</v>
+        <v>3.793549036498667</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1251,43 +1251,43 @@
         <v>145</v>
       </c>
       <c r="E12" s="2">
-        <v>0.505867756937439</v>
+        <v>0.5192243878584651</v>
       </c>
       <c r="F12" s="2">
-        <v>0.8892476183952933</v>
+        <v>0.8877963428508072</v>
       </c>
       <c r="G12" s="3">
-        <v>-38.33798614578543</v>
+        <v>-36.85719549923421</v>
       </c>
       <c r="H12">
         <v>2</v>
       </c>
       <c r="I12" s="1">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="J12" s="2">
-        <v>0.3890370246923868</v>
+        <v>0.3890370246923867</v>
       </c>
       <c r="K12" s="2">
-        <v>0.9067056666109792</v>
+        <v>0.9067056666109793</v>
       </c>
       <c r="L12" s="3">
-        <v>-51.76686419185924</v>
+        <v>-51.76686419185926</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
       <c r="N12" s="1">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O12" s="2">
-        <v>0.7397435897435897</v>
+        <v>0.7397435897435898</v>
       </c>
       <c r="P12" s="2">
-        <v>0.8718683147728952</v>
+        <v>0.8718683147728951</v>
       </c>
       <c r="Q12" s="3">
-        <v>-13.21247250293055</v>
+        <v>-13.21247250293053</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1301,46 +1301,46 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E13" s="2">
-        <v>0.8199112284949194</v>
+        <v>0.8215704975361628</v>
       </c>
       <c r="F13" s="2">
-        <v>0.8892476183952933</v>
+        <v>0.8877963428508072</v>
       </c>
       <c r="G13" s="3">
-        <v>-6.933638990037394</v>
+        <v>-6.622584531464437</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="I13" s="1">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J13" s="2">
-        <v>0.8</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="K13" s="2">
-        <v>0.9067056666109792</v>
+        <v>0.9067056666109793</v>
       </c>
       <c r="L13" s="3">
-        <v>-10.67056666109791</v>
+        <v>-10.67056666109794</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13" s="1">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2">
         <v>0.839822456989839</v>
       </c>
       <c r="P13" s="2">
-        <v>0.8718683147728952</v>
+        <v>0.8718683147728951</v>
       </c>
       <c r="Q13" s="3">
-        <v>-3.204585778305613</v>
+        <v>-3.204585778305602</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1354,28 +1354,28 @@
         <v>9</v>
       </c>
       <c r="D14" s="1">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="E14" s="2">
-        <v>0.8308405718627611</v>
+        <v>0.8334285107518109</v>
       </c>
       <c r="F14" s="2">
-        <v>0.8832310106190311</v>
+        <v>0.8820441438344169</v>
       </c>
       <c r="G14" s="3">
-        <v>-5.239043875627003</v>
+        <v>-4.861563308260597</v>
       </c>
       <c r="H14">
         <v>9</v>
       </c>
       <c r="I14" s="1">
-        <v>1036</v>
+        <v>950</v>
       </c>
       <c r="J14" s="2">
-        <v>0.8014056257163361</v>
+        <v>0.8014056257163362</v>
       </c>
       <c r="K14" s="2">
-        <v>0.8974165249242002</v>
+        <v>0.8974165249242003</v>
       </c>
       <c r="L14" s="3">
         <v>-9.601089920786411</v>
@@ -1384,16 +1384,16 @@
         <v>8</v>
       </c>
       <c r="N14" s="1">
-        <v>1009</v>
+        <v>1093</v>
       </c>
       <c r="O14" s="2">
-        <v>0.8634130196031233</v>
+        <v>0.8634130196031231</v>
       </c>
       <c r="P14" s="2">
-        <v>0.8689401163742244</v>
+        <v>0.8689401163742245</v>
       </c>
       <c r="Q14" s="3">
-        <v>-0.5527096771101081</v>
+        <v>-0.5527096771101414</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1407,43 +1407,43 @@
         <v>18</v>
       </c>
       <c r="D15" s="1">
-        <v>4513</v>
+        <v>4502</v>
       </c>
       <c r="E15" s="2">
-        <v>0.9317578224731498</v>
+        <v>0.9294131381574559</v>
       </c>
       <c r="F15" s="2">
-        <v>0.8832310106190311</v>
+        <v>0.8820441438344169</v>
       </c>
       <c r="G15" s="3">
-        <v>4.852681185411867</v>
+        <v>4.736899432303899</v>
       </c>
       <c r="H15">
         <v>18</v>
       </c>
       <c r="I15" s="1">
-        <v>2325</v>
+        <v>2131</v>
       </c>
       <c r="J15" s="2">
         <v>0.9598940342614757</v>
       </c>
       <c r="K15" s="2">
-        <v>0.8974165249242002</v>
+        <v>0.8974165249242003</v>
       </c>
       <c r="L15" s="3">
-        <v>6.247750933727547</v>
+        <v>6.247750933727536</v>
       </c>
       <c r="M15">
         <v>18</v>
       </c>
       <c r="N15" s="1">
-        <v>2188</v>
+        <v>2371</v>
       </c>
       <c r="O15" s="2">
-        <v>0.9036216106848236</v>
+        <v>0.9036216106848237</v>
       </c>
       <c r="P15" s="2">
-        <v>0.8689401163742244</v>
+        <v>0.8689401163742245</v>
       </c>
       <c r="Q15" s="3">
         <v>3.468149431059919</v>
@@ -1460,16 +1460,16 @@
         <v>1</v>
       </c>
       <c r="D16" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E16" s="2">
-        <v>0.2833333333333333</v>
+        <v>0.2833333333333334</v>
       </c>
       <c r="F16" s="2">
-        <v>0.8832310106190311</v>
+        <v>0.8820441438344169</v>
       </c>
       <c r="G16" s="3">
-        <v>-59.98976772856979</v>
+        <v>-59.87108105010834</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -1490,13 +1490,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O16" s="2">
-        <v>0.2833333333333333</v>
+        <v>0.2833333333333334</v>
       </c>
       <c r="P16" s="2">
-        <v>0.8689401163742244</v>
+        <v>0.8689401163742245</v>
       </c>
       <c r="Q16" s="3">
         <v>-58.56067830408911</v>
@@ -1516,43 +1516,43 @@
         <v>274</v>
       </c>
       <c r="E17" s="2">
-        <v>0.7499861607157744</v>
+        <v>0.7501112700683514</v>
       </c>
       <c r="F17" s="2">
-        <v>0.8832310106190311</v>
+        <v>0.8820441438344169</v>
       </c>
       <c r="G17" s="3">
-        <v>-13.32448499032567</v>
+        <v>-13.19328737660654</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="I17" s="1">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="J17" s="2">
-        <v>0.7484848484848485</v>
+        <v>0.7484848484848484</v>
       </c>
       <c r="K17" s="2">
-        <v>0.8974165249242002</v>
+        <v>0.8974165249242003</v>
       </c>
       <c r="L17" s="3">
-        <v>-14.89316764393517</v>
+        <v>-14.89316764393519</v>
       </c>
       <c r="M17">
         <v>1</v>
       </c>
       <c r="N17" s="1">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="O17" s="2">
         <v>0.7514874729467003</v>
       </c>
       <c r="P17" s="2">
-        <v>0.8689401163742244</v>
+        <v>0.8689401163742245</v>
       </c>
       <c r="Q17" s="3">
-        <v>-11.74526434275242</v>
+        <v>-11.74526434275243</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1566,37 +1566,37 @@
         <v>10</v>
       </c>
       <c r="D18" s="1">
-        <v>2263</v>
+        <v>2244</v>
       </c>
       <c r="E18" s="2">
-        <v>0.8242827196385248</v>
+        <v>0.8211863127057473</v>
       </c>
       <c r="F18" s="2">
-        <v>0.8854281330823822</v>
+        <v>0.8830321953349407</v>
       </c>
       <c r="G18" s="3">
-        <v>-6.114541344385738</v>
+        <v>-6.184588262919344</v>
       </c>
       <c r="H18">
         <v>10</v>
       </c>
       <c r="I18" s="1">
-        <v>1248</v>
+        <v>1144</v>
       </c>
       <c r="J18" s="2">
-        <v>0.8592265267111892</v>
+        <v>0.8592265267111894</v>
       </c>
       <c r="K18" s="2">
         <v>0.9142711014561837</v>
       </c>
       <c r="L18" s="3">
-        <v>-5.504457474499458</v>
+        <v>-5.504457474499436</v>
       </c>
       <c r="M18">
         <v>9</v>
       </c>
       <c r="N18" s="1">
-        <v>1015</v>
+        <v>1099</v>
       </c>
       <c r="O18" s="2">
         <v>0.7850218886804252</v>
@@ -1622,19 +1622,19 @@
         <v>4584</v>
       </c>
       <c r="E19" s="2">
-        <v>0.9464569374360094</v>
+        <v>0.9463879239690844</v>
       </c>
       <c r="F19" s="2">
-        <v>0.8854281330823822</v>
+        <v>0.8830321953349407</v>
       </c>
       <c r="G19" s="3">
-        <v>6.102880435362723</v>
+        <v>6.335572863414374</v>
       </c>
       <c r="H19">
         <v>18</v>
       </c>
       <c r="I19" s="1">
-        <v>2294</v>
+        <v>2103</v>
       </c>
       <c r="J19" s="2">
         <v>0.9472850990391087</v>
@@ -1649,16 +1649,16 @@
         <v>18</v>
       </c>
       <c r="N19" s="1">
-        <v>2290</v>
+        <v>2481</v>
       </c>
       <c r="O19" s="2">
-        <v>0.9456287758329098</v>
+        <v>0.9456287758329101</v>
       </c>
       <c r="P19" s="2">
         <v>0.8567540311007951</v>
       </c>
       <c r="Q19" s="3">
-        <v>8.887474473211476</v>
+        <v>8.887474473211498</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1672,16 +1672,16 @@
         <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2">
         <v>0.1856314882065955</v>
       </c>
       <c r="F20" s="2">
-        <v>0.8854281330823822</v>
+        <v>0.8830321953349407</v>
       </c>
       <c r="G20" s="3">
-        <v>-69.97966448757866</v>
+        <v>-69.74007071283452</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1702,7 +1702,7 @@
         <v>1</v>
       </c>
       <c r="N20" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O20" s="2">
         <v>0.1856314882065955</v>
@@ -1725,37 +1725,37 @@
         <v>10</v>
       </c>
       <c r="D21" s="1">
-        <v>2575</v>
+        <v>2567</v>
       </c>
       <c r="E21" s="2">
-        <v>0.8864505493457829</v>
+        <v>0.8835069171342177</v>
       </c>
       <c r="F21" s="2">
-        <v>0.900596320229565</v>
+        <v>0.900363951394849</v>
       </c>
       <c r="G21" s="3">
-        <v>-1.414577088378211</v>
+        <v>-1.685703426063134</v>
       </c>
       <c r="H21">
         <v>10</v>
       </c>
       <c r="I21" s="1">
-        <v>1339</v>
+        <v>1227</v>
       </c>
       <c r="J21" s="2">
         <v>0.9217741358845654</v>
       </c>
       <c r="K21" s="2">
-        <v>0.9033915164078746</v>
+        <v>0.9033915164078745</v>
       </c>
       <c r="L21" s="3">
-        <v>1.838261947669073</v>
+        <v>1.838261947669084</v>
       </c>
       <c r="M21">
         <v>10</v>
       </c>
       <c r="N21" s="1">
-        <v>1236</v>
+        <v>1339</v>
       </c>
       <c r="O21" s="2">
         <v>0.8511269628070005</v>
@@ -1778,46 +1778,46 @@
         <v>18</v>
       </c>
       <c r="D22" s="1">
-        <v>4311</v>
+        <v>4325</v>
       </c>
       <c r="E22" s="2">
-        <v>0.911121537870012</v>
+        <v>0.9123725801641929</v>
       </c>
       <c r="F22" s="2">
-        <v>0.900596320229565</v>
+        <v>0.900363951394849</v>
       </c>
       <c r="G22" s="3">
-        <v>1.0525217640447</v>
+        <v>1.200862876934383</v>
       </c>
       <c r="H22">
         <v>17</v>
       </c>
       <c r="I22" s="1">
-        <v>2069</v>
+        <v>1896</v>
       </c>
       <c r="J22" s="2">
-        <v>0.8957133395476622</v>
+        <v>0.8957133395476624</v>
       </c>
       <c r="K22" s="2">
-        <v>0.9033915164078746</v>
+        <v>0.9033915164078745</v>
       </c>
       <c r="L22" s="3">
-        <v>-0.7678176860212438</v>
+        <v>-0.7678176860212105</v>
       </c>
       <c r="M22">
         <v>18</v>
       </c>
       <c r="N22" s="1">
-        <v>2242</v>
+        <v>2429</v>
       </c>
       <c r="O22" s="2">
-        <v>0.9258147661870106</v>
+        <v>0.9258147661870108</v>
       </c>
       <c r="P22" s="2">
         <v>0.8978135972482332</v>
       </c>
       <c r="Q22" s="3">
-        <v>2.800116893877747</v>
+        <v>2.800116893877758</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -1831,31 +1831,31 @@
         <v>1</v>
       </c>
       <c r="D23" s="1">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E23" s="2">
-        <v>0.8090685038929032</v>
+        <v>0.8090685038929034</v>
       </c>
       <c r="F23" s="2">
-        <v>0.900596320229565</v>
+        <v>0.900363951394849</v>
       </c>
       <c r="G23" s="3">
-        <v>-9.152781633666185</v>
+        <v>-9.129544750194562</v>
       </c>
       <c r="H23">
         <v>1</v>
       </c>
       <c r="I23" s="1">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="J23" s="2">
-        <v>0.8090685038929032</v>
+        <v>0.8090685038929034</v>
       </c>
       <c r="K23" s="2">
-        <v>0.9033915164078746</v>
+        <v>0.9033915164078745</v>
       </c>
       <c r="L23" s="3">
-        <v>-9.432301251497144</v>
+        <v>-9.43230125149711</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -1887,43 +1887,43 @@
         <v>2666</v>
       </c>
       <c r="E24" s="2">
-        <v>0.9178438558452716</v>
+        <v>0.9177074047856255</v>
       </c>
       <c r="F24" s="2">
-        <v>0.8976433816886573</v>
+        <v>0.897420995390633</v>
       </c>
       <c r="G24" s="3">
-        <v>2.02004741566143</v>
+        <v>2.028640939499249</v>
       </c>
       <c r="H24">
         <v>10</v>
       </c>
       <c r="I24" s="1">
-        <v>1336</v>
+        <v>1224</v>
       </c>
       <c r="J24" s="2">
         <v>0.9194812685610232</v>
       </c>
       <c r="K24" s="2">
-        <v>0.9003120172649495</v>
+        <v>0.9003120172649496</v>
       </c>
       <c r="L24" s="3">
-        <v>1.916925129607372</v>
+        <v>1.916925129607361</v>
       </c>
       <c r="M24">
         <v>10</v>
       </c>
       <c r="N24" s="1">
-        <v>1331</v>
+        <v>1442</v>
       </c>
       <c r="O24" s="2">
-        <v>0.9162064431295202</v>
+        <v>0.91620644312952</v>
       </c>
       <c r="P24" s="2">
-        <v>0.8949747461123653</v>
+        <v>0.8949747461123654</v>
       </c>
       <c r="Q24" s="3">
-        <v>2.123169701715488</v>
+        <v>2.123169701715466</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -1937,28 +1937,28 @@
         <v>17</v>
       </c>
       <c r="D25" s="1">
-        <v>4079</v>
+        <v>4078</v>
       </c>
       <c r="E25" s="2">
-        <v>0.8829938672288915</v>
+        <v>0.8827683711099118</v>
       </c>
       <c r="F25" s="2">
-        <v>0.8976433816886573</v>
+        <v>0.897420995390633</v>
       </c>
       <c r="G25" s="3">
-        <v>-1.464951445976581</v>
+        <v>-1.465262428072123</v>
       </c>
       <c r="H25">
         <v>17</v>
       </c>
       <c r="I25" s="1">
-        <v>2046</v>
+        <v>1875</v>
       </c>
       <c r="J25" s="2">
-        <v>0.8856998206566474</v>
+        <v>0.8856998206566475</v>
       </c>
       <c r="K25" s="2">
-        <v>0.9003120172649495</v>
+        <v>0.9003120172649496</v>
       </c>
       <c r="L25" s="3">
         <v>-1.461219660830204</v>
@@ -1967,16 +1967,16 @@
         <v>17</v>
       </c>
       <c r="N25" s="1">
-        <v>2033</v>
+        <v>2202</v>
       </c>
       <c r="O25" s="2">
         <v>0.8802879138011356</v>
       </c>
       <c r="P25" s="2">
-        <v>0.8949747461123653</v>
+        <v>0.8949747461123654</v>
       </c>
       <c r="Q25" s="3">
-        <v>-1.468683231122969</v>
+        <v>-1.46868323112298</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -1990,46 +1990,46 @@
         <v>1</v>
       </c>
       <c r="D26" s="1">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E26" s="2">
-        <v>0.9448668398760819</v>
+        <v>0.9434072704867532</v>
       </c>
       <c r="F26" s="2">
-        <v>0.8976433816886573</v>
+        <v>0.897420995390633</v>
       </c>
       <c r="G26" s="3">
-        <v>4.722345818742458</v>
+        <v>4.598627509612019</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26" s="1">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="J26" s="2">
-        <v>0.962381672548031</v>
+        <v>0.9623816725480314</v>
       </c>
       <c r="K26" s="2">
-        <v>0.9003120172649495</v>
+        <v>0.9003120172649496</v>
       </c>
       <c r="L26" s="3">
-        <v>6.20696552830815</v>
+        <v>6.206965528308183</v>
       </c>
       <c r="M26">
         <v>1</v>
       </c>
       <c r="N26" s="1">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="O26" s="2">
-        <v>0.9273520072041328</v>
+        <v>0.927352007204133</v>
       </c>
       <c r="P26" s="2">
-        <v>0.8949747461123653</v>
+        <v>0.8949747461123654</v>
       </c>
       <c r="Q26" s="3">
-        <v>3.237726109176753</v>
+        <v>3.237726109176764</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -2043,43 +2043,43 @@
         <v>10</v>
       </c>
       <c r="D27" s="1">
-        <v>2553</v>
+        <v>2559</v>
       </c>
       <c r="E27" s="2">
-        <v>0.8786414348589903</v>
+        <v>0.8808554218446855</v>
       </c>
       <c r="F27" s="2">
-        <v>0.9089816498597452</v>
+        <v>0.9107816193810581</v>
       </c>
       <c r="G27" s="3">
-        <v>-3.03402150007549</v>
+        <v>-2.99261975363726</v>
       </c>
       <c r="H27">
         <v>10</v>
       </c>
       <c r="I27" s="1">
-        <v>1238</v>
+        <v>1135</v>
       </c>
       <c r="J27" s="2">
-        <v>0.8520735910306462</v>
+        <v>0.8520735910306463</v>
       </c>
       <c r="K27" s="2">
         <v>0.8873820156039891</v>
       </c>
       <c r="L27" s="3">
-        <v>-3.530842457334293</v>
+        <v>-3.530842457334282</v>
       </c>
       <c r="M27">
         <v>10</v>
       </c>
       <c r="N27" s="1">
-        <v>1315</v>
+        <v>1424</v>
       </c>
       <c r="O27" s="2">
-        <v>0.9052092786873343</v>
+        <v>0.9052092786873344</v>
       </c>
       <c r="P27" s="2">
-        <v>0.9305812841155011</v>
+        <v>0.9305812841155012</v>
       </c>
       <c r="Q27" s="3">
         <v>-2.537200542816687</v>
@@ -2096,22 +2096,22 @@
         <v>17</v>
       </c>
       <c r="D28" s="1">
-        <v>4283</v>
+        <v>4290</v>
       </c>
       <c r="E28" s="2">
-        <v>0.927226114564215</v>
+        <v>0.9287760963202814</v>
       </c>
       <c r="F28" s="2">
-        <v>0.9089816498597452</v>
+        <v>0.9107816193810581</v>
       </c>
       <c r="G28" s="3">
-        <v>1.824446470446983</v>
+        <v>1.799447693922329</v>
       </c>
       <c r="H28">
         <v>17</v>
       </c>
       <c r="I28" s="1">
-        <v>2098</v>
+        <v>1924</v>
       </c>
       <c r="J28" s="2">
         <v>0.9086263334914172</v>
@@ -2126,16 +2126,16 @@
         <v>17</v>
       </c>
       <c r="N28" s="1">
-        <v>2184</v>
+        <v>2366</v>
       </c>
       <c r="O28" s="2">
         <v>0.9458258956370127</v>
       </c>
       <c r="P28" s="2">
-        <v>0.9305812841155011</v>
+        <v>0.9305812841155012</v>
       </c>
       <c r="Q28" s="3">
-        <v>1.524461152151158</v>
+        <v>1.524461152151146</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2152,43 +2152,43 @@
         <v>177</v>
       </c>
       <c r="E29" s="2">
-        <v>0.9293370215736204</v>
+        <v>0.9308841651263093</v>
       </c>
       <c r="F29" s="2">
-        <v>0.9089816498597452</v>
+        <v>0.9107816193810581</v>
       </c>
       <c r="G29" s="3">
-        <v>2.035537171387525</v>
+        <v>2.010254574525128</v>
       </c>
       <c r="H29">
         <v>1</v>
       </c>
       <c r="I29" s="1">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="J29" s="2">
-        <v>0.9107712989413542</v>
+        <v>0.9107712989413546</v>
       </c>
       <c r="K29" s="2">
         <v>0.8873820156039891</v>
       </c>
       <c r="L29" s="3">
-        <v>2.338928333736512</v>
+        <v>2.338928333736545</v>
       </c>
       <c r="M29">
         <v>1</v>
       </c>
       <c r="N29" s="1">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="O29" s="2">
         <v>0.9479027442058864</v>
       </c>
       <c r="P29" s="2">
-        <v>0.9305812841155011</v>
+        <v>0.9305812841155012</v>
       </c>
       <c r="Q29" s="3">
-        <v>1.732146009038527</v>
+        <v>1.732146009038515</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2202,46 +2202,46 @@
         <v>10</v>
       </c>
       <c r="D30" s="1">
-        <v>2624</v>
+        <v>2618</v>
       </c>
       <c r="E30" s="2">
-        <v>0.903181871350819</v>
+        <v>0.9012379179557094</v>
       </c>
       <c r="F30" s="2">
-        <v>0.8899624718866596</v>
+        <v>0.8892359879245889</v>
       </c>
       <c r="G30" s="3">
-        <v>1.32193994641594</v>
+        <v>1.200193003112049</v>
       </c>
       <c r="H30">
         <v>10</v>
       </c>
       <c r="I30" s="1">
-        <v>1346</v>
+        <v>1234</v>
       </c>
       <c r="J30" s="2">
-        <v>0.9265093120921341</v>
+        <v>0.9265093120921343</v>
       </c>
       <c r="K30" s="2">
-        <v>0.8987016100814504</v>
+        <v>0.8987016100814506</v>
       </c>
       <c r="L30" s="3">
-        <v>2.780770201068361</v>
+        <v>2.780770201068372</v>
       </c>
       <c r="M30">
         <v>10</v>
       </c>
       <c r="N30" s="1">
-        <v>1278</v>
+        <v>1385</v>
       </c>
       <c r="O30" s="2">
         <v>0.8798544306095037</v>
       </c>
       <c r="P30" s="2">
-        <v>0.8812626321898004</v>
+        <v>0.8812626321898005</v>
       </c>
       <c r="Q30" s="3">
-        <v>-0.1408201580296642</v>
+        <v>-0.1408201580296753</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2255,28 +2255,28 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E31" s="2">
-        <v>0.6968224669941409</v>
+        <v>0.6823299157526626</v>
       </c>
       <c r="F31" s="2">
-        <v>0.8899624718866596</v>
+        <v>0.8892359879245889</v>
       </c>
       <c r="G31" s="3">
-        <v>-19.31400048925187</v>
+        <v>-20.69060721719264</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31" s="1">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="J31" s="2">
-        <v>0.8707330818918803</v>
+        <v>0.8707330818918804</v>
       </c>
       <c r="K31" s="2">
-        <v>0.8987016100814504</v>
+        <v>0.8987016100814506</v>
       </c>
       <c r="L31" s="3">
         <v>-2.796852818957019</v>
@@ -2285,16 +2285,16 @@
         <v>1</v>
       </c>
       <c r="N31" s="1">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="O31" s="2">
-        <v>0.5229118520964015</v>
+        <v>0.5229118520964013</v>
       </c>
       <c r="P31" s="2">
-        <v>0.8812626321898004</v>
+        <v>0.8812626321898005</v>
       </c>
       <c r="Q31" s="3">
-        <v>-35.8350780093399</v>
+        <v>-35.83507800933992</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2308,46 +2308,46 @@
         <v>16</v>
       </c>
       <c r="D32" s="1">
-        <v>3809</v>
+        <v>3820</v>
       </c>
       <c r="E32" s="2">
-        <v>0.9037525403789572</v>
+        <v>0.9042387895378126</v>
       </c>
       <c r="F32" s="2">
-        <v>0.8899624718866596</v>
+        <v>0.8892359879245889</v>
       </c>
       <c r="G32" s="3">
-        <v>1.379006849229769</v>
+        <v>1.500280161322365</v>
       </c>
       <c r="H32">
         <v>15</v>
       </c>
       <c r="I32" s="1">
-        <v>1841</v>
+        <v>1687</v>
       </c>
       <c r="J32" s="2">
-        <v>0.8977420850179436</v>
+        <v>0.8977420850179435</v>
       </c>
       <c r="K32" s="2">
-        <v>0.8987016100814504</v>
+        <v>0.8987016100814506</v>
       </c>
       <c r="L32" s="3">
-        <v>-0.09595250635068275</v>
+        <v>-0.09595250635070496</v>
       </c>
       <c r="M32">
         <v>16</v>
       </c>
       <c r="N32" s="1">
-        <v>1968</v>
+        <v>2132</v>
       </c>
       <c r="O32" s="2">
         <v>0.9094468685168369</v>
       </c>
       <c r="P32" s="2">
-        <v>0.8812626321898004</v>
+        <v>0.8812626321898005</v>
       </c>
       <c r="Q32" s="3">
-        <v>2.818423632703648</v>
+        <v>2.818423632703637</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2361,43 +2361,43 @@
         <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E33" s="2">
-        <v>0.7991594806011983</v>
+        <v>0.8076977698295813</v>
       </c>
       <c r="F33" s="2">
-        <v>0.8899624718866596</v>
+        <v>0.8892359879245889</v>
       </c>
       <c r="G33" s="3">
-        <v>-9.080299128546121</v>
+        <v>-8.15382180950076</v>
       </c>
       <c r="H33">
         <v>2</v>
       </c>
       <c r="I33" s="1">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="J33" s="2">
         <v>0.7246278209088127</v>
       </c>
       <c r="K33" s="2">
-        <v>0.8987016100814504</v>
+        <v>0.8987016100814506</v>
       </c>
       <c r="L33" s="3">
-        <v>-17.40737891726377</v>
+        <v>-17.40737891726378</v>
       </c>
       <c r="M33">
         <v>1</v>
       </c>
       <c r="N33" s="1">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="O33" s="2">
-        <v>0.949187165268496</v>
+        <v>0.9491871652684961</v>
       </c>
       <c r="P33" s="2">
-        <v>0.8812626321898004</v>
+        <v>0.8812626321898005</v>
       </c>
       <c r="Q33" s="3">
         <v>6.792453307869561</v>
@@ -2414,37 +2414,37 @@
         <v>11</v>
       </c>
       <c r="D34" s="1">
-        <v>2846</v>
+        <v>2850</v>
       </c>
       <c r="E34" s="2">
-        <v>0.9026263386372083</v>
+        <v>0.9036828703703704</v>
       </c>
       <c r="F34" s="2">
-        <v>0.8989994739016479</v>
+        <v>0.8987230663251737</v>
       </c>
       <c r="G34" s="3">
-        <v>0.3626864735560398</v>
+        <v>0.4959804045196692</v>
       </c>
       <c r="H34">
         <v>11</v>
       </c>
       <c r="I34" s="1">
-        <v>1403</v>
+        <v>1286</v>
       </c>
       <c r="J34" s="2">
-        <v>0.8899479578392622</v>
+        <v>0.8899479578392623</v>
       </c>
       <c r="K34" s="2">
-        <v>0.9023163648193399</v>
+        <v>0.9023163648193397</v>
       </c>
       <c r="L34" s="3">
-        <v>-1.236840698007768</v>
+        <v>-1.236840698007746</v>
       </c>
       <c r="M34">
         <v>11</v>
       </c>
       <c r="N34" s="1">
-        <v>1443</v>
+        <v>1563</v>
       </c>
       <c r="O34" s="2">
         <v>0.9153047194351542</v>
@@ -2467,37 +2467,37 @@
         <v>1</v>
       </c>
       <c r="D35" s="1">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E35" s="2">
-        <v>0.9134381117213735</v>
+        <v>0.9146836750914006</v>
       </c>
       <c r="F35" s="2">
-        <v>0.8989994739016479</v>
+        <v>0.8987230663251737</v>
       </c>
       <c r="G35" s="3">
-        <v>1.443863781972554</v>
+        <v>1.596060876622685</v>
       </c>
       <c r="H35">
         <v>1</v>
       </c>
       <c r="I35" s="1">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="J35" s="2">
-        <v>0.8984913512810507</v>
+        <v>0.898491351281051</v>
       </c>
       <c r="K35" s="2">
-        <v>0.9023163648193399</v>
+        <v>0.9023163648193397</v>
       </c>
       <c r="L35" s="3">
-        <v>-0.3825013538289124</v>
+        <v>-0.3825013538288791</v>
       </c>
       <c r="M35">
         <v>1</v>
       </c>
       <c r="N35" s="1">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="O35" s="2">
         <v>0.9283848721616962</v>
@@ -2520,37 +2520,37 @@
         <v>14</v>
       </c>
       <c r="D36" s="1">
-        <v>3463</v>
+        <v>3457</v>
       </c>
       <c r="E36" s="2">
-        <v>0.893674513558197</v>
+        <v>0.8920566960882409</v>
       </c>
       <c r="F36" s="2">
-        <v>0.8989994739016479</v>
+        <v>0.8987230663251737</v>
       </c>
       <c r="G36" s="3">
-        <v>-0.5324960343450869</v>
+        <v>-0.6666370236932839</v>
       </c>
       <c r="H36">
         <v>14</v>
       </c>
       <c r="I36" s="1">
-        <v>1769</v>
+        <v>1622</v>
       </c>
       <c r="J36" s="2">
-        <v>0.9130883231976713</v>
+        <v>0.9130883231976714</v>
       </c>
       <c r="K36" s="2">
-        <v>0.9023163648193399</v>
+        <v>0.9023163648193397</v>
       </c>
       <c r="L36" s="3">
-        <v>1.077195837833145</v>
+        <v>1.077195837833167</v>
       </c>
       <c r="M36">
         <v>14</v>
       </c>
       <c r="N36" s="1">
-        <v>1694</v>
+        <v>1835</v>
       </c>
       <c r="O36" s="2">
         <v>0.8742607039187227</v>
@@ -2576,34 +2576,34 @@
         <v>348</v>
       </c>
       <c r="E37" s="2">
-        <v>0.9092608646327653</v>
+        <v>0.9101328946025917</v>
       </c>
       <c r="F37" s="2">
-        <v>0.8989994739016479</v>
+        <v>0.8987230663251737</v>
       </c>
       <c r="G37" s="3">
-        <v>1.026139073111743</v>
+        <v>1.140982827741799</v>
       </c>
       <c r="H37">
         <v>2</v>
       </c>
       <c r="I37" s="1">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="J37" s="2">
-        <v>0.8987965049948521</v>
+        <v>0.8987965049948522</v>
       </c>
       <c r="K37" s="2">
-        <v>0.9023163648193399</v>
+        <v>0.9023163648193397</v>
       </c>
       <c r="L37" s="3">
-        <v>-0.351985982448777</v>
+        <v>-0.3519859824487548</v>
       </c>
       <c r="M37">
         <v>2</v>
       </c>
       <c r="N37" s="1">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="O37" s="2">
         <v>0.9197252242706788</v>
@@ -2626,46 +2626,46 @@
         <v>11</v>
       </c>
       <c r="D38" s="1">
-        <v>2711</v>
+        <v>2700</v>
       </c>
       <c r="E38" s="2">
-        <v>0.8597541214823824</v>
+        <v>0.8561875</v>
       </c>
       <c r="F38" s="2">
-        <v>0.9011232026280093</v>
+        <v>0.9004013768967175</v>
       </c>
       <c r="G38" s="3">
-        <v>-4.136908114562687</v>
+        <v>-4.421387689671752</v>
       </c>
       <c r="H38">
         <v>11</v>
       </c>
       <c r="I38" s="1">
-        <v>1423</v>
+        <v>1304</v>
       </c>
       <c r="J38" s="2">
         <v>0.9025535792709706</v>
       </c>
       <c r="K38" s="2">
-        <v>0.9097851114035129</v>
+        <v>0.909785111403513</v>
       </c>
       <c r="L38" s="3">
-        <v>-0.7231532132542351</v>
+        <v>-0.7231532132542462</v>
       </c>
       <c r="M38">
         <v>11</v>
       </c>
       <c r="N38" s="1">
-        <v>1288</v>
+        <v>1395</v>
       </c>
       <c r="O38" s="2">
         <v>0.8169546636937941</v>
       </c>
       <c r="P38" s="2">
-        <v>0.8924612938525056</v>
+        <v>0.8924612938525057</v>
       </c>
       <c r="Q38" s="3">
-        <v>-7.550663015871151</v>
+        <v>-7.550663015871162</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -2679,46 +2679,46 @@
         <v>1</v>
       </c>
       <c r="D39" s="1">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E39" s="2">
-        <v>0.8914113068619506</v>
+        <v>0.8932562390716896</v>
       </c>
       <c r="F39" s="2">
-        <v>0.9011232026280093</v>
+        <v>0.9004013768967175</v>
       </c>
       <c r="G39" s="3">
-        <v>-0.9711895766058687</v>
+        <v>-0.7145137825027903</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39" s="1">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="J39" s="2">
         <v>0.8692721203450816</v>
       </c>
       <c r="K39" s="2">
-        <v>0.9097851114035129</v>
+        <v>0.909785111403513</v>
       </c>
       <c r="L39" s="3">
-        <v>-4.051299105843132</v>
+        <v>-4.051299105843142</v>
       </c>
       <c r="M39">
         <v>1</v>
       </c>
       <c r="N39" s="1">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="O39" s="2">
-        <v>0.9135504933788197</v>
+        <v>0.9135504933788196</v>
       </c>
       <c r="P39" s="2">
-        <v>0.8924612938525056</v>
+        <v>0.8924612938525057</v>
       </c>
       <c r="Q39" s="3">
-        <v>2.108919952631405</v>
+        <v>2.108919952631383</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -2732,46 +2732,46 @@
         <v>14</v>
       </c>
       <c r="D40" s="1">
-        <v>3627</v>
+        <v>3631</v>
       </c>
       <c r="E40" s="2">
-        <v>0.9358336194608706</v>
+        <v>0.9370332898561082</v>
       </c>
       <c r="F40" s="2">
-        <v>0.9011232026280093</v>
+        <v>0.9004013768967175</v>
       </c>
       <c r="G40" s="3">
-        <v>3.471041683286136</v>
+        <v>3.663191295939072</v>
       </c>
       <c r="H40">
         <v>14</v>
       </c>
       <c r="I40" s="1">
-        <v>1785</v>
+        <v>1637</v>
       </c>
       <c r="J40" s="2">
         <v>0.9214375747180207</v>
       </c>
       <c r="K40" s="2">
-        <v>0.9097851114035129</v>
+        <v>0.909785111403513</v>
       </c>
       <c r="L40" s="3">
-        <v>1.165246331450775</v>
+        <v>1.165246331450764</v>
       </c>
       <c r="M40">
         <v>14</v>
       </c>
       <c r="N40" s="1">
-        <v>1841</v>
+        <v>1995</v>
       </c>
       <c r="O40" s="2">
         <v>0.9502296642037207</v>
       </c>
       <c r="P40" s="2">
-        <v>0.8924612938525056</v>
+        <v>0.8924612938525057</v>
       </c>
       <c r="Q40" s="3">
-        <v>5.776837035121507</v>
+        <v>5.776837035121495</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -2785,46 +2785,46 @@
         <v>2</v>
       </c>
       <c r="D41" s="1">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E41" s="2">
-        <v>0.8997632074078353</v>
+        <v>0.900574558718498</v>
       </c>
       <c r="F41" s="2">
-        <v>0.9011232026280093</v>
+        <v>0.9004013768967175</v>
       </c>
       <c r="G41" s="3">
-        <v>-0.1359995220173937</v>
+        <v>0.01731818217804992</v>
       </c>
       <c r="H41">
         <v>2</v>
       </c>
       <c r="I41" s="1">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="J41" s="2">
-        <v>0.8900269916798841</v>
+        <v>0.8900269916798843</v>
       </c>
       <c r="K41" s="2">
-        <v>0.9097851114035129</v>
+        <v>0.909785111403513</v>
       </c>
       <c r="L41" s="3">
-        <v>-1.975811972362884</v>
+        <v>-1.975811972362873</v>
       </c>
       <c r="M41">
         <v>2</v>
       </c>
       <c r="N41" s="1">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="O41" s="2">
         <v>0.9094994231357866</v>
       </c>
       <c r="P41" s="2">
-        <v>0.8924612938525056</v>
+        <v>0.8924612938525057</v>
       </c>
       <c r="Q41" s="3">
-        <v>1.703812928328097</v>
+        <v>1.703812928328086</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -2838,46 +2838,46 @@
         <v>11</v>
       </c>
       <c r="D42" s="1">
-        <v>2798</v>
+        <v>2800</v>
       </c>
       <c r="E42" s="2">
-        <v>0.8874809381439817</v>
+        <v>0.8879067028985507</v>
       </c>
       <c r="F42" s="2">
-        <v>0.8896079030766169</v>
+        <v>0.8904269118708189</v>
       </c>
       <c r="G42" s="3">
-        <v>-0.21269649326352</v>
+        <v>-0.2520208972268234</v>
       </c>
       <c r="H42">
         <v>11</v>
       </c>
       <c r="I42" s="1">
-        <v>1391</v>
+        <v>1275</v>
       </c>
       <c r="J42" s="2">
-        <v>0.8823717610891525</v>
+        <v>0.8823717610891524</v>
       </c>
       <c r="K42" s="2">
         <v>0.8797797975461918</v>
       </c>
       <c r="L42" s="3">
-        <v>0.2591963542960651</v>
+        <v>0.259196354296054</v>
       </c>
       <c r="M42">
         <v>11</v>
       </c>
       <c r="N42" s="1">
-        <v>1407</v>
+        <v>1525</v>
       </c>
       <c r="O42" s="2">
-        <v>0.8925901151988109</v>
+        <v>0.8925901151988108</v>
       </c>
       <c r="P42" s="2">
         <v>0.8994360086070419</v>
       </c>
       <c r="Q42" s="3">
-        <v>-0.6845893408230941</v>
+        <v>-0.6845893408231052</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -2891,46 +2891,46 @@
         <v>1</v>
       </c>
       <c r="D43" s="1">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E43" s="2">
-        <v>0.8524710625568995</v>
+        <v>0.8550886186615799</v>
       </c>
       <c r="F43" s="2">
-        <v>0.8896079030766169</v>
+        <v>0.8904269118708189</v>
       </c>
       <c r="G43" s="3">
-        <v>-3.713684051971733</v>
+        <v>-3.533829320923898</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43" s="1">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="J43" s="2">
-        <v>0.8210603893007328</v>
+        <v>0.8210603893007326</v>
       </c>
       <c r="K43" s="2">
         <v>0.8797797975461918</v>
       </c>
       <c r="L43" s="3">
-        <v>-5.871940824545907</v>
+        <v>-5.871940824545929</v>
       </c>
       <c r="M43">
         <v>1</v>
       </c>
       <c r="N43" s="1">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="O43" s="2">
-        <v>0.8838817358130663</v>
+        <v>0.8838817358130662</v>
       </c>
       <c r="P43" s="2">
         <v>0.8994360086070419</v>
       </c>
       <c r="Q43" s="3">
-        <v>-1.555427279397559</v>
+        <v>-1.55542727939757</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -2944,37 +2944,37 @@
         <v>14</v>
       </c>
       <c r="D44" s="1">
-        <v>3468</v>
+        <v>3473</v>
       </c>
       <c r="E44" s="2">
-        <v>0.8949823288132678</v>
+        <v>0.8960717880455499</v>
       </c>
       <c r="F44" s="2">
-        <v>0.8896079030766169</v>
+        <v>0.8904269118708189</v>
       </c>
       <c r="G44" s="3">
-        <v>0.5374425736650923</v>
+        <v>0.5644876174730973</v>
       </c>
       <c r="H44">
         <v>14</v>
       </c>
       <c r="I44" s="1">
-        <v>1709</v>
+        <v>1566</v>
       </c>
       <c r="J44" s="2">
-        <v>0.8819088180258848</v>
+        <v>0.8819088180258849</v>
       </c>
       <c r="K44" s="2">
         <v>0.8797797975461918</v>
       </c>
       <c r="L44" s="3">
-        <v>0.2129020479692989</v>
+        <v>0.21290204796931</v>
       </c>
       <c r="M44">
         <v>14</v>
       </c>
       <c r="N44" s="1">
-        <v>1760</v>
+        <v>1906</v>
       </c>
       <c r="O44" s="2">
         <v>0.9080558396006508</v>
@@ -3000,43 +3000,43 @@
         <v>340</v>
       </c>
       <c r="E45" s="2">
-        <v>0.8881371459883856</v>
+        <v>0.8877423222120192</v>
       </c>
       <c r="F45" s="2">
-        <v>0.8896079030766169</v>
+        <v>0.8904269118708189</v>
       </c>
       <c r="G45" s="3">
-        <v>-0.14707570882313</v>
+        <v>-0.2684589658799696</v>
       </c>
       <c r="H45">
         <v>2</v>
       </c>
       <c r="I45" s="1">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="J45" s="2">
-        <v>0.8928750313047832</v>
+        <v>0.8928750313047834</v>
       </c>
       <c r="K45" s="2">
         <v>0.8797797975461918</v>
       </c>
       <c r="L45" s="3">
-        <v>1.309523375859134</v>
+        <v>1.309523375859156</v>
       </c>
       <c r="M45">
         <v>2</v>
       </c>
       <c r="N45" s="1">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="O45" s="2">
-        <v>0.8833992606719878</v>
+        <v>0.8833992606719879</v>
       </c>
       <c r="P45" s="2">
         <v>0.8994360086070419</v>
       </c>
       <c r="Q45" s="3">
-        <v>-1.603674793505405</v>
+        <v>-1.603674793505394</v>
       </c>
     </row>
     <row r="46" spans="1:17">
@@ -3050,28 +3050,28 @@
         <v>12</v>
       </c>
       <c r="D46" s="1">
-        <v>2869</v>
+        <v>2872</v>
       </c>
       <c r="E46" s="2">
-        <v>0.866034093501505</v>
+        <v>0.8704321489919538</v>
       </c>
       <c r="F46" s="2">
-        <v>0.8901845880970316</v>
+        <v>0.8916101253733195</v>
       </c>
       <c r="G46" s="3">
-        <v>-2.415049459552665</v>
+        <v>-2.117797638136576</v>
       </c>
       <c r="H46">
         <v>12</v>
       </c>
       <c r="I46" s="1">
-        <v>1417</v>
+        <v>1299</v>
       </c>
       <c r="J46" s="2">
-        <v>0.8158870585045082</v>
+        <v>0.8158870585045083</v>
       </c>
       <c r="K46" s="2">
-        <v>0.8731126143424988</v>
+        <v>0.8731126143424989</v>
       </c>
       <c r="L46" s="3">
         <v>-5.72255558379906</v>
@@ -3080,16 +3080,16 @@
         <v>11</v>
       </c>
       <c r="N46" s="1">
-        <v>1453</v>
+        <v>1574</v>
       </c>
       <c r="O46" s="2">
         <v>0.9212612411742847</v>
       </c>
       <c r="P46" s="2">
-        <v>0.9073203142788924</v>
+        <v>0.9073203142788925</v>
       </c>
       <c r="Q46" s="3">
-        <v>1.394092689539228</v>
+        <v>1.394092689539217</v>
       </c>
     </row>
     <row r="47" spans="1:17">
@@ -3103,46 +3103,46 @@
         <v>1</v>
       </c>
       <c r="D47" s="1">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E47" s="2">
-        <v>0.7223892940631138</v>
+        <v>0.7325504689238594</v>
       </c>
       <c r="F47" s="2">
-        <v>0.8901845880970316</v>
+        <v>0.8916101253733195</v>
       </c>
       <c r="G47" s="3">
-        <v>-16.77952940339178</v>
+        <v>-15.90596564494601</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47" s="1">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J47" s="2">
         <v>0.6004551957341656</v>
       </c>
       <c r="K47" s="2">
-        <v>0.8731126143424988</v>
+        <v>0.8731126143424989</v>
       </c>
       <c r="L47" s="3">
-        <v>-27.26574186083332</v>
+        <v>-27.26574186083333</v>
       </c>
       <c r="M47">
         <v>1</v>
       </c>
       <c r="N47" s="1">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="O47" s="2">
-        <v>0.844323392392062</v>
+        <v>0.8443233923920619</v>
       </c>
       <c r="P47" s="2">
-        <v>0.9073203142788924</v>
+        <v>0.9073203142788925</v>
       </c>
       <c r="Q47" s="3">
-        <v>-6.299692188683037</v>
+        <v>-6.299692188683059</v>
       </c>
     </row>
     <row r="48" spans="1:17">
@@ -3156,46 +3156,46 @@
         <v>14</v>
       </c>
       <c r="D48" s="1">
-        <v>3444</v>
+        <v>3448</v>
       </c>
       <c r="E48" s="2">
-        <v>0.9233149690798519</v>
+        <v>0.9213447249166987</v>
       </c>
       <c r="F48" s="2">
-        <v>0.8901845880970316</v>
+        <v>0.8916101253733195</v>
       </c>
       <c r="G48" s="3">
-        <v>3.313038098282028</v>
+        <v>2.97345995433792</v>
       </c>
       <c r="H48">
         <v>13</v>
       </c>
       <c r="I48" s="1">
-        <v>1699</v>
+        <v>1558</v>
       </c>
       <c r="J48" s="2">
         <v>0.9479953082803935</v>
       </c>
       <c r="K48" s="2">
-        <v>0.8731126143424988</v>
+        <v>0.8731126143424989</v>
       </c>
       <c r="L48" s="3">
-        <v>7.488269393789471</v>
+        <v>7.48826939378946</v>
       </c>
       <c r="M48">
         <v>14</v>
       </c>
       <c r="N48" s="1">
-        <v>1745</v>
+        <v>1890</v>
       </c>
       <c r="O48" s="2">
         <v>0.9004840678189734</v>
       </c>
       <c r="P48" s="2">
-        <v>0.9073203142788924</v>
+        <v>0.9073203142788925</v>
       </c>
       <c r="Q48" s="3">
-        <v>-0.6836246459918982</v>
+        <v>-0.6836246459919093</v>
       </c>
     </row>
     <row r="49" spans="1:17">
@@ -3212,43 +3212,43 @@
         <v>358</v>
       </c>
       <c r="E49" s="2">
-        <v>0.9363880380409306</v>
+        <v>0.9351698806244261</v>
       </c>
       <c r="F49" s="2">
-        <v>0.8901845880970316</v>
+        <v>0.8916101253733195</v>
       </c>
       <c r="G49" s="3">
-        <v>4.620344994389902</v>
+        <v>4.355975525110656</v>
       </c>
       <c r="H49">
         <v>2</v>
       </c>
       <c r="I49" s="1">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="J49" s="2">
         <v>0.9510059270389848</v>
       </c>
       <c r="K49" s="2">
-        <v>0.8731126143424988</v>
+        <v>0.8731126143424989</v>
       </c>
       <c r="L49" s="3">
-        <v>7.789331269648603</v>
+        <v>7.789331269648592</v>
       </c>
       <c r="M49">
         <v>2</v>
       </c>
       <c r="N49" s="1">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="O49" s="2">
         <v>0.9217701490428762</v>
       </c>
       <c r="P49" s="2">
-        <v>0.9073203142788924</v>
+        <v>0.9073203142788925</v>
       </c>
       <c r="Q49" s="3">
-        <v>1.444983476398387</v>
+        <v>1.444983476398376</v>
       </c>
     </row>
     <row r="50" spans="1:17">
@@ -3262,46 +3262,46 @@
         <v>12</v>
       </c>
       <c r="D50" s="1">
-        <v>3015</v>
+        <v>3020</v>
       </c>
       <c r="E50" s="2">
-        <v>0.8680563109303734</v>
+        <v>0.8695394861897033</v>
       </c>
       <c r="F50" s="2">
-        <v>0.8911929620742598</v>
+        <v>0.8919409061730958</v>
       </c>
       <c r="G50" s="3">
-        <v>-2.313665114388641</v>
+        <v>-2.240141998339251</v>
       </c>
       <c r="H50">
         <v>12</v>
       </c>
       <c r="I50" s="1">
-        <v>1476</v>
+        <v>1353</v>
       </c>
       <c r="J50" s="2">
-        <v>0.850258207818413</v>
+        <v>0.8502582078184132</v>
       </c>
       <c r="K50" s="2">
         <v>0.8822176328882262</v>
       </c>
       <c r="L50" s="3">
-        <v>-3.19594250698132</v>
+        <v>-3.195942506981297</v>
       </c>
       <c r="M50">
         <v>12</v>
       </c>
       <c r="N50" s="1">
-        <v>1538</v>
+        <v>1666</v>
       </c>
       <c r="O50" s="2">
         <v>0.8858544140423334</v>
       </c>
       <c r="P50" s="2">
-        <v>0.9001682912602934</v>
+        <v>0.9001682912602933</v>
       </c>
       <c r="Q50" s="3">
-        <v>-1.431387721795996</v>
+        <v>-1.431387721795985</v>
       </c>
     </row>
     <row r="51" spans="1:17">
@@ -3318,40 +3318,40 @@
         <v>285</v>
       </c>
       <c r="E51" s="2">
-        <v>0.7803220384765451</v>
+        <v>0.7800925925925927</v>
       </c>
       <c r="F51" s="2">
-        <v>0.8911929620742598</v>
+        <v>0.8919409061730958</v>
       </c>
       <c r="G51" s="3">
-        <v>-11.08709235977147</v>
+        <v>-11.18483135805032</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51" s="1">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J51" s="2">
-        <v>0.7830753890839729</v>
+        <v>0.7830753890839728</v>
       </c>
       <c r="K51" s="2">
         <v>0.8822176328882262</v>
       </c>
       <c r="L51" s="3">
-        <v>-9.914224380425329</v>
+        <v>-9.91422438042534</v>
       </c>
       <c r="M51">
         <v>1</v>
       </c>
       <c r="N51" s="1">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="O51" s="2">
-        <v>0.7775686878691171</v>
+        <v>0.777568687869117</v>
       </c>
       <c r="P51" s="2">
-        <v>0.9001682912602934</v>
+        <v>0.9001682912602933</v>
       </c>
       <c r="Q51" s="3">
         <v>-12.25996033911763</v>
@@ -3368,22 +3368,22 @@
         <v>13</v>
       </c>
       <c r="D52" s="1">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="E52" s="2">
-        <v>0.9508504687262365</v>
+        <v>0.9505710717090947</v>
       </c>
       <c r="F52" s="2">
-        <v>0.8911929620742598</v>
+        <v>0.8919409061730958</v>
       </c>
       <c r="G52" s="3">
-        <v>5.965750665197667</v>
+        <v>5.863016553599887</v>
       </c>
       <c r="H52">
         <v>13</v>
       </c>
       <c r="I52" s="1">
-        <v>1710</v>
+        <v>1568</v>
       </c>
       <c r="J52" s="2">
         <v>0.9542032329319385</v>
@@ -3398,16 +3398,16 @@
         <v>13</v>
       </c>
       <c r="N52" s="1">
-        <v>1698</v>
+        <v>1840</v>
       </c>
       <c r="O52" s="2">
         <v>0.9474977045205345</v>
       </c>
       <c r="P52" s="2">
-        <v>0.9001682912602934</v>
+        <v>0.9001682912602933</v>
       </c>
       <c r="Q52" s="3">
-        <v>4.732941326024109</v>
+        <v>4.73294132602412</v>
       </c>
     </row>
     <row r="53" spans="1:17">
@@ -3421,46 +3421,46 @@
         <v>2</v>
       </c>
       <c r="D53" s="1">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E53" s="2">
-        <v>0.6481435995898805</v>
+        <v>0.6527745893276197</v>
       </c>
       <c r="F53" s="2">
-        <v>0.8911929620742598</v>
+        <v>0.8919409061730958</v>
       </c>
       <c r="G53" s="3">
-        <v>-24.30493624843793</v>
+        <v>-23.91663168454762</v>
       </c>
       <c r="H53">
         <v>2</v>
       </c>
       <c r="I53" s="1">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="J53" s="2">
-        <v>0.5925717227370119</v>
+        <v>0.5925717227370121</v>
       </c>
       <c r="K53" s="2">
         <v>0.8822176328882262</v>
       </c>
       <c r="L53" s="3">
-        <v>-28.96459101512143</v>
+        <v>-28.96459101512141</v>
       </c>
       <c r="M53">
         <v>2</v>
       </c>
       <c r="N53" s="1">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="O53" s="2">
         <v>0.7037154764427491</v>
       </c>
       <c r="P53" s="2">
-        <v>0.9001682912602934</v>
+        <v>0.9001682912602933</v>
       </c>
       <c r="Q53" s="3">
-        <v>-19.64528148175443</v>
+        <v>-19.64528148175442</v>
       </c>
     </row>
     <row r="54" spans="1:17">
@@ -3474,46 +3474,46 @@
         <v>12</v>
       </c>
       <c r="D54" s="1">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="E54" s="2">
-        <v>0.9104591727963224</v>
+        <v>0.9103590019154567</v>
       </c>
       <c r="F54" s="2">
-        <v>0.9228596929801954</v>
+        <v>0.9231384495294301</v>
       </c>
       <c r="G54" s="3">
-        <v>-1.240052018387305</v>
+        <v>-1.277944761397343</v>
       </c>
       <c r="H54">
         <v>12</v>
       </c>
       <c r="I54" s="1">
-        <v>1583</v>
+        <v>1451</v>
       </c>
       <c r="J54" s="2">
         <v>0.911661223366711</v>
       </c>
       <c r="K54" s="2">
-        <v>0.9195146143893789</v>
+        <v>0.9195146143893788</v>
       </c>
       <c r="L54" s="3">
-        <v>-0.785339102266791</v>
+        <v>-0.7853391022667799</v>
       </c>
       <c r="M54">
         <v>12</v>
       </c>
       <c r="N54" s="1">
-        <v>1579</v>
+        <v>1710</v>
       </c>
       <c r="O54" s="2">
-        <v>0.9092571222259339</v>
+        <v>0.909257122225934</v>
       </c>
       <c r="P54" s="2">
         <v>0.9262047715710119</v>
       </c>
       <c r="Q54" s="3">
-        <v>-1.694764934507798</v>
+        <v>-1.694764934507786</v>
       </c>
     </row>
     <row r="55" spans="1:17">
@@ -3530,25 +3530,25 @@
         <v>314</v>
       </c>
       <c r="E55" s="2">
-        <v>0.8597196794621688</v>
+        <v>0.8611150850421238</v>
       </c>
       <c r="F55" s="2">
-        <v>0.9228596929801954</v>
+        <v>0.9231384495294301</v>
       </c>
       <c r="G55" s="3">
-        <v>-6.314001351802667</v>
+        <v>-6.202336448730639</v>
       </c>
       <c r="H55">
         <v>1</v>
       </c>
       <c r="I55" s="1">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="J55" s="2">
-        <v>0.8429748125027097</v>
+        <v>0.8429748125027096</v>
       </c>
       <c r="K55" s="2">
-        <v>0.9195146143893789</v>
+        <v>0.9195146143893788</v>
       </c>
       <c r="L55" s="3">
         <v>-7.65398018866692</v>
@@ -3557,7 +3557,7 @@
         <v>1</v>
       </c>
       <c r="N55" s="1">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="O55" s="2">
         <v>0.876464546421628</v>
@@ -3580,46 +3580,46 @@
         <v>13</v>
       </c>
       <c r="D56" s="1">
-        <v>3364</v>
+        <v>3366</v>
       </c>
       <c r="E56" s="2">
-        <v>0.9384065590607483</v>
+        <v>0.9389221262924763</v>
       </c>
       <c r="F56" s="2">
-        <v>0.9228596929801954</v>
+        <v>0.9231384495294301</v>
       </c>
       <c r="G56" s="3">
-        <v>1.554686608055289</v>
+        <v>1.578367676304615</v>
       </c>
       <c r="H56">
         <v>13</v>
       </c>
       <c r="I56" s="1">
-        <v>1671</v>
+        <v>1532</v>
       </c>
       <c r="J56" s="2">
-        <v>0.9322197522800142</v>
+        <v>0.9322197522800143</v>
       </c>
       <c r="K56" s="2">
-        <v>0.9195146143893789</v>
+        <v>0.9195146143893788</v>
       </c>
       <c r="L56" s="3">
-        <v>1.270513789063532</v>
+        <v>1.270513789063554</v>
       </c>
       <c r="M56">
         <v>13</v>
       </c>
       <c r="N56" s="1">
-        <v>1693</v>
+        <v>1834</v>
       </c>
       <c r="O56" s="2">
-        <v>0.9445933658414826</v>
+        <v>0.9445933658414827</v>
       </c>
       <c r="P56" s="2">
         <v>0.9262047715710119</v>
       </c>
       <c r="Q56" s="3">
-        <v>1.838859427047068</v>
+        <v>1.838859427047079</v>
       </c>
     </row>
     <row r="57" spans="1:17">
@@ -3636,43 +3636,43 @@
         <v>364</v>
       </c>
       <c r="E57" s="2">
-        <v>0.9499738324118489</v>
+        <v>0.9504074839302112</v>
       </c>
       <c r="F57" s="2">
-        <v>0.9228596929801954</v>
+        <v>0.9231384495294301</v>
       </c>
       <c r="G57" s="3">
-        <v>2.711413943165342</v>
+        <v>2.72690344007811</v>
       </c>
       <c r="H57">
         <v>2</v>
       </c>
       <c r="I57" s="1">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="J57" s="2">
-        <v>0.9447700141915018</v>
+        <v>0.944770014191502</v>
       </c>
       <c r="K57" s="2">
-        <v>0.9195146143893789</v>
+        <v>0.9195146143893788</v>
       </c>
       <c r="L57" s="3">
-        <v>2.525539980212288</v>
+        <v>2.525539980212321</v>
       </c>
       <c r="M57">
         <v>2</v>
       </c>
       <c r="N57" s="1">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="O57" s="2">
-        <v>0.9551776506321961</v>
+        <v>0.955177650632196</v>
       </c>
       <c r="P57" s="2">
         <v>0.9262047715710119</v>
       </c>
       <c r="Q57" s="3">
-        <v>2.897287906118418</v>
+        <v>2.897287906118406</v>
       </c>
     </row>
     <row r="58" spans="1:17">
@@ -3686,46 +3686,46 @@
         <v>12</v>
       </c>
       <c r="D58" s="1">
-        <v>3062</v>
+        <v>3060</v>
       </c>
       <c r="E58" s="2">
-        <v>0.8817272991078755</v>
+        <v>0.8810449291573452</v>
       </c>
       <c r="F58" s="2">
-        <v>0.8832011896592704</v>
+        <v>0.8818391330542817</v>
       </c>
       <c r="G58" s="3">
-        <v>-0.1473890551394907</v>
+        <v>-0.07942038969365184</v>
       </c>
       <c r="H58">
         <v>12</v>
       </c>
       <c r="I58" s="1">
-        <v>1545</v>
+        <v>1416</v>
       </c>
       <c r="J58" s="2">
-        <v>0.8899157385142382</v>
+        <v>0.8899157385142384</v>
       </c>
       <c r="K58" s="2">
-        <v>0.8998879811680002</v>
+        <v>0.8998879811680001</v>
       </c>
       <c r="L58" s="3">
-        <v>-0.9972242653761954</v>
+        <v>-0.997224265376162</v>
       </c>
       <c r="M58">
         <v>12</v>
       </c>
       <c r="N58" s="1">
-        <v>1517</v>
+        <v>1643</v>
       </c>
       <c r="O58" s="2">
-        <v>0.8735388597015126</v>
+        <v>0.8735388597015127</v>
       </c>
       <c r="P58" s="2">
-        <v>0.8671352200822801</v>
+        <v>0.8671352200822799</v>
       </c>
       <c r="Q58" s="3">
-        <v>0.6403639619232515</v>
+        <v>0.6403639619232737</v>
       </c>
     </row>
     <row r="59" spans="1:17">
@@ -3739,43 +3739,43 @@
         <v>1</v>
       </c>
       <c r="D59" s="1">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E59" s="2">
-        <v>0.8404462252101738</v>
+        <v>0.8390180416467968</v>
       </c>
       <c r="F59" s="2">
-        <v>0.8832011896592704</v>
+        <v>0.8818391330542817</v>
       </c>
       <c r="G59" s="3">
-        <v>-4.275496444909665</v>
+        <v>-4.282109140748491</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59" s="1">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="J59" s="2">
-        <v>0.8575844279706941</v>
+        <v>0.8575844279706939</v>
       </c>
       <c r="K59" s="2">
-        <v>0.8998879811680002</v>
+        <v>0.8998879811680001</v>
       </c>
       <c r="L59" s="3">
-        <v>-4.230355319730606</v>
+        <v>-4.230355319730617</v>
       </c>
       <c r="M59">
         <v>1</v>
       </c>
       <c r="N59" s="1">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="O59" s="2">
-        <v>0.8233080224496533</v>
+        <v>0.8233080224496532</v>
       </c>
       <c r="P59" s="2">
-        <v>0.8671352200822801</v>
+        <v>0.8671352200822799</v>
       </c>
       <c r="Q59" s="3">
         <v>-4.382719763262677</v>
@@ -3792,46 +3792,46 @@
         <v>13</v>
       </c>
       <c r="D60" s="1">
-        <v>3030</v>
+        <v>3033</v>
       </c>
       <c r="E60" s="2">
-        <v>0.8807695193467282</v>
+        <v>0.8786854690824963</v>
       </c>
       <c r="F60" s="2">
-        <v>0.8832011896592704</v>
+        <v>0.8818391330542817</v>
       </c>
       <c r="G60" s="3">
-        <v>-0.2431670312542211</v>
+        <v>-0.3153663971785403</v>
       </c>
       <c r="H60">
         <v>12</v>
       </c>
       <c r="I60" s="1">
-        <v>1494</v>
+        <v>1370</v>
       </c>
       <c r="J60" s="2">
-        <v>0.9069721808246398</v>
+        <v>0.9069721808246399</v>
       </c>
       <c r="K60" s="2">
-        <v>0.8998879811680002</v>
+        <v>0.8998879811680001</v>
       </c>
       <c r="L60" s="3">
-        <v>0.7084199656639645</v>
+        <v>0.7084199656639867</v>
       </c>
       <c r="M60">
         <v>13</v>
       </c>
       <c r="N60" s="1">
-        <v>1536</v>
+        <v>1664</v>
       </c>
       <c r="O60" s="2">
-        <v>0.8566894283141819</v>
+        <v>0.856689428314182</v>
       </c>
       <c r="P60" s="2">
-        <v>0.8671352200822801</v>
+        <v>0.8671352200822799</v>
       </c>
       <c r="Q60" s="3">
-        <v>-1.044579176809812</v>
+        <v>-1.04457917680979</v>
       </c>
     </row>
     <row r="61" spans="1:17">
@@ -3848,43 +3848,43 @@
         <v>367</v>
       </c>
       <c r="E61" s="2">
-        <v>0.9591932248957041</v>
+        <v>0.9583154780124478</v>
       </c>
       <c r="F61" s="2">
-        <v>0.8832011896592704</v>
+        <v>0.8818391330542817</v>
       </c>
       <c r="G61" s="3">
-        <v>7.599203523643371</v>
+        <v>7.647634495816602</v>
       </c>
       <c r="H61">
         <v>2</v>
       </c>
       <c r="I61" s="1">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="J61" s="2">
-        <v>0.9697261874947825</v>
+        <v>0.9697261874947826</v>
       </c>
       <c r="K61" s="2">
-        <v>0.8998879811680002</v>
+        <v>0.8998879811680001</v>
       </c>
       <c r="L61" s="3">
-        <v>6.983820632678228</v>
+        <v>6.983820632678251</v>
       </c>
       <c r="M61">
         <v>2</v>
       </c>
       <c r="N61" s="1">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="O61" s="2">
-        <v>0.9486602622966257</v>
+        <v>0.9486602622966258</v>
       </c>
       <c r="P61" s="2">
-        <v>0.8671352200822801</v>
+        <v>0.8671352200822799</v>
       </c>
       <c r="Q61" s="3">
-        <v>8.152504221434565</v>
+        <v>8.152504221434587</v>
       </c>
     </row>
     <row r="62" spans="1:17">
@@ -3898,46 +3898,46 @@
         <v>12</v>
       </c>
       <c r="D62" s="1">
-        <v>2871</v>
+        <v>2893</v>
       </c>
       <c r="E62" s="2">
-        <v>0.8266992022321671</v>
+        <v>0.8329921882996301</v>
       </c>
       <c r="F62" s="2">
-        <v>0.8751218241573298</v>
+        <v>0.878462470772397</v>
       </c>
       <c r="G62" s="3">
-        <v>-4.842262192516267</v>
+        <v>-4.547028247276696</v>
       </c>
       <c r="H62">
         <v>12</v>
       </c>
       <c r="I62" s="1">
-        <v>1304</v>
+        <v>1196</v>
       </c>
       <c r="J62" s="2">
-        <v>0.7511833694226113</v>
+        <v>0.7511833694226114</v>
       </c>
       <c r="K62" s="2">
         <v>0.8350340647765211</v>
       </c>
       <c r="L62" s="3">
-        <v>-8.385069535390976</v>
+        <v>-8.385069535390965</v>
       </c>
       <c r="M62">
         <v>12</v>
       </c>
       <c r="N62" s="1">
-        <v>1567</v>
+        <v>1697</v>
       </c>
       <c r="O62" s="2">
-        <v>0.9022150350417226</v>
+        <v>0.9022150350417228</v>
       </c>
       <c r="P62" s="2">
-        <v>0.9152095835381384</v>
+        <v>0.9152095835381383</v>
       </c>
       <c r="Q62" s="3">
-        <v>-1.299454849641579</v>
+        <v>-1.299454849641546</v>
       </c>
     </row>
     <row r="63" spans="1:17">
@@ -3951,22 +3951,22 @@
         <v>1</v>
       </c>
       <c r="D63" s="1">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E63" s="2">
-        <v>0.7680162469862041</v>
+        <v>0.7700484819583532</v>
       </c>
       <c r="F63" s="2">
-        <v>0.8751218241573298</v>
+        <v>0.878462470772397</v>
       </c>
       <c r="G63" s="3">
-        <v>-10.71055771711257</v>
+        <v>-10.84139888140438</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63" s="1">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J63" s="2">
         <v>0.7436294273204145</v>
@@ -3981,16 +3981,16 @@
         <v>1</v>
       </c>
       <c r="N63" s="1">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="O63" s="2">
         <v>0.7924030666519937</v>
       </c>
       <c r="P63" s="2">
-        <v>0.9152095835381384</v>
+        <v>0.9152095835381383</v>
       </c>
       <c r="Q63" s="3">
-        <v>-12.28065168861447</v>
+        <v>-12.28065168861446</v>
       </c>
     </row>
     <row r="64" spans="1:17">
@@ -4004,46 +4004,46 @@
         <v>12</v>
       </c>
       <c r="D64" s="1">
-        <v>3079</v>
+        <v>3080</v>
       </c>
       <c r="E64" s="2">
-        <v>0.9345711087987254</v>
+        <v>0.9349950084068936</v>
       </c>
       <c r="F64" s="2">
-        <v>0.8751218241573298</v>
+        <v>0.878462470772397</v>
       </c>
       <c r="G64" s="3">
-        <v>5.944928464139565</v>
+        <v>5.653253763449662</v>
       </c>
       <c r="H64">
         <v>12</v>
       </c>
       <c r="I64" s="1">
-        <v>1531</v>
+        <v>1404</v>
       </c>
       <c r="J64" s="2">
-        <v>0.9294843135007068</v>
+        <v>0.929484313500707</v>
       </c>
       <c r="K64" s="2">
         <v>0.8350340647765211</v>
       </c>
       <c r="L64" s="3">
-        <v>9.445024872418573</v>
+        <v>9.445024872418594</v>
       </c>
       <c r="M64">
         <v>12</v>
       </c>
       <c r="N64" s="1">
-        <v>1548</v>
+        <v>1677</v>
       </c>
       <c r="O64" s="2">
         <v>0.9396579040967439</v>
       </c>
       <c r="P64" s="2">
-        <v>0.9152095835381384</v>
+        <v>0.9152095835381383</v>
       </c>
       <c r="Q64" s="3">
-        <v>2.444832055860546</v>
+        <v>2.444832055860557</v>
       </c>
     </row>
     <row r="65" spans="1:17">
@@ -4057,46 +4057,46 @@
         <v>2</v>
       </c>
       <c r="D65" s="1">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E65" s="2">
-        <v>0.9049063425096482</v>
+        <v>0.9078142536475869</v>
       </c>
       <c r="F65" s="2">
-        <v>0.8751218241573298</v>
+        <v>0.878462470772397</v>
       </c>
       <c r="G65" s="3">
-        <v>2.978451835231843</v>
+        <v>2.935178287518991</v>
       </c>
       <c r="H65">
         <v>2</v>
       </c>
       <c r="I65" s="1">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="J65" s="2">
-        <v>0.870011408854384</v>
+        <v>0.8700114088543841</v>
       </c>
       <c r="K65" s="2">
         <v>0.8350340647765211</v>
       </c>
       <c r="L65" s="3">
-        <v>3.49773440778629</v>
+        <v>3.497734407786302</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65" s="1">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="O65" s="2">
         <v>0.9398012761649124</v>
       </c>
       <c r="P65" s="2">
-        <v>0.9152095835381384</v>
+        <v>0.9152095835381383</v>
       </c>
       <c r="Q65" s="3">
-        <v>2.459169262677396</v>
+        <v>2.459169262677408</v>
       </c>
     </row>
     <row r="66" spans="1:17">
@@ -4110,46 +4110,46 @@
         <v>12</v>
       </c>
       <c r="D66" s="1">
-        <v>2283</v>
+        <v>2326</v>
       </c>
       <c r="E66" s="2">
-        <v>0.6573617219294281</v>
+        <v>0.6699163632641721</v>
       </c>
       <c r="F66" s="2">
-        <v>0.6913538250570118</v>
+        <v>0.7050154264312666</v>
       </c>
       <c r="G66" s="3">
-        <v>-3.399210312758372</v>
+        <v>-3.509906316709444</v>
       </c>
       <c r="H66">
         <v>12</v>
       </c>
       <c r="I66" s="1">
-        <v>880</v>
+        <v>807</v>
       </c>
       <c r="J66" s="2">
-        <v>0.5067060259125004</v>
+        <v>0.5067060259125005</v>
       </c>
       <c r="K66" s="2">
         <v>0.5315285559222972</v>
       </c>
       <c r="L66" s="3">
-        <v>-2.482253000979684</v>
+        <v>-2.482253000979673</v>
       </c>
       <c r="M66">
         <v>12</v>
       </c>
       <c r="N66" s="1">
-        <v>1403</v>
+        <v>1520</v>
       </c>
       <c r="O66" s="2">
-        <v>0.8080174179463558</v>
+        <v>0.808017417946356</v>
       </c>
       <c r="P66" s="2">
         <v>0.8589431775079349</v>
       </c>
       <c r="Q66" s="3">
-        <v>-5.092575956157908</v>
+        <v>-5.092575956157896</v>
       </c>
     </row>
     <row r="67" spans="1:17">
@@ -4163,22 +4163,22 @@
         <v>2</v>
       </c>
       <c r="D67" s="1">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E67" s="2">
-        <v>0.5906869954080255</v>
+        <v>0.6020723482526057</v>
       </c>
       <c r="F67" s="2">
-        <v>0.6913538250570118</v>
+        <v>0.7050154264312666</v>
       </c>
       <c r="G67" s="3">
-        <v>-10.06668296489863</v>
+        <v>-10.29430781786609</v>
       </c>
       <c r="H67">
         <v>2</v>
       </c>
       <c r="I67" s="1">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="J67" s="2">
         <v>0.4910651580179477</v>
@@ -4193,16 +4193,16 @@
         <v>1</v>
       </c>
       <c r="N67" s="1">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="O67" s="2">
-        <v>0.789930670188181</v>
+        <v>0.7899306701881808</v>
       </c>
       <c r="P67" s="2">
         <v>0.8589431775079349</v>
       </c>
       <c r="Q67" s="3">
-        <v>-6.901250731975395</v>
+        <v>-6.901250731975416</v>
       </c>
     </row>
     <row r="68" spans="1:17">
@@ -4216,37 +4216,37 @@
         <v>12</v>
       </c>
       <c r="D68" s="1">
-        <v>2445</v>
+        <v>2493</v>
       </c>
       <c r="E68" s="2">
-        <v>0.7421922444936315</v>
+        <v>0.7567654476670871</v>
       </c>
       <c r="F68" s="2">
-        <v>0.6913538250570118</v>
+        <v>0.7050154264312666</v>
       </c>
       <c r="G68" s="3">
-        <v>5.083841943661971</v>
+        <v>5.17500212358205</v>
       </c>
       <c r="H68">
         <v>12</v>
       </c>
       <c r="I68" s="1">
-        <v>935</v>
+        <v>857</v>
       </c>
       <c r="J68" s="2">
-        <v>0.567313806412167</v>
+        <v>0.5673138064121671</v>
       </c>
       <c r="K68" s="2">
         <v>0.5315285559222972</v>
       </c>
       <c r="L68" s="3">
-        <v>3.57852504898698</v>
+        <v>3.578525048986991</v>
       </c>
       <c r="M68">
         <v>12</v>
       </c>
       <c r="N68" s="1">
-        <v>1511</v>
+        <v>1637</v>
       </c>
       <c r="O68" s="2">
         <v>0.9170706825750962</v>
@@ -4269,46 +4269,46 @@
         <v>2</v>
       </c>
       <c r="D69" s="1">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E69" s="2">
-        <v>0.7061979725202865</v>
+        <v>0.7212216865625958</v>
       </c>
       <c r="F69" s="2">
-        <v>0.6913538250570118</v>
+        <v>0.7050154264312666</v>
       </c>
       <c r="G69" s="3">
-        <v>1.484414746327467</v>
+        <v>1.62062601313292</v>
       </c>
       <c r="H69">
         <v>2</v>
       </c>
       <c r="I69" s="1">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="J69" s="2">
-        <v>0.5259134040125775</v>
+        <v>0.5259134040125777</v>
       </c>
       <c r="K69" s="2">
         <v>0.5315285559222972</v>
       </c>
       <c r="L69" s="3">
-        <v>-0.5615151909719729</v>
+        <v>-0.5615151909719507</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69" s="1">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="O69" s="2">
-        <v>0.8864825410279955</v>
+        <v>0.8864825410279954</v>
       </c>
       <c r="P69" s="2">
         <v>0.8589431775079349</v>
       </c>
       <c r="Q69" s="3">
-        <v>2.753936352006059</v>
+        <v>2.753936352006048</v>
       </c>
     </row>
     <row r="70" spans="1:17">
@@ -4322,37 +4322,37 @@
         <v>11</v>
       </c>
       <c r="D70" s="1">
-        <v>2863</v>
+        <v>2867</v>
       </c>
       <c r="E70" s="2">
-        <v>0.8964080781839797</v>
+        <v>0.8977507075621701</v>
       </c>
       <c r="F70" s="2">
-        <v>0.9089425774522214</v>
+        <v>0.9097412475239556</v>
       </c>
       <c r="G70" s="3">
-        <v>-1.253449926824168</v>
+        <v>-1.199053996178545</v>
       </c>
       <c r="H70">
         <v>11</v>
       </c>
       <c r="I70" s="1">
-        <v>1406</v>
+        <v>1288</v>
       </c>
       <c r="J70" s="2">
-        <v>0.8802965256456955</v>
+        <v>0.8802965256456957</v>
       </c>
       <c r="K70" s="2">
         <v>0.8993585365914101</v>
       </c>
       <c r="L70" s="3">
-        <v>-1.906201094571458</v>
+        <v>-1.906201094571436</v>
       </c>
       <c r="M70">
         <v>11</v>
       </c>
       <c r="N70" s="1">
-        <v>1457</v>
+        <v>1578</v>
       </c>
       <c r="O70" s="2">
         <v>0.9125196307222637</v>
@@ -4375,46 +4375,46 @@
         <v>2</v>
       </c>
       <c r="D71" s="1">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E71" s="2">
-        <v>0.8008252715334261</v>
+        <v>0.8047995151804165</v>
       </c>
       <c r="F71" s="2">
-        <v>0.9089425774522214</v>
+        <v>0.9097412475239556</v>
       </c>
       <c r="G71" s="3">
-        <v>-10.81173059187953</v>
+        <v>-10.49417323435391</v>
       </c>
       <c r="H71">
         <v>2</v>
       </c>
       <c r="I71" s="1">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="J71" s="2">
-        <v>0.753134347769541</v>
+        <v>0.7531343477695408</v>
       </c>
       <c r="K71" s="2">
         <v>0.8993585365914101</v>
       </c>
       <c r="L71" s="3">
-        <v>-14.6224188821869</v>
+        <v>-14.62241888218693</v>
       </c>
       <c r="M71">
         <v>2</v>
       </c>
       <c r="N71" s="1">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="O71" s="2">
-        <v>0.8485161952973113</v>
+        <v>0.8485161952973111</v>
       </c>
       <c r="P71" s="2">
         <v>0.9185266183130327</v>
       </c>
       <c r="Q71" s="3">
-        <v>-7.001042301572147</v>
+        <v>-7.001042301572157</v>
       </c>
     </row>
     <row r="72" spans="1:17">
@@ -4428,46 +4428,46 @@
         <v>12</v>
       </c>
       <c r="D72" s="1">
-        <v>3115</v>
+        <v>3113</v>
       </c>
       <c r="E72" s="2">
-        <v>0.9454178828737466</v>
+        <v>0.9450226810985008</v>
       </c>
       <c r="F72" s="2">
-        <v>0.9089425774522214</v>
+        <v>0.9097412475239556</v>
       </c>
       <c r="G72" s="3">
-        <v>3.647530542152522</v>
+        <v>3.528143357454527</v>
       </c>
       <c r="H72">
         <v>12</v>
       </c>
       <c r="I72" s="1">
-        <v>1565</v>
+        <v>1435</v>
       </c>
       <c r="J72" s="2">
-        <v>0.9501603041766975</v>
+        <v>0.9501603041766977</v>
       </c>
       <c r="K72" s="2">
         <v>0.8993585365914101</v>
       </c>
       <c r="L72" s="3">
-        <v>5.080176758528743</v>
+        <v>5.080176758528765</v>
       </c>
       <c r="M72">
         <v>12</v>
       </c>
       <c r="N72" s="1">
-        <v>1550</v>
+        <v>1679</v>
       </c>
       <c r="O72" s="2">
-        <v>0.9406754615707957</v>
+        <v>0.9406754615707958</v>
       </c>
       <c r="P72" s="2">
         <v>0.9185266183130327</v>
       </c>
       <c r="Q72" s="3">
-        <v>2.214884325776301</v>
+        <v>2.214884325776312</v>
       </c>
     </row>
     <row r="73" spans="1:17">
@@ -4484,34 +4484,34 @@
         <v>542</v>
       </c>
       <c r="E73" s="2">
-        <v>0.9069374057315234</v>
+        <v>0.907531045751634</v>
       </c>
       <c r="F73" s="2">
-        <v>0.9089425774522214</v>
+        <v>0.9097412475239556</v>
       </c>
       <c r="G73" s="3">
-        <v>-0.2005171720698029</v>
+        <v>-0.2210201772321563</v>
       </c>
       <c r="H73">
         <v>3</v>
       </c>
       <c r="I73" s="1">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="J73" s="2">
-        <v>0.899813725490196</v>
+        <v>0.8998137254901962</v>
       </c>
       <c r="K73" s="2">
         <v>0.8993585365914101</v>
       </c>
       <c r="L73" s="3">
-        <v>0.04551888987859298</v>
+        <v>0.04551888987861519</v>
       </c>
       <c r="M73">
         <v>3</v>
       </c>
       <c r="N73" s="1">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="O73" s="2">
         <v>0.9140610859728506</v>
@@ -57598,10 +57598,10 @@
         <v>8000</v>
       </c>
       <c r="F2">
-        <v>4006</v>
+        <v>4007</v>
       </c>
       <c r="G2" s="5">
-        <v>3994</v>
+        <v>3993</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -57621,10 +57621,10 @@
         <v>7650</v>
       </c>
       <c r="F3">
-        <v>4064</v>
+        <v>4070</v>
       </c>
       <c r="G3" s="5">
-        <v>3586</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -57644,10 +57644,10 @@
         <v>7700</v>
       </c>
       <c r="F4">
-        <v>1823</v>
+        <v>1830</v>
       </c>
       <c r="G4" s="5">
-        <v>5877</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -57667,10 +57667,10 @@
         <v>6800</v>
       </c>
       <c r="F5">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G5" s="5">
-        <v>6272</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -57736,10 +57736,10 @@
         <v>8000</v>
       </c>
       <c r="F8">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="G8" s="5">
-        <v>6168</v>
+        <v>6159</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -57759,10 +57759,10 @@
         <v>6400</v>
       </c>
       <c r="F9">
-        <v>5131</v>
+        <v>5135</v>
       </c>
       <c r="G9" s="5">
-        <v>1269</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -57782,10 +57782,10 @@
         <v>7700</v>
       </c>
       <c r="F10">
-        <v>4133</v>
+        <v>4132</v>
       </c>
       <c r="G10" s="5">
-        <v>3567</v>
+        <v>3568</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -57805,10 +57805,10 @@
         <v>5300</v>
       </c>
       <c r="F11">
-        <v>5110</v>
+        <v>5112</v>
       </c>
       <c r="G11" s="5">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -57828,10 +57828,10 @@
         <v>7750</v>
       </c>
       <c r="F12">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="G12" s="5">
-        <v>6131</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -57851,10 +57851,10 @@
         <v>8000</v>
       </c>
       <c r="F13">
-        <v>4096</v>
+        <v>4114</v>
       </c>
       <c r="G13" s="5">
-        <v>3904</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -57874,10 +57874,10 @@
         <v>8000</v>
       </c>
       <c r="F14">
-        <v>3115</v>
+        <v>3124</v>
       </c>
       <c r="G14" s="5">
-        <v>4885</v>
+        <v>4876</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -57897,10 +57897,10 @@
         <v>8000</v>
       </c>
       <c r="F15">
-        <v>5154</v>
+        <v>5156</v>
       </c>
       <c r="G15" s="5">
-        <v>2846</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -57920,10 +57920,10 @@
         <v>7700</v>
       </c>
       <c r="F16">
-        <v>4333</v>
+        <v>4334</v>
       </c>
       <c r="G16" s="5">
-        <v>3367</v>
+        <v>3366</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -57943,10 +57943,10 @@
         <v>8000</v>
       </c>
       <c r="F17">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="G17" s="5">
-        <v>5853</v>
+        <v>5851</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -57966,10 +57966,10 @@
         <v>9600</v>
       </c>
       <c r="F18">
-        <v>1552</v>
+        <v>1561</v>
       </c>
       <c r="G18" s="5">
-        <v>8048</v>
+        <v>8039</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -57989,10 +57989,10 @@
         <v>9600</v>
       </c>
       <c r="F19">
-        <v>4583</v>
+        <v>4595</v>
       </c>
       <c r="G19" s="5">
-        <v>5017</v>
+        <v>5005</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -58012,10 +58012,10 @@
         <v>9600</v>
       </c>
       <c r="F20">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="G20" s="5">
-        <v>7183</v>
+        <v>7181</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -58058,10 +58058,10 @@
         <v>8000</v>
       </c>
       <c r="F22">
-        <v>1918</v>
+        <v>1922</v>
       </c>
       <c r="G22" s="5">
-        <v>6082</v>
+        <v>6078</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -58081,10 +58081,10 @@
         <v>6750</v>
       </c>
       <c r="F23">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="G23" s="5">
-        <v>6428</v>
+        <v>6423</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -58104,10 +58104,10 @@
         <v>7700</v>
       </c>
       <c r="F24">
-        <v>3096</v>
+        <v>3093</v>
       </c>
       <c r="G24" s="5">
-        <v>4604</v>
+        <v>4607</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -58127,10 +58127,10 @@
         <v>8000</v>
       </c>
       <c r="F25">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G25" s="5">
-        <v>7815</v>
+        <v>7814</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -58150,10 +58150,10 @@
         <v>13350</v>
       </c>
       <c r="F26">
-        <v>5430</v>
+        <v>5431</v>
       </c>
       <c r="G26" s="5">
-        <v>7920</v>
+        <v>7919</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -58196,10 +58196,10 @@
         <v>9600</v>
       </c>
       <c r="F28">
-        <v>4695</v>
+        <v>4699</v>
       </c>
       <c r="G28" s="5">
-        <v>4905</v>
+        <v>4901</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -58260,7 +58260,7 @@
         <v>127</v>
       </c>
       <c r="C2" s="6">
-        <v>1399.573670154844</v>
+        <v>1399.381603273809</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>36</v>
